--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -15,10 +15,10 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$K$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$K$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B5" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$288,A5)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$290,A5)</f>
         <v/>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B6" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$288,A6)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$290,A6)</f>
         <v/>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B7" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$288,A7)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$290,A7)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B8" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$288,A8)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$290,A8)</f>
         <v/>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="B9" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$288,A9)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$290,A9)</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B10" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$288,A10)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$290,A10)</f>
         <v/>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B11" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$288,A11)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$290,A11)</f>
         <v/>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="B12" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$288,A12)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$290,A12)</f>
         <v/>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B16" s="19">
-        <f>COUNTIFS(Tasks!$A$2:$A$288,"HR-*",Tasks!$E$2:$E$288,"Done")+COUNTIFS(Tasks!$A$2:$A$288,"HR-*",Tasks!$E$2:$E$288,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$290,"HR-*",Tasks!$E$2:$E$290,"Done")+COUNTIFS(Tasks!$A$2:$A$290,"HR-*",Tasks!$E$2:$E$290,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C16" s="19">
@@ -1107,7 +1107,7 @@
         <v/>
       </c>
       <c r="D16" s="19">
-        <f>COUNTIF(Tasks!$A$2:$A$288,"HR-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$290,"HR-*")</f>
         <v/>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B17" s="19">
-        <f>COUNTIFS(Tasks!$A$2:$A$288,"JM-*",Tasks!$E$2:$E$288,"Done")+COUNTIFS(Tasks!$A$2:$A$288,"JM-*",Tasks!$E$2:$E$288,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$290,"JM-*",Tasks!$E$2:$E$290,"Done")+COUNTIFS(Tasks!$A$2:$A$290,"JM-*",Tasks!$E$2:$E$290,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C17" s="19">
@@ -1126,7 +1126,7 @@
         <v/>
       </c>
       <c r="D17" s="19">
-        <f>COUNTIF(Tasks!$A$2:$A$288,"JM-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$290,"JM-*")</f>
         <v/>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B20" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$288,"Earlier (May – 5 Oct 2026)")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$290,"Earlier (May – 5 Oct 2026)")</f>
         <v/>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="B21" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$288,"19 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$290,"19 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B22" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$288,"20 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$290,"20 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="B23" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$288,"21 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$290,"21 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="B24" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$288,"22 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$290,"22 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B25" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$288,"—")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$290,"—")</f>
         <v/>
       </c>
     </row>
@@ -1269,39 +1269,39 @@
         </is>
       </c>
       <c r="B28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A28,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A28,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A28,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A28,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A28,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A28,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A28,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A28,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J28" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A28)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A28)</f>
         <v/>
       </c>
     </row>
@@ -1312,39 +1312,39 @@
         </is>
       </c>
       <c r="B29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A29,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A29,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A29,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A29,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A29,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A29,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A29,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A29,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J29" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A29)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A29)</f>
         <v/>
       </c>
     </row>
@@ -1355,39 +1355,39 @@
         </is>
       </c>
       <c r="B30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A30,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A30,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A30,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A30,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A30,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A30,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A30,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A30,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J30" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A30)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A30)</f>
         <v/>
       </c>
     </row>
@@ -1398,39 +1398,39 @@
         </is>
       </c>
       <c r="B31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A31,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A31,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A31,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A31,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A31,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A31,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A31,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A31,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J31" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A31)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A31)</f>
         <v/>
       </c>
     </row>
@@ -1441,39 +1441,39 @@
         </is>
       </c>
       <c r="B32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A32,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A32,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A32,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A32,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A32,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A32,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A32,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A32,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J32" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A32)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A32)</f>
         <v/>
       </c>
     </row>
@@ -1484,39 +1484,39 @@
         </is>
       </c>
       <c r="B33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A33,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A33,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A33,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A33,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A33,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A33,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A33,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A33,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J33" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A33)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A33)</f>
         <v/>
       </c>
     </row>
@@ -1527,39 +1527,39 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A34,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A34,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A34,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A34,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A34,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A34,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A34,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A34,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J34" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A34)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A34)</f>
         <v/>
       </c>
     </row>
@@ -1570,39 +1570,39 @@
         </is>
       </c>
       <c r="B35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A35,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A35,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A35,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A35,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A35,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A35,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A35,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A35,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J35" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A35)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A35)</f>
         <v/>
       </c>
     </row>
@@ -1613,39 +1613,39 @@
         </is>
       </c>
       <c r="B36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A36,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A36,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A36,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A36,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A36,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A36,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A36,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A36,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J36" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A36)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A36)</f>
         <v/>
       </c>
     </row>
@@ -1656,39 +1656,39 @@
         </is>
       </c>
       <c r="B37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A37,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A37,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A37,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A37,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A37,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A37,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A37,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A37,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J37" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A37)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A37)</f>
         <v/>
       </c>
     </row>
@@ -1699,39 +1699,39 @@
         </is>
       </c>
       <c r="B38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A38,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A38,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A38,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A38,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A38,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A38,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A38,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A38,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J38" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A38)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A38)</f>
         <v/>
       </c>
     </row>
@@ -1742,39 +1742,39 @@
         </is>
       </c>
       <c r="B39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A39,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A39,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A39,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A39,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A39,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A39,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A39,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A39,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J39" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A39)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A39)</f>
         <v/>
       </c>
     </row>
@@ -1785,39 +1785,39 @@
         </is>
       </c>
       <c r="B40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A40,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A40,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A40,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A40,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A40,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A40,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A40,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A40,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J40" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A40)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A40)</f>
         <v/>
       </c>
     </row>
@@ -1828,39 +1828,39 @@
         </is>
       </c>
       <c r="B41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A41,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A41,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A41,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A41,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A41,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A41,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A41,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A41,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J41" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A41)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A41)</f>
         <v/>
       </c>
     </row>
@@ -1871,39 +1871,39 @@
         </is>
       </c>
       <c r="B42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A42,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A42,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A42,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A42,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A42,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A42,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A42,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A42,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J42" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A42)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A42)</f>
         <v/>
       </c>
     </row>
@@ -1914,39 +1914,39 @@
         </is>
       </c>
       <c r="B43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A43,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A43,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A43,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A43,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A43,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A43,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A43,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A43,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J43" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A43)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A43)</f>
         <v/>
       </c>
     </row>
@@ -1957,39 +1957,39 @@
         </is>
       </c>
       <c r="B44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A44,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A44,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A44,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A44,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A44,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A44,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A44,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A44,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J44" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A44)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A44)</f>
         <v/>
       </c>
     </row>
@@ -2000,39 +2000,39 @@
         </is>
       </c>
       <c r="B45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A45,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A45,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A45,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A45,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A45,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A45,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A45,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A45,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J45" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A45)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A45)</f>
         <v/>
       </c>
     </row>
@@ -2043,39 +2043,39 @@
         </is>
       </c>
       <c r="B46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A46,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A46,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A46,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A46,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A46,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A46,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A46,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A46,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J46" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A46)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A46)</f>
         <v/>
       </c>
     </row>
@@ -2086,39 +2086,39 @@
         </is>
       </c>
       <c r="B47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A47,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A47,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A47,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A47,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A47,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A47,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A47,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A47,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J47" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A47)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A47)</f>
         <v/>
       </c>
     </row>
@@ -2129,39 +2129,39 @@
         </is>
       </c>
       <c r="B48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A48,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A48,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A48,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A48,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A48,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A48,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A48,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A48,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J48" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A48)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A48)</f>
         <v/>
       </c>
     </row>
@@ -2172,39 +2172,39 @@
         </is>
       </c>
       <c r="B49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A49,Tasks!$E$2:$E$288,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,B$27)</f>
         <v/>
       </c>
       <c r="C49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A49,Tasks!$E$2:$E$288,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,C$27)</f>
         <v/>
       </c>
       <c r="D49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A49,Tasks!$E$2:$E$288,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,D$27)</f>
         <v/>
       </c>
       <c r="E49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A49,Tasks!$E$2:$E$288,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,E$27)</f>
         <v/>
       </c>
       <c r="F49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A49,Tasks!$E$2:$E$288,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,F$27)</f>
         <v/>
       </c>
       <c r="G49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A49,Tasks!$E$2:$E$288,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,G$27)</f>
         <v/>
       </c>
       <c r="H49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A49,Tasks!$E$2:$E$288,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,H$27)</f>
         <v/>
       </c>
       <c r="I49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$288,$A49,Tasks!$E$2:$E$288,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,I$27)</f>
         <v/>
       </c>
       <c r="J49" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$288,$A49)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$290,$A49)</f>
         <v/>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="B52" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$142,A52)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$145,A52)</f>
         <v/>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="B53" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$142,A53)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$145,A53)</f>
         <v/>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="B54" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$142,A54)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$145,A54)</f>
         <v/>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B55" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$142,A55)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$145,A55)</f>
         <v/>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5430,74 +5430,74 @@
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-70</t>
         </is>
       </c>
       <c r="B56" s="30" t="inlineStr">
         <is>
-          <t>HR dashboard</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college design</t>
+          <t>Job application page update (Fathir) merged into the test branch</t>
         </is>
       </c>
       <c r="D56" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Done – client UAT pending</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Fathir + Abdul Hakeem</t>
         </is>
       </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H56" s="31" t="inlineStr">
         <is>
-          <t>Same look as the Education team's new portals (Instructor Portal): left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so Education's changes cannot break these pages.</t>
+          <t>Fathir's update (22 Oct, PR #2 to develop): grouped form sections, country codes on phone numbers, a PDF receipt after sending, English/Arabic name checks, 194 Arabic texts. Merged into feature/uat-2026-10-22 the same day; conflicts resolved keeping both sides (phone check and Ministry identity check both run; Identity Type and Number stay required; 'Job Rank' in Arabic stays المرتبة الوظيفية). Two clashes Git could not see were fixed (B-42, B-44). Our browser tests now go through the steps of the form. Browser tests re-run: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries.</t>
         </is>
       </c>
       <c r="I56" s="31" t="inlineStr">
         <is>
-          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
+          <t>Client UAT of the application form and the receipt (TC-REC-13, TC-REC-14). Fathir: the phone error message gives a Sri Lankan example (+94 77 123 4567); use a Saudi one (+966 5x xxx xxxx).</t>
         </is>
       </c>
       <c r="J56" s="31" t="inlineStr">
         <is>
-          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
+          <t>www/job-application.html; www/job_application.py; recruitment/receipt.py</t>
         </is>
       </c>
       <c r="K56" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
         <is>
-          <t>HR-62</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="B57" s="30" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>HR User could not open the Holiday List ('Not permitted')</t>
+          <t>HR Portal and Employee Portal in the new college design</t>
         </is>
       </c>
       <c r="D57" s="30" t="inlineStr">
@@ -5517,22 +5517,22 @@
       </c>
       <c r="G57" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H57" s="31" t="inlineStr">
         <is>
-          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
+          <t>Same look as the Education team's new portals (Instructor Portal): left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so Education's changes cannot break these pages.</t>
         </is>
       </c>
       <c r="I57" s="31" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
         </is>
       </c>
       <c r="J57" s="31" t="inlineStr">
         <is>
-          <t>hr_core_permissions.py</t>
+          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
         </is>
       </c>
       <c r="K57" s="30" t="inlineStr">
@@ -5544,17 +5544,17 @@
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-62</t>
         </is>
       </c>
       <c r="B58" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>Full end-to-end test with error sweep (round 3)</t>
+          <t>HR User could not open the Holiday List ('Not permitted')</t>
         </is>
       </c>
       <c r="D58" s="30" t="inlineStr">
@@ -5574,22 +5574,22 @@
       </c>
       <c r="G58" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H58" s="31" t="inlineStr">
         <is>
-          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
+          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
         </is>
       </c>
       <c r="I58" s="31" t="inlineStr">
         <is>
-          <t>Client UAT.</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="J58" s="31" t="inlineStr">
         <is>
-          <t>Test Report</t>
+          <t>hr_core_permissions.py</t>
         </is>
       </c>
       <c r="K58" s="30" t="inlineStr">
@@ -5601,32 +5601,32 @@
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-46</t>
         </is>
       </c>
       <c r="B59" s="30" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>System e-mail account password cannot be decrypted</t>
+          <t>Full end-to-end test with error sweep (round 3)</t>
         </is>
       </c>
       <c r="D59" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E59" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F59" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G59" s="30" t="inlineStr">
@@ -5636,17 +5636,17 @@
       </c>
       <c r="H59" s="31" t="inlineStr">
         <is>
-          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
+          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
         </is>
       </c>
       <c r="I59" s="31" t="inlineStr">
         <is>
-          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
+          <t>Client UAT.</t>
         </is>
       </c>
       <c r="J59" s="31" t="inlineStr">
         <is>
-          <t>Error Log; Email Queue</t>
+          <t>Test Report</t>
         </is>
       </c>
       <c r="K59" s="30" t="inlineStr">
@@ -5658,17 +5658,17 @@
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-47</t>
         </is>
       </c>
       <c r="B60" s="30" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>Instructor form: linking an Employee fails on save</t>
+          <t>System e-mail account password cannot be decrypted</t>
         </is>
       </c>
       <c r="D60" s="30" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Pending – other team</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Education team</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H60" s="31" t="inlineStr">
         <is>
-          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
+          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
         </is>
       </c>
       <c r="I60" s="31" t="inlineStr">
         <is>
-          <t>Education team: remove or map those fetches on Instructor.</t>
+          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
         </is>
       </c>
       <c r="J60" s="31" t="inlineStr">
         <is>
-          <t>education Instructor doctype</t>
+          <t>Error Log; Email Queue</t>
         </is>
       </c>
       <c r="K60" s="30" t="inlineStr">
@@ -5715,32 +5715,32 @@
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
         <is>
-          <t>HR-49</t>
+          <t>HR-48</t>
         </is>
       </c>
       <c r="B61" s="30" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Instructor form: linking an Employee fails on save</t>
         </is>
       </c>
       <c r="D61" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – other team</t>
         </is>
       </c>
       <c r="F61" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Education team</t>
         </is>
       </c>
       <c r="G61" s="30" t="inlineStr">
@@ -5750,17 +5750,17 @@
       </c>
       <c r="H61" s="31" t="inlineStr">
         <is>
-          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
+          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
         </is>
       </c>
       <c r="I61" s="31" t="inlineStr">
         <is>
-          <t>HR to use it to complete the data (HR-50 sheet).</t>
+          <t>Education team: remove or map those fetches on Instructor.</t>
         </is>
       </c>
       <c r="J61" s="31" t="inlineStr">
         <is>
-          <t>report/employees_missing_ministry_data</t>
+          <t>education Instructor doctype</t>
         </is>
       </c>
       <c r="K61" s="30" t="inlineStr">
@@ -5772,7 +5772,7 @@
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
         <is>
-          <t>HR-50</t>
+          <t>HR-49</t>
         </is>
       </c>
       <c r="B62" s="30" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="C62" s="31" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="D62" s="30" t="inlineStr">
@@ -5807,17 +5807,17 @@
       </c>
       <c r="H62" s="31" t="inlineStr">
         <is>
-          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
+          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
         </is>
       </c>
       <c r="I62" s="31" t="inlineStr">
         <is>
-          <t>HR to fill the sheet for all non-academic staff.</t>
+          <t>HR to use it to complete the data (HR-50 sheet).</t>
         </is>
       </c>
       <c r="J62" s="31" t="inlineStr">
         <is>
-          <t>employee_data_sheet.py</t>
+          <t>report/employees_missing_ministry_data</t>
         </is>
       </c>
       <c r="K62" s="30" t="inlineStr">
@@ -5829,17 +5829,17 @@
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
-          <t>HR-51</t>
+          <t>HR-50</t>
         </is>
       </c>
       <c r="B63" s="30" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>Unused duplicate of the applicant Ministry fields removed</t>
+          <t>Data sheet for non-academic staff</t>
         </is>
       </c>
       <c r="D63" s="30" t="inlineStr">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="G63" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H63" s="31" t="inlineStr">
         <is>
-          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
+          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
         </is>
       </c>
       <c r="I63" s="31" t="inlineStr">
         <is>
-          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
+          <t>HR to fill the sheet for all non-academic staff.</t>
         </is>
       </c>
       <c r="J63" s="31" t="inlineStr">
         <is>
-          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
+          <t>employee_data_sheet.py</t>
         </is>
       </c>
       <c r="K63" s="30" t="inlineStr">
@@ -5886,52 +5886,52 @@
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
-          <t>HR-52</t>
+          <t>HR-51</t>
         </is>
       </c>
       <c r="B64" s="30" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C64" s="31" t="inlineStr">
         <is>
-          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
+          <t>Unused duplicate of the applicant Ministry fields removed</t>
         </is>
       </c>
       <c r="D64" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H64" s="31" t="inlineStr">
         <is>
-          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
+          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
         </is>
       </c>
       <c r="I64" s="31" t="inlineStr">
         <is>
-          <t>Confirm whether 9-digit numbers must be accepted.</t>
+          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
         </is>
       </c>
       <c r="J64" s="31" t="inlineStr">
         <is>
-          <t>ministry_lookup_validation.py</t>
+          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
         </is>
       </c>
       <c r="K64" s="30" t="inlineStr">
@@ -5943,17 +5943,17 @@
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
-          <t>HR-53</t>
+          <t>HR-52</t>
         </is>
       </c>
       <c r="B65" s="30" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
+          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
         </is>
       </c>
       <c r="D65" s="30" t="inlineStr">
@@ -5963,32 +5963,32 @@
       </c>
       <c r="E65" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F65" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="G65" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H65" s="31" t="inlineStr">
         <is>
-          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
+          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr">
         <is>
-          <t>Complete or delete the demo record before go-live.</t>
+          <t>Confirm whether 9-digit numbers must be accepted.</t>
         </is>
       </c>
       <c r="J65" s="31" t="inlineStr">
         <is>
-          <t>Employee EMP-00001</t>
+          <t>ministry_lookup_validation.py</t>
         </is>
       </c>
       <c r="K65" s="30" t="inlineStr">
@@ -6000,7 +6000,7 @@
     <row r="66">
       <c r="A66" s="29" t="inlineStr">
         <is>
-          <t>HR-54</t>
+          <t>HR-53</t>
         </is>
       </c>
       <c r="B66" s="30" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="C66" s="31" t="inlineStr">
         <is>
-          <t>Website logo file missing (/files/rchs-logo.png)</t>
+          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
         </is>
       </c>
       <c r="D66" s="30" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
@@ -6035,17 +6035,17 @@
       </c>
       <c r="H66" s="31" t="inlineStr">
         <is>
-          <t>Missing on the local copy; every page requests it.</t>
+          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
         </is>
       </c>
       <c r="I66" s="31" t="inlineStr">
         <is>
-          <t>Check the file exists on the live server.</t>
+          <t>Complete or delete the demo record before go-live.</t>
         </is>
       </c>
       <c r="J66" s="31" t="inlineStr">
         <is>
-          <t>Website Settings</t>
+          <t>Employee EMP-00001</t>
         </is>
       </c>
       <c r="K66" s="30" t="inlineStr">
@@ -6057,7 +6057,7 @@
     <row r="67">
       <c r="A67" s="29" t="inlineStr">
         <is>
-          <t>HR-55</t>
+          <t>HR-54</t>
         </is>
       </c>
       <c r="B67" s="30" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="C67" s="31" t="inlineStr">
         <is>
-          <t>Link the 216 existing Instructors to Employees</t>
+          <t>Website logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
       <c r="D67" s="30" t="inlineStr">
@@ -6082,27 +6082,27 @@
       </c>
       <c r="F67" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G67" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H67" s="31" t="inlineStr">
         <is>
-          <t>Tool ready (HR-35). 1 of 216 linked.</t>
+          <t>Missing on the local copy; every page requests it.</t>
         </is>
       </c>
       <c r="I67" s="31" t="inlineStr">
         <is>
-          <t>HR fills the Instructor data sheet; run the import with commit.</t>
+          <t>Check the file exists on the live server.</t>
         </is>
       </c>
       <c r="J67" s="31" t="inlineStr">
         <is>
-          <t>instructor_data_sheet.py</t>
+          <t>Website Settings</t>
         </is>
       </c>
       <c r="K67" s="30" t="inlineStr">
@@ -6114,17 +6114,17 @@
     <row r="68">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-55</t>
         </is>
       </c>
       <c r="B68" s="30" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C68" s="31" t="inlineStr">
         <is>
-          <t>Connect attendance devices</t>
+          <t>Link the 216 existing Instructors to Employees</t>
         </is>
       </c>
       <c r="D68" s="30" t="inlineStr">
@@ -6139,27 +6139,27 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G68" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H68" s="31" t="inlineStr">
         <is>
-          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
+          <t>Tool ready (HR-35). 1 of 216 linked.</t>
         </is>
       </c>
       <c r="I68" s="31" t="inlineStr">
         <is>
-          <t>Connect devices; map device user IDs to Employees.</t>
+          <t>HR fills the Instructor data sheet; run the import with commit.</t>
         </is>
       </c>
       <c r="J68" s="31" t="inlineStr">
         <is>
-          <t>bfac883</t>
+          <t>instructor_data_sheet.py</t>
         </is>
       </c>
       <c r="K68" s="30" t="inlineStr">
@@ -6171,7 +6171,7 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>HR-57</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="B69" s="30" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>Set the Academic Holiday List</t>
+          <t>Connect attendance devices</t>
         </is>
       </c>
       <c r="D69" s="30" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F69" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="G69" s="30" t="inlineStr">
@@ -6206,17 +6206,17 @@
       </c>
       <c r="H69" s="31" t="inlineStr">
         <is>
-          <t>Not set; the page warns about it.</t>
+          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
         </is>
       </c>
       <c r="I69" s="31" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
+          <t>Connect devices; map device user IDs to Employees.</t>
         </is>
       </c>
       <c r="J69" s="31" t="inlineStr">
         <is>
-          <t>academic_presence_setup.py</t>
+          <t>bfac883</t>
         </is>
       </c>
       <c r="K69" s="30" t="inlineStr">
@@ -6228,17 +6228,17 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>HR-58</t>
+          <t>HR-57</t>
         </is>
       </c>
       <c r="B70" s="30" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C70" s="31" t="inlineStr">
         <is>
-          <t>Deploy to the live server</t>
+          <t>Set the Academic Holiday List</t>
         </is>
       </c>
       <c r="D70" s="30" t="inlineStr">
@@ -6253,64 +6253,64 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H70" s="31" t="inlineStr">
         <is>
-          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy.</t>
+          <t>Not set; the page warns about it.</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr">
         <is>
-          <t>Merge, pull on the server, bench migrate, restart; smoke-test with the Test Cases workbook.</t>
+          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
         </is>
       </c>
       <c r="J70" s="31" t="inlineStr">
         <is>
-          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
+          <t>academic_presence_setup.py</t>
         </is>
       </c>
       <c r="K70" s="30" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="29" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>HR-58</t>
         </is>
       </c>
       <c r="B71" s="30" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>Research: Jameah system, Ministry documents, view contract</t>
+          <t>Deploy to the live server</t>
         </is>
       </c>
       <c r="D71" s="30" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E71" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F71" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G71" s="30" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="H71" s="31" t="inlineStr">
         <is>
-          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
+          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too.</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Merge, pull on the server, bench migrate, restart; smoke-test with the Test Cases workbook.</t>
         </is>
       </c>
       <c r="J71" s="31" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
         </is>
       </c>
       <c r="K71" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="29" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="B72" s="30" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
-          <t>Ministry views for Employees (5) and Students (10)</t>
+          <t>Research: Jameah system, Ministry documents, view contract</t>
         </is>
       </c>
       <c r="D72" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
@@ -6372,22 +6372,22 @@
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H72" s="31" t="inlineStr">
         <is>
-          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
+          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
         </is>
       </c>
       <c r="I72" s="31" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J72" s="31" t="inlineStr">
         <is>
-          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="K72" s="30" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="B73" s="30" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
-          <t>Code crosswalk (Jameah Code Map)</t>
+          <t>Ministry views for Employees (5) and Students (10)</t>
         </is>
       </c>
       <c r="D73" s="30" t="inlineStr">
@@ -6429,22 +6429,22 @@
       </c>
       <c r="G73" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H73" s="31" t="inlineStr">
         <is>
-          <t>299 college values mapped to official codes by meaning; wrong codes in Education masters (City 90, REL001...) no longer reach the Ministry.</t>
+          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr">
         <is>
-          <t>Review 3 values (JM-11).</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="J73" s="31" t="inlineStr">
         <is>
-          <t>jameah/code_map.py</t>
+          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
         </is>
       </c>
       <c r="K73" s="30" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
         <is>
-          <t>JM-04</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="B74" s="30" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C74" s="31" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>Code crosswalk (Jameah Code Map)</t>
         </is>
       </c>
       <c r="D74" s="30" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="H74" s="31" t="inlineStr">
         <is>
-          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
+          <t>299 college values mapped to official codes by meaning; wrong codes in Education masters (City 90, REL001...) no longer reach the Ministry.</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr">
         <is>
-          <t>Fill 6 values (JM-10).</t>
+          <t>Review 3 values (JM-11).</t>
         </is>
       </c>
       <c r="J74" s="31" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>jameah/code_map.py</t>
         </is>
       </c>
       <c r="K74" s="30" t="inlineStr">
@@ -6513,7 +6513,7 @@
     <row r="75">
       <c r="A75" s="29" t="inlineStr">
         <is>
-          <t>JM-05</t>
+          <t>JM-04</t>
         </is>
       </c>
       <c r="B75" s="30" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="D75" s="30" t="inlineStr">
@@ -6548,17 +6548,17 @@
       </c>
       <c r="H75" s="31" t="inlineStr">
         <is>
-          <t>Follows the transcript; view answers in ~3 s instead of 30 s.</t>
+          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
         </is>
       </c>
       <c r="I75" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Fill 6 values (JM-10).</t>
         </is>
       </c>
       <c r="J75" s="31" t="inlineStr">
         <is>
-          <t>jameah/summary.py</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="K75" s="30" t="inlineStr">
@@ -6570,7 +6570,7 @@
     <row r="76">
       <c r="A76" s="29" t="inlineStr">
         <is>
-          <t>JM-06</t>
+          <t>JM-05</t>
         </is>
       </c>
       <c r="B76" s="30" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C76" s="31" t="inlineStr">
         <is>
-          <t>Independent verification of every view</t>
+          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
         </is>
       </c>
       <c r="D76" s="30" t="inlineStr">
@@ -6600,34 +6600,34 @@
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H76" s="31" t="inlineStr">
         <is>
-          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the Education update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
+          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
         </is>
       </c>
       <c r="I76" s="31" t="inlineStr">
         <is>
-          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J76" s="31" t="inlineStr">
         <is>
-          <t>jameah/verify.py; test_jameah.py</t>
+          <t>jameah/summary.py</t>
         </is>
       </c>
       <c r="K76" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="29" t="inlineStr">
         <is>
-          <t>JM-18</t>
+          <t>JM-06</t>
         </is>
       </c>
       <c r="B77" s="30" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>Ministry GPA and credit hours = the college's official figures</t>
+          <t>Independent verification of every view</t>
         </is>
       </c>
       <c r="D77" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E77" s="30" t="inlineStr">
@@ -6662,17 +6662,17 @@
       </c>
       <c r="H77" s="31" t="inlineStr">
         <is>
-          <t>Found 21 Oct: Education's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads Education's official functions (read only, no change to Education); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
+          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the Education update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
         </is>
       </c>
       <c r="I77" s="31" t="inlineStr">
         <is>
-          <t>Deploy together with the Education master update (HR-58); re-run verify on the live server.</t>
+          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="J77" s="31" t="inlineStr">
         <is>
-          <t>jameah/summary.py; jameah/verify.py</t>
+          <t>jameah/verify.py; test_jameah.py</t>
         </is>
       </c>
       <c r="K77" s="30" t="inlineStr">
@@ -6684,7 +6684,7 @@
     <row r="78">
       <c r="A78" s="29" t="inlineStr">
         <is>
-          <t>JM-07</t>
+          <t>JM-18</t>
         </is>
       </c>
       <c r="B78" s="30" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="C78" s="31" t="inlineStr">
         <is>
-          <t>Jameah Data Check page and Employee preview</t>
+          <t>Ministry GPA and credit hours = the college's official figures</t>
         </is>
       </c>
       <c r="D78" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -6714,22 +6714,22 @@
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H78" s="31" t="inlineStr">
         <is>
-          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
+          <t>Found 21 Oct: Education's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads Education's official functions (read only, no change to Education); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Deploy together with the Education master update (HR-58); re-run verify on the live server.</t>
         </is>
       </c>
       <c r="J78" s="31" t="inlineStr">
         <is>
-          <t>page/jameah_data_check</t>
+          <t>jameah/summary.py; jameah/verify.py</t>
         </is>
       </c>
       <c r="K78" s="30" t="inlineStr">
@@ -6741,7 +6741,7 @@
     <row r="79">
       <c r="A79" s="29" t="inlineStr">
         <is>
-          <t>JM-08</t>
+          <t>JM-19</t>
         </is>
       </c>
       <c r="B79" s="30" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>Read-only database account for the Ministry agent</t>
+          <t>Hourly academic summary refresh slows the site while it runs</t>
         </is>
       </c>
       <c r="D79" s="30" t="inlineStr">
@@ -6761,44 +6761,44 @@
       </c>
       <c r="E79" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F79" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G79" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H79" s="31" t="inlineStr">
         <is>
-          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
+          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr">
         <is>
-          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
+          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
         </is>
       </c>
       <c r="J79" s="31" t="inlineStr">
         <is>
-          <t>jameah/README.md</t>
+          <t>jameah/summary.py; hooks.py hourly_long</t>
         </is>
       </c>
       <c r="K79" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="29" t="inlineStr">
         <is>
-          <t>JM-09</t>
+          <t>JM-07</t>
         </is>
       </c>
       <c r="B80" s="30" t="inlineStr">
@@ -6808,42 +6808,42 @@
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
-          <t>Confirm view and column names with the Ministry</t>
+          <t>Jameah Data Check page and Employee preview</t>
         </is>
       </c>
       <c r="D80" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H80" s="31" t="inlineStr">
         <is>
-          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
+          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr">
         <is>
-          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J80" s="31" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>page/jameah_data_check</t>
         </is>
       </c>
       <c r="K80" s="30" t="inlineStr">
@@ -6855,7 +6855,7 @@
     <row r="81">
       <c r="A81" s="29" t="inlineStr">
         <is>
-          <t>JM-10</t>
+          <t>JM-08</t>
         </is>
       </c>
       <c r="B81" s="30" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
-          <t>Fill Jameah Settings (6 values)</t>
+          <t>Read-only database account for the Ministry agent</t>
         </is>
       </c>
       <c r="D81" s="30" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E81" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G81" s="30" t="inlineStr">
@@ -6890,17 +6890,17 @@
       </c>
       <c r="H81" s="31" t="inlineStr">
         <is>
-          <t>Empty values are sent as empty.</t>
+          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
         </is>
       </c>
       <c r="I81" s="31" t="inlineStr">
         <is>
-          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
+          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
         </is>
       </c>
       <c r="J81" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-settings</t>
+          <t>jameah/README.md</t>
         </is>
       </c>
       <c r="K81" s="30" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>JM-11</t>
+          <t>JM-09</t>
         </is>
       </c>
       <c r="B82" s="30" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="C82" s="31" t="inlineStr">
         <is>
-          <t>Map 3 college values to Ministry codes</t>
+          <t>Confirm view and column names with the Ministry</t>
         </is>
       </c>
       <c r="D82" s="30" t="inlineStr">
@@ -6937,27 +6937,27 @@
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H82" s="31" t="inlineStr">
         <is>
-          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
+          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
         </is>
       </c>
       <c r="I82" s="31" t="inlineStr">
         <is>
-          <t>Pick the code in Jameah Code Map and set Verified.</t>
+          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
         </is>
       </c>
       <c r="J82" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-code-map</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="K82" s="30" t="inlineStr">
@@ -6969,7 +6969,7 @@
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>JM-12</t>
+          <t>JM-10</t>
         </is>
       </c>
       <c r="B83" s="30" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C83" s="31" t="inlineStr">
         <is>
-          <t>Ministry fields with no source in the college system</t>
+          <t>Fill Jameah Settings (6 values)</t>
         </is>
       </c>
       <c r="D83" s="30" t="inlineStr">
@@ -6994,27 +6994,27 @@
       </c>
       <c r="F83" s="30" t="inlineStr">
         <is>
-          <t>Academic Affairs + Education team</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G83" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H83" s="31" t="inlineStr">
         <is>
-          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
+          <t>Empty values are sent as empty.</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr">
         <is>
-          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
+          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
         </is>
       </c>
       <c r="J83" s="31" t="inlineStr">
         <is>
-          <t>Jameah report; VIEWS.md</t>
+          <t>/app/jameah-settings</t>
         </is>
       </c>
       <c r="K83" s="30" t="inlineStr">
@@ -7026,7 +7026,7 @@
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
-          <t>JM-13</t>
+          <t>JM-11</t>
         </is>
       </c>
       <c r="B84" s="30" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="C84" s="31" t="inlineStr">
         <is>
-          <t>Correct source data found by the checks</t>
+          <t>Map 3 college values to Ministry codes</t>
         </is>
       </c>
       <c r="D84" s="30" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Registrar / Education team</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G84" s="30" t="inlineStr">
@@ -7061,17 +7061,17 @@
       </c>
       <c r="H84" s="31" t="inlineStr">
         <is>
-          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
+          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
         </is>
       </c>
       <c r="I84" s="31" t="inlineStr">
         <is>
-          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
+          <t>Pick the code in Jameah Code Map and set Verified.</t>
         </is>
       </c>
       <c r="J84" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-data-check</t>
+          <t>/app/jameah-code-map</t>
         </is>
       </c>
       <c r="K84" s="30" t="inlineStr">
@@ -7083,7 +7083,7 @@
     <row r="85">
       <c r="A85" s="29" t="inlineStr">
         <is>
-          <t>JM-14</t>
+          <t>JM-12</t>
         </is>
       </c>
       <c r="B85" s="30" t="inlineStr">
@@ -7093,42 +7093,42 @@
       </c>
       <c r="C85" s="31" t="inlineStr">
         <is>
-          <t>Faculty views (8 sections)</t>
+          <t>Ministry fields with no source in the college system</t>
         </is>
       </c>
       <c r="D85" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E85" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F85" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Academic Affairs + Education team</t>
         </is>
       </c>
       <c r="G85" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H85" s="31" t="inlineStr">
         <is>
-          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
+          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
         </is>
       </c>
       <c r="I85" s="31" t="inlineStr">
         <is>
-          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
+          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
         </is>
       </c>
       <c r="J85" s="31" t="inlineStr">
         <is>
-          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
+          <t>Jameah report; VIEWS.md</t>
         </is>
       </c>
       <c r="K85" s="30" t="inlineStr">
@@ -7140,7 +7140,7 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>JM-15</t>
+          <t>JM-13</t>
         </is>
       </c>
       <c r="B86" s="30" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="C86" s="31" t="inlineStr">
         <is>
-          <t>Institute views (20 sections)</t>
+          <t>Correct source data found by the checks</t>
         </is>
       </c>
       <c r="D86" s="30" t="inlineStr">
@@ -7160,32 +7160,32 @@
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar / Education team</t>
         </is>
       </c>
       <c r="G86" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H86" s="31" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
         </is>
       </c>
       <c r="I86" s="31" t="inlineStr">
         <is>
-          <t>Build after Faculty; needs institute data from HR.</t>
+          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
         </is>
       </c>
       <c r="J86" s="31" t="inlineStr">
         <is>
-          <t>MINISTRY_FIELD_MAPPING.html</t>
+          <t>/app/jameah-data-check</t>
         </is>
       </c>
       <c r="K86" s="30" t="inlineStr">
@@ -7197,7 +7197,7 @@
     <row r="87">
       <c r="A87" s="29" t="inlineStr">
         <is>
-          <t>JM-16</t>
+          <t>JM-14</t>
         </is>
       </c>
       <c r="B87" s="30" t="inlineStr">
@@ -7207,42 +7207,42 @@
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>Old Education viewJameah* views (42)</t>
+          <t>Faculty views (8 sections)</t>
         </is>
       </c>
       <c r="D87" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E87" s="30" t="inlineStr">
         <is>
-          <t>Pending – other team</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F87" s="30" t="inlineStr">
         <is>
-          <t>Education team</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G87" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H87" s="31" t="inlineStr">
         <is>
-          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
         </is>
       </c>
       <c r="I87" s="31" t="inlineStr">
         <is>
-          <t>Education team to retire them once ours are confirmed.</t>
+          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
         </is>
       </c>
       <c r="J87" s="31" t="inlineStr">
         <is>
-          <t>education/jameah_system</t>
+          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
         </is>
       </c>
       <c r="K87" s="30" t="inlineStr">
@@ -7254,63 +7254,177 @@
     <row r="88">
       <c r="A88" s="29" t="inlineStr">
         <is>
+          <t>JM-15</t>
+        </is>
+      </c>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C88" s="31" t="inlineStr">
+        <is>
+          <t>Institute views (20 sections)</t>
+        </is>
+      </c>
+      <c r="D88" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="30" t="inlineStr">
+        <is>
+          <t>Pending – development</t>
+        </is>
+      </c>
+      <c r="F88" s="30" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G88" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H88" s="31" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="I88" s="31" t="inlineStr">
+        <is>
+          <t>Build after Faculty; needs institute data from HR.</t>
+        </is>
+      </c>
+      <c r="J88" s="31" t="inlineStr">
+        <is>
+          <t>MINISTRY_FIELD_MAPPING.html</t>
+        </is>
+      </c>
+      <c r="K88" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="29" t="inlineStr">
+        <is>
+          <t>JM-16</t>
+        </is>
+      </c>
+      <c r="B89" s="30" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C89" s="31" t="inlineStr">
+        <is>
+          <t>Old Education viewJameah* views (42)</t>
+        </is>
+      </c>
+      <c r="D89" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="30" t="inlineStr">
+        <is>
+          <t>Pending – other team</t>
+        </is>
+      </c>
+      <c r="F89" s="30" t="inlineStr">
+        <is>
+          <t>Education team</t>
+        </is>
+      </c>
+      <c r="G89" s="30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H89" s="31" t="inlineStr">
+        <is>
+          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+        </is>
+      </c>
+      <c r="I89" s="31" t="inlineStr">
+        <is>
+          <t>Education team to retire them once ours are confirmed.</t>
+        </is>
+      </c>
+      <c r="J89" s="31" t="inlineStr">
+        <is>
+          <t>education/jameah_system</t>
+        </is>
+      </c>
+      <c r="K89" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="29" t="inlineStr">
+        <is>
           <t>JM-17</t>
         </is>
       </c>
-      <c r="B88" s="30" t="inlineStr">
+      <c r="B90" s="30" t="inlineStr">
         <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="C88" s="31" t="inlineStr">
+      <c r="C90" s="31" t="inlineStr">
         <is>
           <t>Transcript GPA rounding at exact ties</t>
         </is>
       </c>
-      <c r="D88" s="30" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E88" s="30" t="inlineStr">
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E90" s="30" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F88" s="30" t="inlineStr">
+      <c r="F90" s="30" t="inlineStr">
         <is>
           <t>Education team</t>
         </is>
       </c>
-      <c r="G88" s="30" t="inlineStr">
+      <c r="G90" s="30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H88" s="31" t="inlineStr">
+      <c r="H90" s="31" t="inlineStr">
         <is>
           <t>Resolved by Education's new GPA module (exact half-up rounding); the views now use it (JM-18).</t>
         </is>
       </c>
-      <c r="I88" s="31" t="inlineStr">
+      <c r="I90" s="31" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J88" s="31" t="inlineStr">
+      <c r="J90" s="31" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="K88" s="30" t="inlineStr">
+      <c r="K90" s="30" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K88"/>
-  <conditionalFormatting sqref="A2:K288">
+  <autoFilter ref="A1:K90"/>
+  <conditionalFormatting sqref="A2:K290">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E2="Done"</formula>
     </cfRule>
@@ -7337,10 +7451,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E288" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
+    <dataValidation sqref="E2:E290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
       <formula1>"Done,Done – client UAT pending,In progress,Pending – decision needed,Pending – data / setup,Pending – development,Pending – other team,Planned"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G288" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7354,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9348,37 +9462,37 @@
     <row r="39">
       <c r="A39" s="30" t="inlineStr">
         <is>
-          <t>B-28</t>
+          <t>B-42</t>
         </is>
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D39" s="31" t="inlineStr">
         <is>
-          <t>Employees clicking the 'Medical HRMS' breadcrumb got 'Not permitted - No permission for Page'</t>
+          <t>After merging the job application update, the academic 'Appreciation' list would have been empty, so academic applicants could not send the form</t>
         </is>
       </c>
       <c r="E39" s="31" t="inlineStr">
         <is>
-          <t>Frappe chooses the breadcrumb workspace without a permission check</t>
+          <t>The updated page sends only the lookup lists it names; the Ministry grade list (Student Evaluation Coding, fix B-22) was not one of them</t>
         </is>
       </c>
       <c r="F39" s="31" t="inlineStr">
         <is>
-          <t>Keep only workspaces the user can open</t>
+          <t>List added</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
         <is>
-          <t>HR-59</t>
+          <t>HR-70</t>
         </is>
       </c>
       <c r="H39" s="30" t="inlineStr">
@@ -9388,174 +9502,330 @@
       </c>
       <c r="I39" s="31" t="inlineStr">
         <is>
-          <t>E2E NAV-01/02</t>
+          <t>E2E REC-05</t>
         </is>
       </c>
       <c r="J39" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="30" t="inlineStr">
         <is>
-          <t>B-25</t>
+          <t>B-44</t>
         </is>
       </c>
       <c r="B40" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D40" s="31" t="inlineStr">
         <is>
-          <t>System e-mails fail: password cannot be decrypted</t>
+          <t>After the merge, a work telephone extension such as 321 was refused as 'not a valid phone number'</t>
         </is>
       </c>
       <c r="E40" s="31" t="inlineStr">
         <is>
-          <t>Email Account 'Notifications' password encrypted with another key</t>
+          <t>Our 20 Oct change made the extension a phone-type input; the updated form checks every phone-type input as a full number (7-15 digits)</t>
         </is>
       </c>
       <c r="F40" s="31" t="inlineStr">
         <is>
-          <t>Re-enter the password on the server</t>
+          <t>Extension is a numbers-only field (up to 6 digits) with its own check</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-70</t>
         </is>
       </c>
       <c r="H40" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I40" s="31" t="inlineStr">
         <is>
-          <t>Error Log</t>
+          <t>E2E REC-03/04/05</t>
         </is>
       </c>
       <c r="J40" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
-          <t>B-26</t>
+          <t>B-43</t>
         </is>
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>Instructor (Education)</t>
+          <t>Deployment / Jameah</t>
         </is>
       </c>
       <c r="D41" s="31" t="inlineStr">
         <is>
-          <t>Linking an Employee in the Instructor form fails</t>
+          <t>A migrate stopped with 'Lock wait timeout exceeded' at its last step</t>
         </is>
       </c>
       <c r="E41" s="31" t="inlineStr">
         <is>
-          <t>fetch_from copies Ministry codes into Education lists</t>
+          <t>It rebuilt the Jameah academic summary while the hourly job was rebuilding the same table; it waited for the table lock until the database gave up</t>
         </is>
       </c>
       <c r="F41" s="31" t="inlineStr">
         <is>
-          <t>Education team to change the fetch</t>
+          <t>One rebuild at a time: a second one is skipped at once (database lock)</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>JM-05</t>
         </is>
       </c>
       <c r="H41" s="30" t="inlineStr">
         <is>
-          <t>Open – other team</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I41" s="31" t="inlineStr">
         <is>
-          <t>Reproduced 21 Oct</t>
+          <t>Unit test TestJameahSummaryRefresh; migrate re-run 22 Oct</t>
         </is>
       </c>
       <c r="J41" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="30" t="inlineStr">
         <is>
+          <t>B-28</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>Employees clicking the 'Medical HRMS' breadcrumb got 'Not permitted - No permission for Page'</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>Frappe chooses the breadcrumb workspace without a permission check</t>
+        </is>
+      </c>
+      <c r="F42" s="31" t="inlineStr">
+        <is>
+          <t>Keep only workspaces the user can open</t>
+        </is>
+      </c>
+      <c r="G42" s="30" t="inlineStr">
+        <is>
+          <t>HR-59</t>
+        </is>
+      </c>
+      <c r="H42" s="30" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I42" s="31" t="inlineStr">
+        <is>
+          <t>E2E NAV-01/02</t>
+        </is>
+      </c>
+      <c r="J42" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t>B-25</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="inlineStr">
+        <is>
+          <t>System e-mails fail: password cannot be decrypted</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>Email Account 'Notifications' password encrypted with another key</t>
+        </is>
+      </c>
+      <c r="F43" s="31" t="inlineStr">
+        <is>
+          <t>Re-enter the password on the server</t>
+        </is>
+      </c>
+      <c r="G43" s="30" t="inlineStr">
+        <is>
+          <t>HR-47</t>
+        </is>
+      </c>
+      <c r="H43" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I43" s="31" t="inlineStr">
+        <is>
+          <t>Error Log</t>
+        </is>
+      </c>
+      <c r="J43" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>B-26</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C44" s="30" t="inlineStr">
+        <is>
+          <t>Instructor (Education)</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="inlineStr">
+        <is>
+          <t>Linking an Employee in the Instructor form fails</t>
+        </is>
+      </c>
+      <c r="E44" s="31" t="inlineStr">
+        <is>
+          <t>fetch_from copies Ministry codes into Education lists</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="inlineStr">
+        <is>
+          <t>Education team to change the fetch</t>
+        </is>
+      </c>
+      <c r="G44" s="30" t="inlineStr">
+        <is>
+          <t>HR-48</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="inlineStr">
+        <is>
+          <t>Open – other team</t>
+        </is>
+      </c>
+      <c r="I44" s="31" t="inlineStr">
+        <is>
+          <t>Reproduced 21 Oct</t>
+        </is>
+      </c>
+      <c r="J44" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
           <t>B-27</t>
         </is>
       </c>
-      <c r="B42" s="30" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C42" s="30" t="inlineStr">
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="D42" s="31" t="inlineStr">
+      <c r="D45" s="31" t="inlineStr">
         <is>
           <t>Logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
-      <c r="E42" s="31" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>File not on this copy</t>
         </is>
       </c>
-      <c r="F42" s="31" t="inlineStr">
+      <c r="F45" s="31" t="inlineStr">
         <is>
           <t>Check on the live server</t>
         </is>
       </c>
-      <c r="G42" s="30" t="inlineStr">
+      <c r="G45" s="30" t="inlineStr">
         <is>
           <t>HR-54</t>
         </is>
       </c>
-      <c r="H42" s="30" t="inlineStr">
+      <c r="H45" s="30" t="inlineStr">
         <is>
           <t>Open – check server</t>
         </is>
       </c>
-      <c r="I42" s="31" t="inlineStr">
+      <c r="I45" s="31" t="inlineStr">
         <is>
           <t>Error sweep</t>
         </is>
       </c>
-      <c r="J42" s="30" t="inlineStr">
+      <c r="J45" s="30" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J42"/>
-  <conditionalFormatting sqref="A2:J142">
+  <autoFilter ref="A1:J45"/>
+  <conditionalFormatting sqref="A2:J145">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H2="Fixed"</formula>
     </cfRule>
@@ -9570,7 +9840,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Fixed,Open,Open – other team,Open – check server"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10127,7 +10397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10177,12 +10447,12 @@
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D2" s="31" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E2" s="30" t="inlineStr">
@@ -10199,17 +10469,17 @@
       </c>
       <c r="B3" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D3" s="31" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E3" s="30" t="inlineStr">
@@ -10221,22 +10491,22 @@
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D4" s="31" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
@@ -10253,17 +10523,17 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D5" s="31" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E5" s="30" t="inlineStr">
@@ -10280,17 +10550,17 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D6" s="31" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
@@ -10302,7 +10572,7 @@
     <row r="7">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B7" s="30" t="inlineStr">
@@ -10312,12 +10582,12 @@
       </c>
       <c r="C7" s="31" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D7" s="31" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E7" s="30" t="inlineStr">
@@ -10329,7 +10599,7 @@
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="30" t="inlineStr">
@@ -10339,12 +10609,12 @@
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
@@ -10356,32 +10626,59 @@
     <row r="9">
       <c r="A9" s="30" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -15,10 +15,10 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$K$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$K$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -674,7 +674,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Al-Riyada College for Health Sciences · last updated 22 Oct 2026</t>
+          <t>Al-Riyada College for Health Sciences · last updated 23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -954,7 +954,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Counts are formulas over the Tasks and Bugs sheets. As of 22 Oct 2026.</t>
+          <t>Counts are formulas over the Tasks and Bugs sheets. As of 23 Oct 2026.</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B5" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$290,A5)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$293,A5)</f>
         <v/>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B6" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$290,A6)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$293,A6)</f>
         <v/>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B7" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$290,A7)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$293,A7)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B8" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$290,A8)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$293,A8)</f>
         <v/>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="B9" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$290,A9)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$293,A9)</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B10" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$290,A10)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$293,A10)</f>
         <v/>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="B11" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$290,A11)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$293,A11)</f>
         <v/>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="B12" s="19">
-        <f>COUNTIF(Tasks!$E$2:$E$290,A12)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$293,A12)</f>
         <v/>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B16" s="19">
-        <f>COUNTIFS(Tasks!$A$2:$A$290,"HR-*",Tasks!$E$2:$E$290,"Done")+COUNTIFS(Tasks!$A$2:$A$290,"HR-*",Tasks!$E$2:$E$290,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$293,"HR-*",Tasks!$E$2:$E$293,"Done")+COUNTIFS(Tasks!$A$2:$A$293,"HR-*",Tasks!$E$2:$E$293,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C16" s="19">
@@ -1107,7 +1107,7 @@
         <v/>
       </c>
       <c r="D16" s="19">
-        <f>COUNTIF(Tasks!$A$2:$A$290,"HR-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$293,"HR-*")</f>
         <v/>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B17" s="19">
-        <f>COUNTIFS(Tasks!$A$2:$A$290,"JM-*",Tasks!$E$2:$E$290,"Done")+COUNTIFS(Tasks!$A$2:$A$290,"JM-*",Tasks!$E$2:$E$290,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$293,"JM-*",Tasks!$E$2:$E$293,"Done")+COUNTIFS(Tasks!$A$2:$A$293,"JM-*",Tasks!$E$2:$E$293,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C17" s="19">
@@ -1126,7 +1126,7 @@
         <v/>
       </c>
       <c r="D17" s="19">
-        <f>COUNTIF(Tasks!$A$2:$A$290,"JM-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$293,"JM-*")</f>
         <v/>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B20" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$290,"Earlier (May – 5 Oct 2026)")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$293,"Earlier (May – 5 Oct 2026)")</f>
         <v/>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="B21" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$290,"19 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$293,"19 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B22" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$290,"20 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$293,"20 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="B23" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$290,"21 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$293,"21 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1194,1074 +1194,1128 @@
         </is>
       </c>
       <c r="B24" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$290,"22 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$293,"22 Oct 2026")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B25" s="19">
+        <f>COUNTIF(Tasks!$D$2:$D$293,"23 Oct 2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
           <t>— (not done yet)</t>
         </is>
       </c>
-      <c r="B25" s="19">
-        <f>COUNTIF(Tasks!$D$2:$D$290,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="B26" s="19">
+        <f>COUNTIF(Tasks!$D$2:$D$293,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Done – client UAT pending</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Pending – decision needed</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Pending – data / setup</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>Pending – development</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>Pending – other team</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="B28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,B$27)</f>
-        <v/>
-      </c>
-      <c r="C28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,C$27)</f>
-        <v/>
-      </c>
-      <c r="D28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,D$27)</f>
-        <v/>
-      </c>
-      <c r="E28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,E$27)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,F$27)</f>
-        <v/>
-      </c>
-      <c r="G28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,G$27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,H$27)</f>
-        <v/>
-      </c>
-      <c r="I28" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A28,Tasks!$E$2:$E$290,I$27)</f>
-        <v/>
-      </c>
-      <c r="J28" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A28)</f>
-        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>Master data</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="B29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I29" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A29,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J29" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A29)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Master data</t>
         </is>
       </c>
       <c r="B30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I30" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A30,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J30" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A30)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="B31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I31" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A31,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J31" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A31)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>HR dashboard</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="B32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I32" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A32,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J32" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A32)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>Self-service</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="B33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I33" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A33,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J33" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A33)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Self-service</t>
         </is>
       </c>
       <c r="B34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I34" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A34,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J34" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A34)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I35" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A35,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J35" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A35)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="B36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I36" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A36,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J36" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A36)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="B37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I37" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A37,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J37" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A37)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="B38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I38" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A38,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J38" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A38)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="B39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I39" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A39,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J39" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A39)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="B40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I40" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A40,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J40" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A40)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="B41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I41" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A41,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J41" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A41)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="B42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I42" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A42,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J42" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A42)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>Employee master</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="B43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I43" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A43,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J43" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A43)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>Employee master</t>
         </is>
       </c>
       <c r="B44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I44" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A44,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J44" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A44)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="B45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I45" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A45,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J45" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A45)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I46" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A46,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J46" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A46)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="B47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I47" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A47,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J47" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A47)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,B$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,B$28)</f>
         <v/>
       </c>
       <c r="C48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,C$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,C$28)</f>
         <v/>
       </c>
       <c r="D48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,D$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,D$28)</f>
         <v/>
       </c>
       <c r="E48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,E$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,E$28)</f>
         <v/>
       </c>
       <c r="F48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,F$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,F$28)</f>
         <v/>
       </c>
       <c r="G48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,G$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,G$28)</f>
         <v/>
       </c>
       <c r="H48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,H$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,H$28)</f>
         <v/>
       </c>
       <c r="I48" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A48,Tasks!$E$2:$E$290,I$27)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,I$28)</f>
         <v/>
       </c>
       <c r="J48" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A48)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B49" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,B$28)</f>
+        <v/>
+      </c>
+      <c r="C49" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,C$28)</f>
+        <v/>
+      </c>
+      <c r="D49" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,D$28)</f>
+        <v/>
+      </c>
+      <c r="E49" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,E$28)</f>
+        <v/>
+      </c>
+      <c r="F49" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,F$28)</f>
+        <v/>
+      </c>
+      <c r="G49" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,G$28)</f>
+        <v/>
+      </c>
+      <c r="H49" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,H$28)</f>
+        <v/>
+      </c>
+      <c r="I49" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,I$28)</f>
+        <v/>
+      </c>
+      <c r="J49" s="19">
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B50" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,B$28)</f>
+        <v/>
+      </c>
+      <c r="C50" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,C$28)</f>
+        <v/>
+      </c>
+      <c r="D50" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,D$28)</f>
+        <v/>
+      </c>
+      <c r="E50" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,E$28)</f>
+        <v/>
+      </c>
+      <c r="F50" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,F$28)</f>
+        <v/>
+      </c>
+      <c r="G50" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,G$28)</f>
+        <v/>
+      </c>
+      <c r="H50" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,H$28)</f>
+        <v/>
+      </c>
+      <c r="I50" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,I$28)</f>
+        <v/>
+      </c>
+      <c r="J50" s="19">
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="B49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,B$27)</f>
-        <v/>
-      </c>
-      <c r="C49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,C$27)</f>
-        <v/>
-      </c>
-      <c r="D49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,D$27)</f>
-        <v/>
-      </c>
-      <c r="E49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,E$27)</f>
-        <v/>
-      </c>
-      <c r="F49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,F$27)</f>
-        <v/>
-      </c>
-      <c r="G49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,G$27)</f>
-        <v/>
-      </c>
-      <c r="H49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,H$27)</f>
-        <v/>
-      </c>
-      <c r="I49" s="19">
-        <f>COUNTIFS(Tasks!$B$2:$B$290,$A49,Tasks!$E$2:$E$290,I$27)</f>
-        <v/>
-      </c>
-      <c r="J49" s="19">
-        <f>COUNTIF(Tasks!$B$2:$B$290,$A49)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="B51" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,B$28)</f>
+        <v/>
+      </c>
+      <c r="C51" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,C$28)</f>
+        <v/>
+      </c>
+      <c r="D51" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,D$28)</f>
+        <v/>
+      </c>
+      <c r="E51" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,E$28)</f>
+        <v/>
+      </c>
+      <c r="F51" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,F$28)</f>
+        <v/>
+      </c>
+      <c r="G51" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,G$28)</f>
+        <v/>
+      </c>
+      <c r="H51" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,H$28)</f>
+        <v/>
+      </c>
+      <c r="I51" s="19">
+        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,I$28)</f>
+        <v/>
+      </c>
+      <c r="J51" s="19">
+        <f>COUNTIF(Tasks!$B$2:$B$293,$A51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>Bugs</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="B52" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$145,A52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="28" t="inlineStr">
+      <c r="B54" s="19">
+        <f>COUNTIF(Bugs!$H$2:$H$152,A54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="B53" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$145,A53)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="25" t="inlineStr">
+      <c r="B55" s="19">
+        <f>COUNTIF(Bugs!$H$2:$H$152,A55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>Open – other team</t>
         </is>
       </c>
-      <c r="B54" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$145,A54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="23" t="inlineStr">
+      <c r="B56" s="19">
+        <f>COUNTIF(Bugs!$H$2:$H$152,A56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>Open – check server</t>
         </is>
       </c>
-      <c r="B55" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$145,A55)</f>
+      <c r="B57" s="19">
+        <f>COUNTIF(Bugs!$H$2:$H$152,A57)</f>
         <v/>
       </c>
     </row>
@@ -2276,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3698,12 +3752,12 @@
       </c>
       <c r="H25" s="31" t="inlineStr">
         <is>
-          <t>Found 22 Oct by the new setup check: leave period not active, no holiday list, 3 of 4 employees without a leave approver, 4 of 4 without annual leave. Until this is done its employees have no leave to apply for (only the demo company 'Medical College' is set up).</t>
+          <t>Found 22 Oct by the new setup check on the development copy: no active leave period and no holiday list for Al Riyada College. (Correction 23 Oct: the '3 of 4 employees without a leave approver / annual leave' counted QA test hires; this copy has no real Al Riyada College staff, so the employee checks must be read on the live server.) Until the setup is done its employees have no leave to apply for.</t>
         </is>
       </c>
       <c r="I25" s="31" t="inlineStr">
         <is>
-          <t>HR Portal &gt; Leave &gt; Yearly setup, steps 1-6, until the Leave setup check is green (Checklist CL-28 - CL-32).</t>
+          <t>On the live server: HR Portal &gt; Leave &gt; Yearly setup, steps 1-6, until the Leave setup check is green (Checklist CL-28 - CL-32).</t>
         </is>
       </c>
       <c r="J25" s="31" t="inlineStr">
@@ -3713,7 +3767,7 @@
       </c>
       <c r="K25" s="30" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -5487,22 +5541,22 @@
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-71</t>
         </is>
       </c>
       <c r="B57" s="30" t="inlineStr">
         <is>
-          <t>HR dashboard</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college design</t>
+          <t>Every branch merged into develop (the team's main branch)</t>
         </is>
       </c>
       <c r="D57" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="E57" s="30" t="inlineStr">
@@ -5522,44 +5576,44 @@
       </c>
       <c r="H57" s="31" t="inlineStr">
         <is>
-          <t>Same look as the Education team's new portals (Instructor Portal): left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so Education's changes cannot break these pages.</t>
+          <t>In this order: our work (feature/uat-2026-10-22, which already held fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views and the portal design), then feature/hr-portal-design, then employee-applicant, then ministry-lookup last (Fathir's 22 Oct update was already in). Conflicts: feature/hr-portal-design's own 22 Oct merge had dropped the Ministry identity check from the application form and kept an old Create Employee signature; develop's tested versions kept. employee-applicant (Dinesh, May-Jul prototype of recruitment, replaced by his September rebuild) recorded as merged without taking its files (decision of the HR lead, 23 Oct): its 17 old patches, second /job-application controller and old Return from Leave doctype would have broken recruitment, leave returns and migrate. The merged code is identical to the code tested on 22 Oct. Re-tested: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="I57" s="31" t="inlineStr">
         <is>
-          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
+          <t>Delete the merged branches on GitHub after UAT (Checklist CL-34). New work: a branch from develop and a pull request (README).</t>
         </is>
       </c>
       <c r="J57" s="31" t="inlineStr">
         <is>
-          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
+          <t>develop; README.md</t>
         </is>
       </c>
       <c r="K57" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
-          <t>HR-62</t>
+          <t>HR-72</t>
         </is>
       </c>
       <c r="B58" s="30" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>HR User could not open the Holiday List ('Not permitted')</t>
+          <t>Full check of every file and page of the app</t>
         </is>
       </c>
       <c r="D58" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
@@ -5574,116 +5628,116 @@
       </c>
       <c r="G58" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H58" s="31" t="inlineStr">
         <is>
-          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
+          <t>Files: 177 Python files compile, no undefined names (pyflakes); 26 JS files and the job form's 3 inline scripts parse; 26 JSON files load; 571 Arabic translations keep their placeholders. Site: 109 hooks / scheduler jobs / overrides / assets / patches resolve; 29 Medical HRMS doctypes, 73 custom link fields, the newest saved records (validate), the report, 4 pages and 2 workspaces. Server: all 29 methods called as visitor, employee and HR User (87 calls, none open to the wrong role, no server error). Unit tests: 19 files, 37 tests. Browser: the full suite, with the error sweep now opening every Medical HRMS doctype (list, new form, newest record), the report and both workspaces for HR, and employees' own request lists. The checks are kept as tests/checks/files.py, site.py and api_methods.py. Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="I58" s="31" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>Run tests/checks and the browser suite before every release (Checklist CL-36).</t>
         </is>
       </c>
       <c r="J58" s="31" t="inlineStr">
         <is>
-          <t>hr_core_permissions.py</t>
+          <t>tests/checks; tests/e2e</t>
         </is>
       </c>
       <c r="K58" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-73</t>
         </is>
       </c>
       <c r="B59" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>Full end-to-end test with error sweep (round 3)</t>
+          <t>Review the 39 one-off setup scripts that nothing calls</t>
         </is>
       </c>
       <c r="D59" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E59" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F59" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>To assign</t>
         </is>
       </c>
       <c r="G59" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H59" s="31" t="inlineStr">
         <is>
-          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
+          <t>Found 23 Oct: 39 of the 79 scripts in medical_hrms/ are not used by hooks, patches or other code (run by hand in the past): add_fields, apply_hr_workspace_layout, check_hrm_readiness, check_local_leave_flows, cleanup_duplicate_employee_ministry_fields, configure_hr_workspace_access, configure_hrm_request_governance, configure_instructor_handoff_permissions, create_company_car, create_education_allowance, create_medical_license, create_overtime_request, create_permission_request, create_remaining_doctypes, create_remote_work, create_return_from_leave, create_salary_cert, create_training_request, create_workspace, ensure_notification_settings, fill_jameah_arabic_fallback, fix_assessment_group_doctype, fix_child_table_column_widths, fix_return_from_leave_list_view, fix_swapped_ministry_code_rows, grant_hr_login_access, grant_hr_module_permissions, migrate_jameah_dummy_data, normalize_jameah_ministry_codes, quick_grant_hr_permissions, rebuild_workspace, rename_children_medical_allowance_doctype, rename_employee_jameah_labels, report_hr_permissions, run_hrm_demo_verification, translate_jameah_ministry_names_to_arabic, unify_workspace, update_workspace_db (+ a duplicate removed, B-45). Some are risky to run again (configure_hrm_request_governance replaces the request doctypes' permissions; create_* and rename_* recreate or rename doctypes).</t>
         </is>
       </c>
       <c r="I59" s="31" t="inlineStr">
         <is>
-          <t>Client UAT.</t>
+          <t>Keep the useful tools (check_hrm_readiness, report_hr_permissions, run_hrm_demo_verification) in a tools/ folder; delete the one-offs already applied; never run configure_hrm_request_governance.</t>
         </is>
       </c>
       <c r="J59" s="31" t="inlineStr">
         <is>
-          <t>Test Report</t>
+          <t>medical_hrms/*.py</t>
         </is>
       </c>
       <c r="K59" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="B60" s="30" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>System e-mail account password cannot be decrypted</t>
+          <t>HR Portal and Employee Portal in the new college design</t>
         </is>
       </c>
       <c r="D60" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
@@ -5693,17 +5747,17 @@
       </c>
       <c r="H60" s="31" t="inlineStr">
         <is>
-          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
+          <t>Same look as the Education team's new portals (Instructor Portal): left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so Education's changes cannot break these pages.</t>
         </is>
       </c>
       <c r="I60" s="31" t="inlineStr">
         <is>
-          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
+          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
         </is>
       </c>
       <c r="J60" s="31" t="inlineStr">
         <is>
-          <t>Error Log; Email Queue</t>
+          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
         </is>
       </c>
       <c r="K60" s="30" t="inlineStr">
@@ -5715,32 +5769,32 @@
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-62</t>
         </is>
       </c>
       <c r="B61" s="30" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>Instructor form: linking an Employee fails on save</t>
+          <t>HR User could not open the Holiday List ('Not permitted')</t>
         </is>
       </c>
       <c r="D61" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E61" s="30" t="inlineStr">
         <is>
-          <t>Pending – other team</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F61" s="30" t="inlineStr">
         <is>
-          <t>Education team</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G61" s="30" t="inlineStr">
@@ -5750,17 +5804,17 @@
       </c>
       <c r="H61" s="31" t="inlineStr">
         <is>
-          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
+          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
         </is>
       </c>
       <c r="I61" s="31" t="inlineStr">
         <is>
-          <t>Education team: remove or map those fetches on Instructor.</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="J61" s="31" t="inlineStr">
         <is>
-          <t>education Instructor doctype</t>
+          <t>hr_core_permissions.py</t>
         </is>
       </c>
       <c r="K61" s="30" t="inlineStr">
@@ -5772,17 +5826,17 @@
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
         <is>
-          <t>HR-49</t>
+          <t>HR-46</t>
         </is>
       </c>
       <c r="B62" s="30" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C62" s="31" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Full end-to-end test with error sweep (round 3)</t>
         </is>
       </c>
       <c r="D62" s="30" t="inlineStr">
@@ -5802,22 +5856,22 @@
       </c>
       <c r="G62" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H62" s="31" t="inlineStr">
         <is>
-          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
+          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
         </is>
       </c>
       <c r="I62" s="31" t="inlineStr">
         <is>
-          <t>HR to use it to complete the data (HR-50 sheet).</t>
+          <t>Client UAT.</t>
         </is>
       </c>
       <c r="J62" s="31" t="inlineStr">
         <is>
-          <t>report/employees_missing_ministry_data</t>
+          <t>Test Report</t>
         </is>
       </c>
       <c r="K62" s="30" t="inlineStr">
@@ -5829,52 +5883,52 @@
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
-          <t>HR-50</t>
+          <t>HR-47</t>
         </is>
       </c>
       <c r="B63" s="30" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff</t>
+          <t>System e-mail account password cannot be decrypted</t>
         </is>
       </c>
       <c r="D63" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F63" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G63" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H63" s="31" t="inlineStr">
         <is>
-          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
+          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
         </is>
       </c>
       <c r="I63" s="31" t="inlineStr">
         <is>
-          <t>HR to fill the sheet for all non-academic staff.</t>
+          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
         </is>
       </c>
       <c r="J63" s="31" t="inlineStr">
         <is>
-          <t>employee_data_sheet.py</t>
+          <t>Error Log; Email Queue</t>
         </is>
       </c>
       <c r="K63" s="30" t="inlineStr">
@@ -5886,52 +5940,52 @@
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
-          <t>HR-51</t>
+          <t>HR-48</t>
         </is>
       </c>
       <c r="B64" s="30" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C64" s="31" t="inlineStr">
         <is>
-          <t>Unused duplicate of the applicant Ministry fields removed</t>
+          <t>Instructor form: linking an Employee fails on save</t>
         </is>
       </c>
       <c r="D64" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – other team</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Education team</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H64" s="31" t="inlineStr">
         <is>
-          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
+          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
         </is>
       </c>
       <c r="I64" s="31" t="inlineStr">
         <is>
-          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
+          <t>Education team: remove or map those fetches on Instructor.</t>
         </is>
       </c>
       <c r="J64" s="31" t="inlineStr">
         <is>
-          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
+          <t>education Instructor doctype</t>
         </is>
       </c>
       <c r="K64" s="30" t="inlineStr">
@@ -5943,7 +5997,7 @@
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
-          <t>HR-52</t>
+          <t>HR-49</t>
         </is>
       </c>
       <c r="B65" s="30" t="inlineStr">
@@ -5953,22 +6007,22 @@
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="D65" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E65" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F65" s="30" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G65" s="30" t="inlineStr">
@@ -5978,17 +6032,17 @@
       </c>
       <c r="H65" s="31" t="inlineStr">
         <is>
-          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
+          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr">
         <is>
-          <t>Confirm whether 9-digit numbers must be accepted.</t>
+          <t>HR to use it to complete the data (HR-50 sheet).</t>
         </is>
       </c>
       <c r="J65" s="31" t="inlineStr">
         <is>
-          <t>ministry_lookup_validation.py</t>
+          <t>report/employees_missing_ministry_data</t>
         </is>
       </c>
       <c r="K65" s="30" t="inlineStr">
@@ -6000,52 +6054,52 @@
     <row r="66">
       <c r="A66" s="29" t="inlineStr">
         <is>
-          <t>HR-53</t>
+          <t>HR-50</t>
         </is>
       </c>
       <c r="B66" s="30" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C66" s="31" t="inlineStr">
         <is>
-          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
+          <t>Data sheet for non-academic staff</t>
         </is>
       </c>
       <c r="D66" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H66" s="31" t="inlineStr">
         <is>
-          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
+          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
         </is>
       </c>
       <c r="I66" s="31" t="inlineStr">
         <is>
-          <t>Complete or delete the demo record before go-live.</t>
+          <t>HR to fill the sheet for all non-academic staff.</t>
         </is>
       </c>
       <c r="J66" s="31" t="inlineStr">
         <is>
-          <t>Employee EMP-00001</t>
+          <t>employee_data_sheet.py</t>
         </is>
       </c>
       <c r="K66" s="30" t="inlineStr">
@@ -6057,32 +6111,32 @@
     <row r="67">
       <c r="A67" s="29" t="inlineStr">
         <is>
-          <t>HR-54</t>
+          <t>HR-51</t>
         </is>
       </c>
       <c r="B67" s="30" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C67" s="31" t="inlineStr">
         <is>
-          <t>Website logo file missing (/files/rchs-logo.png)</t>
+          <t>Unused duplicate of the applicant Ministry fields removed</t>
         </is>
       </c>
       <c r="D67" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E67" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F67" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G67" s="30" t="inlineStr">
@@ -6092,17 +6146,17 @@
       </c>
       <c r="H67" s="31" t="inlineStr">
         <is>
-          <t>Missing on the local copy; every page requests it.</t>
+          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
         </is>
       </c>
       <c r="I67" s="31" t="inlineStr">
         <is>
-          <t>Check the file exists on the live server.</t>
+          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
         </is>
       </c>
       <c r="J67" s="31" t="inlineStr">
         <is>
-          <t>Website Settings</t>
+          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
         </is>
       </c>
       <c r="K67" s="30" t="inlineStr">
@@ -6114,17 +6168,17 @@
     <row r="68">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>HR-55</t>
+          <t>HR-52</t>
         </is>
       </c>
       <c r="B68" s="30" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C68" s="31" t="inlineStr">
         <is>
-          <t>Link the 216 existing Instructors to Employees</t>
+          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
         </is>
       </c>
       <c r="D68" s="30" t="inlineStr">
@@ -6134,32 +6188,32 @@
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="G68" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H68" s="31" t="inlineStr">
         <is>
-          <t>Tool ready (HR-35). 1 of 216 linked.</t>
+          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
         </is>
       </c>
       <c r="I68" s="31" t="inlineStr">
         <is>
-          <t>HR fills the Instructor data sheet; run the import with commit.</t>
+          <t>Confirm whether 9-digit numbers must be accepted.</t>
         </is>
       </c>
       <c r="J68" s="31" t="inlineStr">
         <is>
-          <t>instructor_data_sheet.py</t>
+          <t>ministry_lookup_validation.py</t>
         </is>
       </c>
       <c r="K68" s="30" t="inlineStr">
@@ -6171,17 +6225,17 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-53</t>
         </is>
       </c>
       <c r="B69" s="30" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>Connect attendance devices</t>
+          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
         </is>
       </c>
       <c r="D69" s="30" t="inlineStr">
@@ -6196,27 +6250,27 @@
       </c>
       <c r="F69" s="30" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G69" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H69" s="31" t="inlineStr">
         <is>
-          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
+          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
         </is>
       </c>
       <c r="I69" s="31" t="inlineStr">
         <is>
-          <t>Connect devices; map device user IDs to Employees.</t>
+          <t>Complete or delete the demo record before go-live.</t>
         </is>
       </c>
       <c r="J69" s="31" t="inlineStr">
         <is>
-          <t>bfac883</t>
+          <t>Employee EMP-00001</t>
         </is>
       </c>
       <c r="K69" s="30" t="inlineStr">
@@ -6228,17 +6282,17 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>HR-57</t>
+          <t>HR-54</t>
         </is>
       </c>
       <c r="B70" s="30" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C70" s="31" t="inlineStr">
         <is>
-          <t>Set the Academic Holiday List</t>
+          <t>Website logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
       <c r="D70" s="30" t="inlineStr">
@@ -6253,27 +6307,27 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H70" s="31" t="inlineStr">
         <is>
-          <t>Not set; the page warns about it.</t>
+          <t>Missing on the local copy; every page requests it.</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
+          <t>Check the file exists on the live server.</t>
         </is>
       </c>
       <c r="J70" s="31" t="inlineStr">
         <is>
-          <t>academic_presence_setup.py</t>
+          <t>Website Settings</t>
         </is>
       </c>
       <c r="K70" s="30" t="inlineStr">
@@ -6285,17 +6339,17 @@
     <row r="71">
       <c r="A71" s="29" t="inlineStr">
         <is>
-          <t>HR-58</t>
+          <t>HR-55</t>
         </is>
       </c>
       <c r="B71" s="30" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>Deploy to the live server</t>
+          <t>Link the 216 existing Instructors to Employees</t>
         </is>
       </c>
       <c r="D71" s="30" t="inlineStr">
@@ -6310,7 +6364,7 @@
       </c>
       <c r="F71" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G71" s="30" t="inlineStr">
@@ -6320,74 +6374,74 @@
       </c>
       <c r="H71" s="31" t="inlineStr">
         <is>
-          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too.</t>
+          <t>Tool ready (HR-35). 1 of 216 linked.</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr">
         <is>
-          <t>Merge, pull on the server, bench migrate, restart; smoke-test with the Test Cases workbook.</t>
+          <t>HR fills the Instructor data sheet; run the import with commit.</t>
         </is>
       </c>
       <c r="J71" s="31" t="inlineStr">
         <is>
-          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
+          <t>instructor_data_sheet.py</t>
         </is>
       </c>
       <c r="K71" s="30" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="29" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="B72" s="30" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
-          <t>Research: Jameah system, Ministry documents, view contract</t>
+          <t>Connect attendance devices</t>
         </is>
       </c>
       <c r="D72" s="30" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H72" s="31" t="inlineStr">
         <is>
-          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
+          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
         </is>
       </c>
       <c r="I72" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Connect devices; map device user IDs to Employees.</t>
         </is>
       </c>
       <c r="J72" s="31" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>bfac883</t>
         </is>
       </c>
       <c r="K72" s="30" t="inlineStr">
@@ -6399,52 +6453,52 @@
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>HR-57</t>
         </is>
       </c>
       <c r="B73" s="30" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
-          <t>Ministry views for Employees (5) and Students (10)</t>
+          <t>Set the Academic Holiday List</t>
         </is>
       </c>
       <c r="D73" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E73" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F73" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G73" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H73" s="31" t="inlineStr">
         <is>
-          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
+          <t>Not set; the page warns about it.</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
         </is>
       </c>
       <c r="J73" s="31" t="inlineStr">
         <is>
-          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
+          <t>academic_presence_setup.py</t>
         </is>
       </c>
       <c r="K73" s="30" t="inlineStr">
@@ -6456,32 +6510,32 @@
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>HR-58</t>
         </is>
       </c>
       <c r="B74" s="30" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C74" s="31" t="inlineStr">
         <is>
-          <t>Code crosswalk (Jameah Code Map)</t>
+          <t>Deploy to the live server</t>
         </is>
       </c>
       <c r="D74" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G74" s="30" t="inlineStr">
@@ -6491,29 +6545,29 @@
       </c>
       <c r="H74" s="31" t="inlineStr">
         <is>
-          <t>299 college values mapped to official codes by meaning; wrong codes in Education masters (City 90, REL001...) no longer reach the Ministry.</t>
+          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr">
         <is>
-          <t>Review 3 values (JM-11).</t>
+          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
         </is>
       </c>
       <c r="J74" s="31" t="inlineStr">
         <is>
-          <t>jameah/code_map.py</t>
+          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
         </is>
       </c>
       <c r="K74" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="29" t="inlineStr">
         <is>
-          <t>JM-04</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="B75" s="30" t="inlineStr">
@@ -6523,12 +6577,12 @@
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>Research: Jameah system, Ministry documents, view contract</t>
         </is>
       </c>
       <c r="D75" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="E75" s="30" t="inlineStr">
@@ -6548,17 +6602,17 @@
       </c>
       <c r="H75" s="31" t="inlineStr">
         <is>
-          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
+          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
         </is>
       </c>
       <c r="I75" s="31" t="inlineStr">
         <is>
-          <t>Fill 6 values (JM-10).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J75" s="31" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="K75" s="30" t="inlineStr">
@@ -6570,7 +6624,7 @@
     <row r="76">
       <c r="A76" s="29" t="inlineStr">
         <is>
-          <t>JM-05</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="B76" s="30" t="inlineStr">
@@ -6580,7 +6634,7 @@
       </c>
       <c r="C76" s="31" t="inlineStr">
         <is>
-          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
+          <t>Ministry views for Employees (5) and Students (10)</t>
         </is>
       </c>
       <c r="D76" s="30" t="inlineStr">
@@ -6600,34 +6654,34 @@
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H76" s="31" t="inlineStr">
         <is>
-          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
+          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
         </is>
       </c>
       <c r="I76" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="J76" s="31" t="inlineStr">
         <is>
-          <t>jameah/summary.py</t>
+          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
         </is>
       </c>
       <c r="K76" s="30" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="29" t="inlineStr">
         <is>
-          <t>JM-06</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="B77" s="30" t="inlineStr">
@@ -6637,7 +6691,7 @@
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>Independent verification of every view</t>
+          <t>Code crosswalk (Jameah Code Map)</t>
         </is>
       </c>
       <c r="D77" s="30" t="inlineStr">
@@ -6657,22 +6711,22 @@
       </c>
       <c r="G77" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H77" s="31" t="inlineStr">
         <is>
-          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the Education update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
+          <t>299 college values mapped to official codes by meaning; wrong codes in Education masters (City 90, REL001...) no longer reach the Ministry.</t>
         </is>
       </c>
       <c r="I77" s="31" t="inlineStr">
         <is>
-          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
+          <t>Review 3 values (JM-11).</t>
         </is>
       </c>
       <c r="J77" s="31" t="inlineStr">
         <is>
-          <t>jameah/verify.py; test_jameah.py</t>
+          <t>jameah/code_map.py</t>
         </is>
       </c>
       <c r="K77" s="30" t="inlineStr">
@@ -6684,7 +6738,7 @@
     <row r="78">
       <c r="A78" s="29" t="inlineStr">
         <is>
-          <t>JM-18</t>
+          <t>JM-04</t>
         </is>
       </c>
       <c r="B78" s="30" t="inlineStr">
@@ -6694,12 +6748,12 @@
       </c>
       <c r="C78" s="31" t="inlineStr">
         <is>
-          <t>Ministry GPA and credit hours = the college's official figures</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="D78" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -6714,22 +6768,22 @@
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H78" s="31" t="inlineStr">
         <is>
-          <t>Found 21 Oct: Education's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads Education's official functions (read only, no change to Education); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
+          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr">
         <is>
-          <t>Deploy together with the Education master update (HR-58); re-run verify on the live server.</t>
+          <t>Fill 6 values (JM-10).</t>
         </is>
       </c>
       <c r="J78" s="31" t="inlineStr">
         <is>
-          <t>jameah/summary.py; jameah/verify.py</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="K78" s="30" t="inlineStr">
@@ -6741,7 +6795,7 @@
     <row r="79">
       <c r="A79" s="29" t="inlineStr">
         <is>
-          <t>JM-19</t>
+          <t>JM-05</t>
         </is>
       </c>
       <c r="B79" s="30" t="inlineStr">
@@ -6751,42 +6805,42 @@
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>Hourly academic summary refresh slows the site while it runs</t>
+          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
         </is>
       </c>
       <c r="D79" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E79" s="30" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F79" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G79" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H79" s="31" t="inlineStr">
         <is>
-          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
+          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr">
         <is>
-          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J79" s="31" t="inlineStr">
         <is>
-          <t>jameah/summary.py; hooks.py hourly_long</t>
+          <t>jameah/summary.py</t>
         </is>
       </c>
       <c r="K79" s="30" t="inlineStr">
@@ -6798,7 +6852,7 @@
     <row r="80">
       <c r="A80" s="29" t="inlineStr">
         <is>
-          <t>JM-07</t>
+          <t>JM-06</t>
         </is>
       </c>
       <c r="B80" s="30" t="inlineStr">
@@ -6808,7 +6862,7 @@
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
-          <t>Jameah Data Check page and Employee preview</t>
+          <t>Independent verification of every view</t>
         </is>
       </c>
       <c r="D80" s="30" t="inlineStr">
@@ -6828,22 +6882,22 @@
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H80" s="31" t="inlineStr">
         <is>
-          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
+          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the Education update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="J80" s="31" t="inlineStr">
         <is>
-          <t>page/jameah_data_check</t>
+          <t>jameah/verify.py; test_jameah.py</t>
         </is>
       </c>
       <c r="K80" s="30" t="inlineStr">
@@ -6855,7 +6909,7 @@
     <row r="81">
       <c r="A81" s="29" t="inlineStr">
         <is>
-          <t>JM-08</t>
+          <t>JM-18</t>
         </is>
       </c>
       <c r="B81" s="30" t="inlineStr">
@@ -6865,42 +6919,42 @@
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
-          <t>Read-only database account for the Ministry agent</t>
+          <t>Ministry GPA and credit hours = the college's official figures</t>
         </is>
       </c>
       <c r="D81" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E81" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G81" s="30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H81" s="31" t="inlineStr">
         <is>
-          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
+          <t>Found 21 Oct: Education's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads Education's official functions (read only, no change to Education); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
         </is>
       </c>
       <c r="I81" s="31" t="inlineStr">
         <is>
-          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
+          <t>Deploy together with the Education master update (HR-58); re-run verify on the live server.</t>
         </is>
       </c>
       <c r="J81" s="31" t="inlineStr">
         <is>
-          <t>jameah/README.md</t>
+          <t>jameah/summary.py; jameah/verify.py</t>
         </is>
       </c>
       <c r="K81" s="30" t="inlineStr">
@@ -6912,7 +6966,7 @@
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>JM-09</t>
+          <t>JM-19</t>
         </is>
       </c>
       <c r="B82" s="30" t="inlineStr">
@@ -6922,7 +6976,7 @@
       </c>
       <c r="C82" s="31" t="inlineStr">
         <is>
-          <t>Confirm view and column names with the Ministry</t>
+          <t>Hourly academic summary refresh slows the site while it runs</t>
         </is>
       </c>
       <c r="D82" s="30" t="inlineStr">
@@ -6932,44 +6986,44 @@
       </c>
       <c r="E82" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H82" s="31" t="inlineStr">
         <is>
-          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
+          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
         </is>
       </c>
       <c r="I82" s="31" t="inlineStr">
         <is>
-          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
+          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
         </is>
       </c>
       <c r="J82" s="31" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>jameah/summary.py; hooks.py hourly_long</t>
         </is>
       </c>
       <c r="K82" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>JM-10</t>
+          <t>JM-07</t>
         </is>
       </c>
       <c r="B83" s="30" t="inlineStr">
@@ -6979,22 +7033,22 @@
       </c>
       <c r="C83" s="31" t="inlineStr">
         <is>
-          <t>Fill Jameah Settings (6 values)</t>
+          <t>Jameah Data Check page and Employee preview</t>
         </is>
       </c>
       <c r="D83" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E83" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F83" s="30" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G83" s="30" t="inlineStr">
@@ -7004,17 +7058,17 @@
       </c>
       <c r="H83" s="31" t="inlineStr">
         <is>
-          <t>Empty values are sent as empty.</t>
+          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
         </is>
       </c>
       <c r="I83" s="31" t="inlineStr">
         <is>
-          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="J83" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-settings</t>
+          <t>page/jameah_data_check</t>
         </is>
       </c>
       <c r="K83" s="30" t="inlineStr">
@@ -7026,7 +7080,7 @@
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
-          <t>JM-11</t>
+          <t>JM-08</t>
         </is>
       </c>
       <c r="B84" s="30" t="inlineStr">
@@ -7036,7 +7090,7 @@
       </c>
       <c r="C84" s="31" t="inlineStr">
         <is>
-          <t>Map 3 college values to Ministry codes</t>
+          <t>Read-only database account for the Ministry agent</t>
         </is>
       </c>
       <c r="D84" s="30" t="inlineStr">
@@ -7046,12 +7100,12 @@
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G84" s="30" t="inlineStr">
@@ -7061,17 +7115,17 @@
       </c>
       <c r="H84" s="31" t="inlineStr">
         <is>
-          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
+          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
         </is>
       </c>
       <c r="I84" s="31" t="inlineStr">
         <is>
-          <t>Pick the code in Jameah Code Map and set Verified.</t>
+          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
         </is>
       </c>
       <c r="J84" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-code-map</t>
+          <t>jameah/README.md</t>
         </is>
       </c>
       <c r="K84" s="30" t="inlineStr">
@@ -7083,7 +7137,7 @@
     <row r="85">
       <c r="A85" s="29" t="inlineStr">
         <is>
-          <t>JM-12</t>
+          <t>JM-09</t>
         </is>
       </c>
       <c r="B85" s="30" t="inlineStr">
@@ -7093,7 +7147,7 @@
       </c>
       <c r="C85" s="31" t="inlineStr">
         <is>
-          <t>Ministry fields with no source in the college system</t>
+          <t>Confirm view and column names with the Ministry</t>
         </is>
       </c>
       <c r="D85" s="30" t="inlineStr">
@@ -7108,27 +7162,27 @@
       </c>
       <c r="F85" s="30" t="inlineStr">
         <is>
-          <t>Academic Affairs + Education team</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="G85" s="30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H85" s="31" t="inlineStr">
         <is>
-          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
+          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
         </is>
       </c>
       <c r="I85" s="31" t="inlineStr">
         <is>
-          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
+          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
         </is>
       </c>
       <c r="J85" s="31" t="inlineStr">
         <is>
-          <t>Jameah report; VIEWS.md</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="K85" s="30" t="inlineStr">
@@ -7140,7 +7194,7 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>JM-13</t>
+          <t>JM-10</t>
         </is>
       </c>
       <c r="B86" s="30" t="inlineStr">
@@ -7150,7 +7204,7 @@
       </c>
       <c r="C86" s="31" t="inlineStr">
         <is>
-          <t>Correct source data found by the checks</t>
+          <t>Fill Jameah Settings (6 values)</t>
         </is>
       </c>
       <c r="D86" s="30" t="inlineStr">
@@ -7160,12 +7214,12 @@
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Registrar / Education team</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G86" s="30" t="inlineStr">
@@ -7175,17 +7229,17 @@
       </c>
       <c r="H86" s="31" t="inlineStr">
         <is>
-          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
+          <t>Empty values are sent as empty.</t>
         </is>
       </c>
       <c r="I86" s="31" t="inlineStr">
         <is>
-          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
+          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
         </is>
       </c>
       <c r="J86" s="31" t="inlineStr">
         <is>
-          <t>/app/jameah-data-check</t>
+          <t>/app/jameah-settings</t>
         </is>
       </c>
       <c r="K86" s="30" t="inlineStr">
@@ -7197,7 +7251,7 @@
     <row r="87">
       <c r="A87" s="29" t="inlineStr">
         <is>
-          <t>JM-14</t>
+          <t>JM-11</t>
         </is>
       </c>
       <c r="B87" s="30" t="inlineStr">
@@ -7207,22 +7261,22 @@
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>Faculty views (8 sections)</t>
+          <t>Map 3 college values to Ministry codes</t>
         </is>
       </c>
       <c r="D87" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F87" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G87" s="30" t="inlineStr">
@@ -7232,17 +7286,17 @@
       </c>
       <c r="H87" s="31" t="inlineStr">
         <is>
-          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
+          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
         </is>
       </c>
       <c r="I87" s="31" t="inlineStr">
         <is>
-          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
+          <t>Pick the code in Jameah Code Map and set Verified.</t>
         </is>
       </c>
       <c r="J87" s="31" t="inlineStr">
         <is>
-          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
+          <t>/app/jameah-code-map</t>
         </is>
       </c>
       <c r="K87" s="30" t="inlineStr">
@@ -7254,7 +7308,7 @@
     <row r="88">
       <c r="A88" s="29" t="inlineStr">
         <is>
-          <t>JM-15</t>
+          <t>JM-12</t>
         </is>
       </c>
       <c r="B88" s="30" t="inlineStr">
@@ -7264,7 +7318,7 @@
       </c>
       <c r="C88" s="31" t="inlineStr">
         <is>
-          <t>Institute views (20 sections)</t>
+          <t>Ministry fields with no source in the college system</t>
         </is>
       </c>
       <c r="D88" s="30" t="inlineStr">
@@ -7274,12 +7328,12 @@
       </c>
       <c r="E88" s="30" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Academic Affairs + Education team</t>
         </is>
       </c>
       <c r="G88" s="30" t="inlineStr">
@@ -7289,17 +7343,17 @@
       </c>
       <c r="H88" s="31" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
         </is>
       </c>
       <c r="I88" s="31" t="inlineStr">
         <is>
-          <t>Build after Faculty; needs institute data from HR.</t>
+          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
         </is>
       </c>
       <c r="J88" s="31" t="inlineStr">
         <is>
-          <t>MINISTRY_FIELD_MAPPING.html</t>
+          <t>Jameah report; VIEWS.md</t>
         </is>
       </c>
       <c r="K88" s="30" t="inlineStr">
@@ -7311,7 +7365,7 @@
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>JM-16</t>
+          <t>JM-13</t>
         </is>
       </c>
       <c r="B89" s="30" t="inlineStr">
@@ -7321,7 +7375,7 @@
       </c>
       <c r="C89" s="31" t="inlineStr">
         <is>
-          <t>Old Education viewJameah* views (42)</t>
+          <t>Correct source data found by the checks</t>
         </is>
       </c>
       <c r="D89" s="30" t="inlineStr">
@@ -7331,32 +7385,32 @@
       </c>
       <c r="E89" s="30" t="inlineStr">
         <is>
-          <t>Pending – other team</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F89" s="30" t="inlineStr">
         <is>
-          <t>Education team</t>
+          <t>Registrar / Education team</t>
         </is>
       </c>
       <c r="G89" s="30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H89" s="31" t="inlineStr">
         <is>
-          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
         </is>
       </c>
       <c r="I89" s="31" t="inlineStr">
         <is>
-          <t>Education team to retire them once ours are confirmed.</t>
+          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
         </is>
       </c>
       <c r="J89" s="31" t="inlineStr">
         <is>
-          <t>education/jameah_system</t>
+          <t>/app/jameah-data-check</t>
         </is>
       </c>
       <c r="K89" s="30" t="inlineStr">
@@ -7368,63 +7422,234 @@
     <row r="90">
       <c r="A90" s="29" t="inlineStr">
         <is>
+          <t>JM-14</t>
+        </is>
+      </c>
+      <c r="B90" s="30" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C90" s="31" t="inlineStr">
+        <is>
+          <t>Faculty views (8 sections)</t>
+        </is>
+      </c>
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E90" s="30" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F90" s="30" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G90" s="30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H90" s="31" t="inlineStr">
+        <is>
+          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
+        </is>
+      </c>
+      <c r="I90" s="31" t="inlineStr">
+        <is>
+          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
+        </is>
+      </c>
+      <c r="J90" s="31" t="inlineStr">
+        <is>
+          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
+        </is>
+      </c>
+      <c r="K90" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="29" t="inlineStr">
+        <is>
+          <t>JM-15</t>
+        </is>
+      </c>
+      <c r="B91" s="30" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C91" s="31" t="inlineStr">
+        <is>
+          <t>Institute views (20 sections)</t>
+        </is>
+      </c>
+      <c r="D91" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="30" t="inlineStr">
+        <is>
+          <t>Pending – development</t>
+        </is>
+      </c>
+      <c r="F91" s="30" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G91" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H91" s="31" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="I91" s="31" t="inlineStr">
+        <is>
+          <t>Build after Faculty; needs institute data from HR.</t>
+        </is>
+      </c>
+      <c r="J91" s="31" t="inlineStr">
+        <is>
+          <t>MINISTRY_FIELD_MAPPING.html</t>
+        </is>
+      </c>
+      <c r="K91" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="29" t="inlineStr">
+        <is>
+          <t>JM-16</t>
+        </is>
+      </c>
+      <c r="B92" s="30" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C92" s="31" t="inlineStr">
+        <is>
+          <t>Old Education viewJameah* views (42)</t>
+        </is>
+      </c>
+      <c r="D92" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="30" t="inlineStr">
+        <is>
+          <t>Pending – other team</t>
+        </is>
+      </c>
+      <c r="F92" s="30" t="inlineStr">
+        <is>
+          <t>Education team</t>
+        </is>
+      </c>
+      <c r="G92" s="30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H92" s="31" t="inlineStr">
+        <is>
+          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+        </is>
+      </c>
+      <c r="I92" s="31" t="inlineStr">
+        <is>
+          <t>Education team to retire them once ours are confirmed.</t>
+        </is>
+      </c>
+      <c r="J92" s="31" t="inlineStr">
+        <is>
+          <t>education/jameah_system</t>
+        </is>
+      </c>
+      <c r="K92" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="29" t="inlineStr">
+        <is>
           <t>JM-17</t>
         </is>
       </c>
-      <c r="B90" s="30" t="inlineStr">
+      <c r="B93" s="30" t="inlineStr">
         <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="C90" s="31" t="inlineStr">
+      <c r="C93" s="31" t="inlineStr">
         <is>
           <t>Transcript GPA rounding at exact ties</t>
         </is>
       </c>
-      <c r="D90" s="30" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E90" s="30" t="inlineStr">
+      <c r="D93" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E93" s="30" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F90" s="30" t="inlineStr">
+      <c r="F93" s="30" t="inlineStr">
         <is>
           <t>Education team</t>
         </is>
       </c>
-      <c r="G90" s="30" t="inlineStr">
+      <c r="G93" s="30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H90" s="31" t="inlineStr">
+      <c r="H93" s="31" t="inlineStr">
         <is>
           <t>Resolved by Education's new GPA module (exact half-up rounding); the views now use it (JM-18).</t>
         </is>
       </c>
-      <c r="I90" s="31" t="inlineStr">
+      <c r="I93" s="31" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J90" s="31" t="inlineStr">
+      <c r="J93" s="31" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="K90" s="30" t="inlineStr">
+      <c r="K93" s="30" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K90"/>
-  <conditionalFormatting sqref="A2:K290">
+  <autoFilter ref="A1:K93"/>
+  <conditionalFormatting sqref="A2:K293">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E2="Done"</formula>
     </cfRule>
@@ -7451,10 +7676,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
+    <dataValidation sqref="E2:E293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
       <formula1>"Done,Done – client UAT pending,In progress,Pending – decision needed,Pending – data / setup,Pending – development,Pending – other team,Planned"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G290" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7468,7 +7693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9618,37 +9843,37 @@
     <row r="42">
       <c r="A42" s="30" t="inlineStr">
         <is>
-          <t>B-28</t>
+          <t>B-45</t>
         </is>
       </c>
       <c r="B42" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="D42" s="31" t="inlineStr">
         <is>
-          <t>Employees clicking the 'Medical HRMS' breadcrumb got 'Not permitted - No permission for Page'</t>
+          <t>Stray files: a duplicate script with a space in its name (setup_jameah_fields copy.py) and a Windows download-marker file (...Copy.html:Zone.Identifier)</t>
         </is>
       </c>
       <c r="E42" s="31" t="inlineStr">
         <is>
-          <t>Frappe chooses the breadcrumb workspace without a permission check</t>
+          <t>Copied by hand / downloaded from Windows</t>
         </is>
       </c>
       <c r="F42" s="31" t="inlineStr">
         <is>
-          <t>Keep only workspaces the user can open</t>
+          <t>Removed</t>
         </is>
       </c>
       <c r="G42" s="30" t="inlineStr">
         <is>
-          <t>HR-59</t>
+          <t>HR-72</t>
         </is>
       </c>
       <c r="H42" s="30" t="inlineStr">
@@ -9658,174 +9883,538 @@
       </c>
       <c r="I42" s="31" t="inlineStr">
         <is>
-          <t>E2E NAV-01/02</t>
+          <t>tests/checks/files.py</t>
         </is>
       </c>
       <c r="J42" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="30" t="inlineStr">
         <is>
-          <t>B-25</t>
+          <t>B-46</t>
         </is>
       </c>
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="D43" s="31" t="inlineStr">
         <is>
-          <t>System e-mails fail: password cannot be decrypted</t>
+          <t>README told admins to run old setup scripts by hand; one of them (configure_hrm_request_governance) replaces the request doctypes' tested permissions with its own</t>
         </is>
       </c>
       <c r="E43" s="31" t="inlineStr">
         <is>
-          <t>Email Account 'Notifications' password encrypted with another key</t>
+          <t>README from June, never updated after the setup moved into migrate</t>
         </is>
       </c>
       <c r="F43" s="31" t="inlineStr">
         <is>
-          <t>Re-enter the password on the server</t>
+          <t>README rewritten: migrate does the setup; those scripts are not to be run; team workflow; documents index</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-72</t>
         </is>
       </c>
       <c r="H43" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I43" s="31" t="inlineStr">
         <is>
-          <t>Error Log</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="J43" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="30" t="inlineStr">
         <is>
-          <t>B-26</t>
+          <t>B-47</t>
         </is>
       </c>
       <c r="B44" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>Instructor (Education)</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="D44" s="31" t="inlineStr">
         <is>
-          <t>Linking an Employee in the Instructor form fails</t>
+          <t>Developer guide described an 'LMS Instructor' field on Employee that does not exist, and the old sick-leave names</t>
         </is>
       </c>
       <c r="E44" s="31" t="inlineStr">
         <is>
-          <t>fetch_from copies Ministry codes into Education lists</t>
+          <t>Guide from May</t>
         </is>
       </c>
       <c r="F44" s="31" t="inlineStr">
         <is>
-          <t>Education team to change the fetch</t>
+          <t>Corrected (Instructor links to Employee; Sick Leave 1/2/3; Start Sick Leave Year)</t>
         </is>
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-72</t>
         </is>
       </c>
       <c r="H44" s="30" t="inlineStr">
         <is>
-          <t>Open – other team</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I44" s="31" t="inlineStr">
         <is>
-          <t>Reproduced 21 Oct</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="J44" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="30" t="inlineStr">
         <is>
+          <t>B-48</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>Testing (QA scripts only)</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>QA setup failed now and then with 'TimestampMismatchError' on a user's Contact</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>Jobs queued by the QA clean-up (linked Contacts, shares) ran a few seconds later, while the setup was creating the same users again</t>
+        </is>
+      </c>
+      <c r="F45" s="31" t="inlineStr">
+        <is>
+          <t>The clean-up runs all its follow-up jobs at once</t>
+        </is>
+      </c>
+      <c r="G45" s="30" t="inlineStr">
+        <is>
+          <t>HR-67</t>
+        </is>
+      </c>
+      <c r="H45" s="30" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I45" s="31" t="inlineStr">
+        <is>
+          <t>3 clean-up + setup cycles in a row</t>
+        </is>
+      </c>
+      <c r="J45" s="30" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>B-49</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>Unit test of the Jameah refresh lock failed while a real hourly refresh was running</t>
+        </is>
+      </c>
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>The test assumed no refresh holds the lock</t>
+        </is>
+      </c>
+      <c r="F46" s="31" t="inlineStr">
+        <is>
+          <t>Skips while a real refresh runs (the lock working as intended)</t>
+        </is>
+      </c>
+      <c r="G46" s="30" t="inlineStr">
+        <is>
+          <t>B-43</t>
+        </is>
+      </c>
+      <c r="H46" s="30" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I46" s="31" t="inlineStr">
+        <is>
+          <t>Unit tests</t>
+        </is>
+      </c>
+      <c r="J46" s="30" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>B-50</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="30" t="inlineStr">
+        <is>
+          <t>Ministry codes</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>The Ministry code search refused a category sent as JSON text by a direct API call</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>It only accepted a dictionary (what the form search sends)</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="inlineStr">
+        <is>
+          <t>Accepts both</t>
+        </is>
+      </c>
+      <c r="G47" s="30" t="inlineStr">
+        <is>
+          <t>HR-72</t>
+        </is>
+      </c>
+      <c r="H47" s="30" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I47" s="31" t="inlineStr">
+        <is>
+          <t>tests/checks/api_methods.py</t>
+        </is>
+      </c>
+      <c r="J47" s="30" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>B-51</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>The error sweep did not open 4 Jameah doctypes, saved records, the report, or employees' own request lists</t>
+        </is>
+      </c>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>Route list written before those existed</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="inlineStr">
+        <is>
+          <t>Sweep covers every Medical HRMS doctype (list, new, newest record), the report, both workspaces and employees' lists</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="inlineStr">
+        <is>
+          <t>HR-72</t>
+        </is>
+      </c>
+      <c r="H48" s="30" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I48" s="31" t="inlineStr">
+        <is>
+          <t>E2E SWP-01 - SWP-03</t>
+        </is>
+      </c>
+      <c r="J48" s="30" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>B-28</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C49" s="30" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="inlineStr">
+        <is>
+          <t>Employees clicking the 'Medical HRMS' breadcrumb got 'Not permitted - No permission for Page'</t>
+        </is>
+      </c>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>Frappe chooses the breadcrumb workspace without a permission check</t>
+        </is>
+      </c>
+      <c r="F49" s="31" t="inlineStr">
+        <is>
+          <t>Keep only workspaces the user can open</t>
+        </is>
+      </c>
+      <c r="G49" s="30" t="inlineStr">
+        <is>
+          <t>HR-59</t>
+        </is>
+      </c>
+      <c r="H49" s="30" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I49" s="31" t="inlineStr">
+        <is>
+          <t>E2E NAV-01/02</t>
+        </is>
+      </c>
+      <c r="J49" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>B-25</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="inlineStr">
+        <is>
+          <t>System e-mails fail: password cannot be decrypted</t>
+        </is>
+      </c>
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>Email Account 'Notifications' password encrypted with another key</t>
+        </is>
+      </c>
+      <c r="F50" s="31" t="inlineStr">
+        <is>
+          <t>Re-enter the password on the server</t>
+        </is>
+      </c>
+      <c r="G50" s="30" t="inlineStr">
+        <is>
+          <t>HR-47</t>
+        </is>
+      </c>
+      <c r="H50" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I50" s="31" t="inlineStr">
+        <is>
+          <t>Error Log</t>
+        </is>
+      </c>
+      <c r="J50" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>B-26</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t>Instructor (Education)</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>Linking an Employee in the Instructor form fails</t>
+        </is>
+      </c>
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>fetch_from copies Ministry codes into Education lists</t>
+        </is>
+      </c>
+      <c r="F51" s="31" t="inlineStr">
+        <is>
+          <t>Education team to change the fetch</t>
+        </is>
+      </c>
+      <c r="G51" s="30" t="inlineStr">
+        <is>
+          <t>HR-48</t>
+        </is>
+      </c>
+      <c r="H51" s="30" t="inlineStr">
+        <is>
+          <t>Open – other team</t>
+        </is>
+      </c>
+      <c r="I51" s="31" t="inlineStr">
+        <is>
+          <t>Reproduced 21 Oct</t>
+        </is>
+      </c>
+      <c r="J51" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
           <t>B-27</t>
         </is>
       </c>
-      <c r="B45" s="30" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C45" s="30" t="inlineStr">
+      <c r="B52" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="D45" s="31" t="inlineStr">
+      <c r="D52" s="31" t="inlineStr">
         <is>
           <t>Logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
-      <c r="E45" s="31" t="inlineStr">
+      <c r="E52" s="31" t="inlineStr">
         <is>
           <t>File not on this copy</t>
         </is>
       </c>
-      <c r="F45" s="31" t="inlineStr">
+      <c r="F52" s="31" t="inlineStr">
         <is>
           <t>Check on the live server</t>
         </is>
       </c>
-      <c r="G45" s="30" t="inlineStr">
+      <c r="G52" s="30" t="inlineStr">
         <is>
           <t>HR-54</t>
         </is>
       </c>
-      <c r="H45" s="30" t="inlineStr">
+      <c r="H52" s="30" t="inlineStr">
         <is>
           <t>Open – check server</t>
         </is>
       </c>
-      <c r="I45" s="31" t="inlineStr">
+      <c r="I52" s="31" t="inlineStr">
         <is>
           <t>Error sweep</t>
         </is>
       </c>
-      <c r="J45" s="30" t="inlineStr">
+      <c r="J52" s="30" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J45"/>
-  <conditionalFormatting sqref="A2:J145">
+  <autoFilter ref="A1:J52"/>
+  <conditionalFormatting sqref="A2:J152">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H2="Fixed"</formula>
     </cfRule>
@@ -9840,7 +10429,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H145" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Fixed,Open,Open – other team,Open – check server"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10397,7 +10986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10437,7 +11026,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B2" s="30" t="inlineStr">
@@ -10447,12 +11036,12 @@
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D2" s="31" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E2" s="30" t="inlineStr">
@@ -10474,12 +11063,12 @@
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D3" s="31" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E3" s="30" t="inlineStr">
@@ -10496,17 +11085,17 @@
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D4" s="31" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
@@ -10518,22 +11107,22 @@
     <row r="5">
       <c r="A5" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D5" s="31" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E5" s="30" t="inlineStr">
@@ -10550,17 +11139,17 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D6" s="31" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
@@ -10577,17 +11166,17 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C7" s="31" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D7" s="31" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E7" s="30" t="inlineStr">
@@ -10599,7 +11188,7 @@
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="30" t="inlineStr">
@@ -10609,12 +11198,12 @@
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
@@ -10626,7 +11215,7 @@
     <row r="9">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
@@ -10636,12 +11225,12 @@
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E9" s="30" t="inlineStr">
@@ -10653,32 +11242,59 @@
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D10" s="31" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -16,9 +16,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$K$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="B54" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$152,A54)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$154,A54)</f>
         <v/>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="B55" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$152,A55)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$154,A55)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="B56" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$152,A56)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$154,A56)</f>
         <v/>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B57" s="19">
-        <f>COUNTIF(Bugs!$H$2:$H$152,A57)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$154,A57)</f>
         <v/>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="H58" s="31" t="inlineStr">
         <is>
-          <t>Files: 177 Python files compile, no undefined names (pyflakes); 26 JS files and the job form's 3 inline scripts parse; 26 JSON files load; 571 Arabic translations keep their placeholders. Site: 109 hooks / scheduler jobs / overrides / assets / patches resolve; 29 Medical HRMS doctypes, 73 custom link fields, the newest saved records (validate), the report, 4 pages and 2 workspaces. Server: all 29 methods called as visitor, employee and HR User (87 calls, none open to the wrong role, no server error). Unit tests: 19 files, 37 tests. Browser: the full suite, with the error sweep now opening every Medical HRMS doctype (list, new form, newest record), the report and both workspaces for HR, and employees' own request lists. The checks are kept as tests/checks/files.py, site.py and api_methods.py. Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>Files: 177 Python files compile, no undefined names (pyflakes); 26 JS files and the job form's 3 inline scripts parse; 26 JSON files load; 571 Arabic translations keep their placeholders. Site: 109 hooks / scheduler jobs / overrides / assets / patches resolve; 29 Medical HRMS doctypes, 73 custom link fields, the newest saved records (validate), the report, 4 pages and 2 workspaces. Server: all 29 methods called as visitor, employee and HR User (87 calls, none open to the wrong role, no server error). Unit tests: 19 files, 37 tests. Browser: the full suite, with the error sweep now opening every Medical HRMS doctype (list, new form, newest record), the report and both workspaces for HR, and employees' own request lists. The checks are kept as tests/checks/files.py, site.py and api_methods.py; each records its result in the Test Cases workbook (Last automated run). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="I58" s="31" t="inlineStr">
@@ -7693,7 +7693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10207,37 +10207,37 @@
     <row r="49">
       <c r="A49" s="30" t="inlineStr">
         <is>
-          <t>B-28</t>
+          <t>B-52</t>
         </is>
       </c>
       <c r="B49" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="D49" s="31" t="inlineStr">
         <is>
-          <t>Employees clicking the 'Medical HRMS' breadcrumb got 'Not permitted - No permission for Page'</t>
+          <t>Test Cases workbook showed '—' as the last automated run of the three new check scripts (TC-ERR-08, TC-ERR-09, TC-SEC-10) although they passed</t>
         </is>
       </c>
       <c r="E49" s="31" t="inlineStr">
         <is>
-          <t>Frappe chooses the breadcrumb workspace without a permission check</t>
+          <t>The workbook only read browser-test results</t>
         </is>
       </c>
       <c r="F49" s="31" t="inlineStr">
         <is>
-          <t>Keep only workspaces the user can open</t>
+          <t>Each check records its result (tests/checks/record.py); the builder shows it</t>
         </is>
       </c>
       <c r="G49" s="30" t="inlineStr">
         <is>
-          <t>HR-59</t>
+          <t>HR-72</t>
         </is>
       </c>
       <c r="H49" s="30" t="inlineStr">
@@ -10247,71 +10247,71 @@
       </c>
       <c r="I49" s="31" t="inlineStr">
         <is>
-          <t>E2E NAV-01/02</t>
+          <t>Test Cases workbook</t>
         </is>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="30" t="inlineStr">
         <is>
-          <t>B-25</t>
+          <t>B-53</t>
         </is>
       </c>
       <c r="B50" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="D50" s="31" t="inlineStr">
         <is>
-          <t>System e-mails fail: password cannot be decrypted</t>
+          <t>tests/checks/site.py used traceback without importing it (would have crashed when reporting an unexpected error)</t>
         </is>
       </c>
       <c r="E50" s="31" t="inlineStr">
         <is>
-          <t>Email Account 'Notifications' password encrypted with another key</t>
+          <t>Lost when two check scripts were combined</t>
         </is>
       </c>
       <c r="F50" s="31" t="inlineStr">
         <is>
-          <t>Re-enter the password on the server</t>
+          <t>Import added</t>
         </is>
       </c>
       <c r="G50" s="30" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-72</t>
         </is>
       </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I50" s="31" t="inlineStr">
         <is>
-          <t>Error Log</t>
+          <t>Found by tests/checks/files.py</t>
         </is>
       </c>
       <c r="J50" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="30" t="inlineStr">
         <is>
-          <t>B-26</t>
+          <t>B-28</t>
         </is>
       </c>
       <c r="B51" s="30" t="inlineStr">
@@ -10321,37 +10321,37 @@
       </c>
       <c r="C51" s="30" t="inlineStr">
         <is>
-          <t>Instructor (Education)</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="D51" s="31" t="inlineStr">
         <is>
-          <t>Linking an Employee in the Instructor form fails</t>
+          <t>Employees clicking the 'Medical HRMS' breadcrumb got 'Not permitted - No permission for Page'</t>
         </is>
       </c>
       <c r="E51" s="31" t="inlineStr">
         <is>
-          <t>fetch_from copies Ministry codes into Education lists</t>
+          <t>Frappe chooses the breadcrumb workspace without a permission check</t>
         </is>
       </c>
       <c r="F51" s="31" t="inlineStr">
         <is>
-          <t>Education team to change the fetch</t>
+          <t>Keep only workspaces the user can open</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-59</t>
         </is>
       </c>
       <c r="H51" s="30" t="inlineStr">
         <is>
-          <t>Open – other team</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I51" s="31" t="inlineStr">
         <is>
-          <t>Reproduced 21 Oct</t>
+          <t>E2E NAV-01/02</t>
         </is>
       </c>
       <c r="J51" s="30" t="inlineStr">
@@ -10363,58 +10363,162 @@
     <row r="52">
       <c r="A52" s="30" t="inlineStr">
         <is>
+          <t>B-25</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="inlineStr">
+        <is>
+          <t>System e-mails fail: password cannot be decrypted</t>
+        </is>
+      </c>
+      <c r="E52" s="31" t="inlineStr">
+        <is>
+          <t>Email Account 'Notifications' password encrypted with another key</t>
+        </is>
+      </c>
+      <c r="F52" s="31" t="inlineStr">
+        <is>
+          <t>Re-enter the password on the server</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>HR-47</t>
+        </is>
+      </c>
+      <c r="H52" s="30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I52" s="31" t="inlineStr">
+        <is>
+          <t>Error Log</t>
+        </is>
+      </c>
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>B-26</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>Instructor (Education)</t>
+        </is>
+      </c>
+      <c r="D53" s="31" t="inlineStr">
+        <is>
+          <t>Linking an Employee in the Instructor form fails</t>
+        </is>
+      </c>
+      <c r="E53" s="31" t="inlineStr">
+        <is>
+          <t>fetch_from copies Ministry codes into Education lists</t>
+        </is>
+      </c>
+      <c r="F53" s="31" t="inlineStr">
+        <is>
+          <t>Education team to change the fetch</t>
+        </is>
+      </c>
+      <c r="G53" s="30" t="inlineStr">
+        <is>
+          <t>HR-48</t>
+        </is>
+      </c>
+      <c r="H53" s="30" t="inlineStr">
+        <is>
+          <t>Open – other team</t>
+        </is>
+      </c>
+      <c r="I53" s="31" t="inlineStr">
+        <is>
+          <t>Reproduced 21 Oct</t>
+        </is>
+      </c>
+      <c r="J53" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
           <t>B-27</t>
         </is>
       </c>
-      <c r="B52" s="30" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C52" s="30" t="inlineStr">
+      <c r="B54" s="30" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="D52" s="31" t="inlineStr">
+      <c r="D54" s="31" t="inlineStr">
         <is>
           <t>Logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
-      <c r="E52" s="31" t="inlineStr">
+      <c r="E54" s="31" t="inlineStr">
         <is>
           <t>File not on this copy</t>
         </is>
       </c>
-      <c r="F52" s="31" t="inlineStr">
+      <c r="F54" s="31" t="inlineStr">
         <is>
           <t>Check on the live server</t>
         </is>
       </c>
-      <c r="G52" s="30" t="inlineStr">
+      <c r="G54" s="30" t="inlineStr">
         <is>
           <t>HR-54</t>
         </is>
       </c>
-      <c r="H52" s="30" t="inlineStr">
+      <c r="H54" s="30" t="inlineStr">
         <is>
           <t>Open – check server</t>
         </is>
       </c>
-      <c r="I52" s="31" t="inlineStr">
+      <c r="I54" s="31" t="inlineStr">
         <is>
           <t>Error sweep</t>
         </is>
       </c>
-      <c r="J52" s="30" t="inlineStr">
+      <c r="J54" s="30" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J52"/>
-  <conditionalFormatting sqref="A2:J152">
+  <autoFilter ref="A1:J54"/>
+  <conditionalFormatting sqref="A2:J154">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H2="Fixed"</formula>
     </cfRule>
@@ -10429,7 +10533,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Fixed,Open,Open – other team,Open – check server"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10986,7 +11090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11031,17 +11135,17 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D2" s="31" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E2" s="30" t="inlineStr">
@@ -11053,7 +11157,7 @@
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B3" s="30" t="inlineStr">
@@ -11063,12 +11167,12 @@
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D3" s="31" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E3" s="30" t="inlineStr">
@@ -11090,12 +11194,12 @@
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D4" s="31" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
@@ -11112,17 +11216,17 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D5" s="31" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E5" s="30" t="inlineStr">
@@ -11134,22 +11238,22 @@
     <row r="6">
       <c r="A6" s="30" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D6" s="31" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
@@ -11166,17 +11270,17 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C7" s="31" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D7" s="31" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E7" s="30" t="inlineStr">
@@ -11193,17 +11297,17 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
@@ -11215,7 +11319,7 @@
     <row r="9">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
@@ -11225,12 +11329,12 @@
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E9" s="30" t="inlineStr">
@@ -11242,7 +11346,7 @@
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
@@ -11252,12 +11356,12 @@
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D10" s="31" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
@@ -11269,32 +11373,59 @@
     <row r="11">
       <c r="A11" s="30" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$K$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$13</definedName>
@@ -805,7 +805,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>One place to see what has been done on Medical HRMS (HR system) and Jameah (Ministry of Education data), what is being done now, and what is still pending.</t>
+          <t>One place to see what has been done on Medical HRMS (HR system) and Jameah (the Ministry data system), what is being done now, and what is still pending.</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Every task: when it was done, status, owner, evidence and the next step. Filter on any column.</t>
+          <t>Every task: when it was done, status, owner (who leads it: Abdul Hakeem for all development), assigned to (who the task is given to), evidence and the next step. Filter on any column.</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2511,11 +2511,12 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2551,25 +2552,30 @@
       </c>
       <c r="G1" s="21" t="inlineStr">
         <is>
+          <t>Assigned to</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
         <is>
           <t>Done so far / evidence</t>
         </is>
       </c>
-      <c r="I1" s="21" t="inlineStr">
+      <c r="J1" s="21" t="inlineStr">
         <is>
           <t>Next step / pending</t>
         </is>
       </c>
-      <c r="J1" s="21" t="inlineStr">
+      <c r="K1" s="21" t="inlineStr">
         <is>
           <t>Reference (commit / file)</t>
         </is>
       </c>
-      <c r="K1" s="21" t="inlineStr">
+      <c r="L1" s="21" t="inlineStr">
         <is>
           <t>Last updated</t>
         </is>
@@ -2608,25 +2614,30 @@
       </c>
       <c r="G2" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H2" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="35" t="inlineStr">
+      <c r="I2" s="35" t="inlineStr">
         <is>
           <t>App, setup scripts and migration hooks exist. Migration re-run several times on 19–21 Oct without errors or duplicates; Ministry fields, permissions and Jameah views are created on every migrate.</t>
         </is>
       </c>
-      <c r="I2" s="35" t="inlineStr">
+      <c r="J2" s="35" t="inlineStr">
         <is>
           <t>Run the same migration once on the production server.</t>
         </is>
       </c>
-      <c r="J2" s="35" t="inlineStr">
+      <c r="K2" s="35" t="inlineStr">
         <is>
           <t>hooks.py; patches.txt</t>
         </is>
       </c>
-      <c r="K2" s="34" t="inlineStr">
+      <c r="L2" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -2665,25 +2676,30 @@
       </c>
       <c r="G3" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H3" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="35" t="inlineStr">
+      <c r="I3" s="35" t="inlineStr">
         <is>
           <t>9,867 Ministry codes loaded from the Arabic and Translated workbooks, every code with Arabic and English names (before: 8,330 showed the code as their name). Loaded automatically on migrate. Demo codes remapped and removed.</t>
         </is>
       </c>
-      <c r="I3" s="35" t="inlineStr">
+      <c r="J3" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J3" s="35" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>277442b; ministry_codes.py; data/ministry_codes.csv</t>
         </is>
       </c>
-      <c r="K3" s="34" t="inlineStr">
+      <c r="L3" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -2722,25 +2738,30 @@
       </c>
       <c r="G4" s="34" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H4" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H4" s="35" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>Branch, Agency, Deanery, College, Academic Department and Facility doctypes exist and are linked to Employee/Instructor.</t>
         </is>
       </c>
-      <c r="I4" s="35" t="inlineStr">
+      <c r="J4" s="35" t="inlineStr">
         <is>
           <t>HR to enter the real hierarchy and confirm employee placement.</t>
         </is>
       </c>
-      <c r="J4" s="35" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t>create_institute_doctypes.py; create_facility_doctype.py</t>
         </is>
       </c>
-      <c r="K4" s="34" t="inlineStr">
+      <c r="L4" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -2774,30 +2795,35 @@
       </c>
       <c r="F5" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
           <t>Fathir</t>
         </is>
       </c>
-      <c r="G5" s="34" t="inlineStr">
+      <c r="H5" s="34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
-        <is>
-          <t>Work started by Dinesh (commits 2–5 Oct); Fathir now handles Dinesh's work.</t>
-        </is>
-      </c>
       <c r="I5" s="35" t="inlineStr">
         <is>
-          <t>Fathir to confirm the scope done and what remains.</t>
+          <t>Assigned to Dinesh first (commits 2–5 Oct); now assigned to Fathir.</t>
         </is>
       </c>
       <c r="J5" s="35" t="inlineStr">
         <is>
+          <t>Fathir to report the scope done and what remains.</t>
+        </is>
+      </c>
+      <c r="K5" s="35" t="inlineStr">
+        <is>
           <t>HRM_TASK_TRACKER.md</t>
         </is>
       </c>
-      <c r="K5" s="34" t="inlineStr">
+      <c r="L5" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -2831,30 +2857,35 @@
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Fathir</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G6" s="34" t="inlineStr">
         <is>
+          <t>Fathir</t>
+        </is>
+      </c>
+      <c r="H6" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t>Ministry identity rules added (national ID 10 digits starting 1 for Saudis, Iqama 10 digits starting 2) and duplicates blocked (same identity number, home ID or job number). Mandatory Ministry fields enforced on save.</t>
         </is>
       </c>
-      <c r="I6" s="35" t="inlineStr">
-        <is>
-          <t>Fathir (taking over Dinesh's part) to confirm the remaining registration scope; complete the EMP-00001 demo record (HR-53).</t>
-        </is>
-      </c>
       <c r="J6" s="35" t="inlineStr">
         <is>
+          <t>Fathir (assigned) to confirm the remaining registration scope; complete the EMP-00001 demo record (HR-53).</t>
+        </is>
+      </c>
+      <c r="K6" s="35" t="inlineStr">
+        <is>
           <t>1f88c78; ministry_lookup_validation.py</t>
         </is>
       </c>
-      <c r="K6" s="34" t="inlineStr">
+      <c r="L6" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -2888,30 +2919,35 @@
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t>Dinesh + Abdul Hakeem</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G7" s="34" t="inlineStr">
         <is>
+          <t>Dinesh</t>
+        </is>
+      </c>
+      <c r="H7" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="35" t="inlineStr">
-        <is>
-          <t>Built by Dinesh with Abdul Hakeem; Fathir now maintains the application form's UI (HR-70). Public application form -&gt; Accept -&gt; Create Employee tested in the browser on 19, 20 and 21 Oct. Creates Employee, login, Instructor / Academic Advisor / HOD records by role. Lost fields fixed on 20 Oct (HR-44).</t>
-        </is>
-      </c>
       <c r="I7" s="35" t="inlineStr">
         <is>
+          <t>Designed and built by Abdul Hakeem, with parts assigned to Dinesh; the form's UI is now assigned to Fathir (HR-70). Public application form -&gt; Accept -&gt; Create Employee tested in the browser on 19, 20 and 21 Oct. Creates Employee, login, Instructor / Academic Advisor / HOD records by role. Lost fields fixed on 20 Oct (HR-44).</t>
+        </is>
+      </c>
+      <c r="J7" s="35" t="inlineStr">
+        <is>
           <t>HR to run one real hire on the test site.</t>
         </is>
       </c>
-      <c r="J7" s="35" t="inlineStr">
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t>job_application.py; 8390598</t>
         </is>
       </c>
-      <c r="K7" s="34" t="inlineStr">
+      <c r="L7" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -2950,25 +2986,30 @@
       </c>
       <c r="G8" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H8" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="35" t="inlineStr">
+      <c r="I8" s="35" t="inlineStr">
         <is>
           <t>Jameah child tables (qualifications, academic experience, previous experience, training, awards, publications) on Employee. 'Appreciation' fixed to use the Ministry grade list on 20 Oct. These feed the Jameah Employee views.</t>
         </is>
       </c>
-      <c r="I8" s="35" t="inlineStr">
+      <c r="J8" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J8" s="35" t="inlineStr">
+      <c r="K8" s="35" t="inlineStr">
         <is>
           <t>setup_employee_ministry_expected_fields.py; d690cb7</t>
         </is>
       </c>
-      <c r="K8" s="34" t="inlineStr">
+      <c r="L8" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3007,25 +3048,30 @@
       </c>
       <c r="G9" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H9" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="35" t="inlineStr">
+      <c r="I9" s="35" t="inlineStr">
         <is>
           <t>Every dashboard link opens without an error (browser test HRD-03, 21 Oct). Counts fixed on 19 Oct. Academic Presence and Jameah sections added. 22 Oct: Leave section - setup check per company, Sick Leave card, daily leave counts and the yearly setup steps in order (LV-06).</t>
         </is>
       </c>
-      <c r="I9" s="35" t="inlineStr">
+      <c r="J9" s="35" t="inlineStr">
         <is>
           <t>HR UAT.</t>
         </is>
       </c>
-      <c r="J9" s="35" t="inlineStr">
+      <c r="K9" s="35" t="inlineStr">
         <is>
           <t>page/hr_dashboard</t>
         </is>
       </c>
-      <c r="K9" s="34" t="inlineStr">
+      <c r="L9" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -3064,25 +3110,30 @@
       </c>
       <c r="G10" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H10" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="35" t="inlineStr">
+      <c r="I10" s="35" t="inlineStr">
         <is>
           <t>All request types, leave request, details view and counters tested in the browser (ESS-01..17). 22 Oct: 11 cards, the three leave cards first (Leave Plan, Leave Application, Leave Return), and a My Leave panel that says what to do next (LV-01..05).</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="J10" s="35" t="inlineStr">
         <is>
           <t>Employee UAT, including on a phone.</t>
         </is>
       </c>
-      <c r="J10" s="35" t="inlineStr">
+      <c r="K10" s="35" t="inlineStr">
         <is>
           <t>page/employee_dashboard</t>
         </is>
       </c>
-      <c r="K10" s="34" t="inlineStr">
+      <c r="L10" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -3121,25 +3172,30 @@
       </c>
       <c r="G11" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H11" s="35" t="inlineStr">
+      <c r="I11" s="35" t="inlineStr">
         <is>
           <t>Workspace renders (browser test HRD-04).</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="J11" s="35" t="inlineStr">
         <is>
           <t>Check long labels and mobile layout during UAT.</t>
         </is>
       </c>
-      <c r="J11" s="35" t="inlineStr">
+      <c r="K11" s="35" t="inlineStr">
         <is>
           <t>public/css/workspace_theme.css</t>
         </is>
       </c>
-      <c r="K11" s="34" t="inlineStr">
+      <c r="L11" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3178,25 +3234,30 @@
       </c>
       <c r="G12" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H12" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="I12" s="35" t="inlineStr">
         <is>
           <t>Not started. Instructors with an Employee record can already use /app/employee-dashboard.</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
-        <is>
-          <t>Add the request and leave cards to the Instructor / HOD dashboards from Medical HRMS (page scripts in this app; the Education app itself is not changed).</t>
-        </is>
-      </c>
       <c r="J12" s="35" t="inlineStr">
         <is>
+          <t>Add the request and leave cards to the Instructor / HOD dashboards from Medical HRMS (page scripts in this app).</t>
+        </is>
+      </c>
+      <c r="K12" s="35" t="inlineStr">
+        <is>
           <t>HRM_TASK_TRACKER.md</t>
         </is>
       </c>
-      <c r="K12" s="34" t="inlineStr">
+      <c r="L12" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -3235,27 +3296,32 @@
       </c>
       <c r="G13" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="35" t="inlineStr">
-        <is>
-          <t>HR Manager / HR User now land on the HR Dashboard after login, employees on the Employee Dashboard; users with an Education dashboard keep it (fix 21 Oct, browser-tested).</t>
-        </is>
-      </c>
       <c r="I13" s="35" t="inlineStr">
         <is>
+          <t>HR Manager / HR User now land on the HR Dashboard after login, employees on the Employee Dashboard; users with their own portal (Instructor, Student ...) keep it (fix 21 Oct, browser-tested).</t>
+        </is>
+      </c>
+      <c r="J13" s="35" t="inlineStr">
+        <is>
           <t>Deploy (HR-58).</t>
         </is>
       </c>
-      <c r="J13" s="35" t="inlineStr">
+      <c r="K13" s="35" t="inlineStr">
         <is>
           <t>1ee80cd; login_redirect.py</t>
         </is>
       </c>
-      <c r="K13" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
+      <c r="L13" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3292,25 +3358,30 @@
       </c>
       <c r="G14" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H14" s="35" t="inlineStr">
+      <c r="I14" s="35" t="inlineStr">
         <is>
           <t>12 security tests pass (SEC-01..12): employees see only their own requests, records, licences and files; cannot approve, spoof or file HR-only requests.</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="J14" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J14" s="35" t="inlineStr">
+      <c r="K14" s="35" t="inlineStr">
         <is>
           <t>employee_permissions.py; self_service.py</t>
         </is>
       </c>
-      <c r="K14" s="34" t="inlineStr">
+      <c r="L14" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3349,25 +3420,30 @@
       </c>
       <c r="G15" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H15" s="35" t="inlineStr">
+      <c r="I15" s="35" t="inlineStr">
         <is>
           <t>Each form's required fields, private attachment upload and sending tested in the browser.</t>
         </is>
       </c>
-      <c r="I15" s="35" t="inlineStr">
+      <c r="J15" s="35" t="inlineStr">
         <is>
           <t>HR UAT of the wording on each form.</t>
         </is>
       </c>
-      <c r="J15" s="35" t="inlineStr">
+      <c r="K15" s="35" t="inlineStr">
         <is>
           <t>self_service.py</t>
         </is>
       </c>
-      <c r="K15" s="34" t="inlineStr">
+      <c r="L15" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3406,25 +3482,30 @@
       </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H16" s="35" t="inlineStr">
+      <c r="I16" s="35" t="inlineStr">
         <is>
           <t>Hour/minute/AM-PM picker saves correct times (10:15–11:45 test); incomplete time refused; details dialog shows saved values.</t>
         </is>
       </c>
-      <c r="I16" s="35" t="inlineStr">
+      <c r="J16" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J16" s="35" t="inlineStr">
+      <c r="K16" s="35" t="inlineStr">
         <is>
           <t>employee_dashboard.js</t>
         </is>
       </c>
-      <c r="K16" s="34" t="inlineStr">
+      <c r="L16" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3463,25 +3544,30 @@
       </c>
       <c r="G17" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="35" t="inlineStr">
+      <c r="I17" s="35" t="inlineStr">
         <is>
           <t>Drafts can be saved; employees cannot edit sent requests.</t>
         </is>
       </c>
-      <c r="I17" s="35" t="inlineStr">
+      <c r="J17" s="35" t="inlineStr">
         <is>
           <t>Let employees open their draft and send it; allow resubmitting a rejected request as a new one with history.</t>
         </is>
       </c>
-      <c r="J17" s="35" t="inlineStr">
+      <c r="K17" s="35" t="inlineStr">
         <is>
           <t>HRM_UAT_SCENARIOS.md #3</t>
         </is>
       </c>
-      <c r="K17" s="34" t="inlineStr">
+      <c r="L17" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3520,25 +3606,30 @@
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="35" t="inlineStr">
+      <c r="I18" s="35" t="inlineStr">
         <is>
           <t>Request form and HR status steps exist.</t>
         </is>
       </c>
-      <c r="I18" s="35" t="inlineStr">
+      <c r="J18" s="35" t="inlineStr">
         <is>
           <t>HR to confirm the steps; apply the approved change to the Employee record with an audit trail.</t>
         </is>
       </c>
-      <c r="J18" s="35" t="inlineStr">
+      <c r="K18" s="35" t="inlineStr">
         <is>
           <t>Employee Data Update Request</t>
         </is>
       </c>
-      <c r="K18" s="34" t="inlineStr">
+      <c r="L18" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3577,25 +3668,30 @@
       </c>
       <c r="G19" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="I19" s="35" t="inlineStr">
         <is>
           <t>Migration creates editable starter records and draft policies; 6 unit tests pass.</t>
         </is>
       </c>
-      <c r="I19" s="35" t="inlineStr">
+      <c r="J19" s="35" t="inlineStr">
         <is>
           <t>HR to confirm final policies.</t>
         </is>
       </c>
-      <c r="J19" s="35" t="inlineStr">
+      <c r="K19" s="35" t="inlineStr">
         <is>
           <t>setup_leave_defaults.py</t>
         </is>
       </c>
-      <c r="K19" s="34" t="inlineStr">
+      <c r="L19" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3634,25 +3730,30 @@
       </c>
       <c r="G20" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H20" s="35" t="inlineStr">
+      <c r="I20" s="35" t="inlineStr">
         <is>
           <t>Full leave flow tested in the browser: request -&gt; approver approves and submits -&gt; balance 21 -&gt; 19. 22 Oct: the HR Portal setup check shows, per company, a missing leave period, holiday list, leave approvers or annual leave.</t>
         </is>
       </c>
-      <c r="I20" s="35" t="inlineStr">
+      <c r="J20" s="35" t="inlineStr">
         <is>
           <t>Set real policies and allocations for the real company (HR-69).</t>
         </is>
       </c>
-      <c r="J20" s="35" t="inlineStr">
+      <c r="K20" s="35" t="inlineStr">
         <is>
           <t>setup_local_leave_demo.py; hr_dashboard.get_leave_overview</t>
         </is>
       </c>
-      <c r="K20" s="34" t="inlineStr">
+      <c r="L20" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -3691,25 +3792,30 @@
       </c>
       <c r="G21" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H21" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H21" s="35" t="inlineStr">
+      <c r="I21" s="35" t="inlineStr">
         <is>
           <t>6 unit tests pass (stages, overlaps, caps). 22 Oct: the stages are named in pay order - Sick Leave 1 - Full Pay (30 days), 2 - 75% Pay (60), 3 - Unpaid (30) - by a migration patch that keeps balances and history; every screen and message says 'Sick Leave'; HR button 'Start Sick Leave Year'.</t>
         </is>
       </c>
-      <c r="I21" s="35" t="inlineStr">
+      <c r="J21" s="35" t="inlineStr">
         <is>
           <t>HR to review stage rules; Finance to review payroll effect.</t>
         </is>
       </c>
-      <c r="J21" s="35" t="inlineStr">
+      <c r="K21" s="35" t="inlineStr">
         <is>
           <t>medical_leave.py</t>
         </is>
       </c>
-      <c r="K21" s="34" t="inlineStr">
+      <c r="L21" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -3748,25 +3854,30 @@
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H22" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="35" t="inlineStr">
+      <c r="I22" s="35" t="inlineStr">
         <is>
           <t>6 unit tests pass. Remote-work limit is currently switched off in HR Settings.</t>
         </is>
       </c>
-      <c r="I22" s="35" t="inlineStr">
+      <c r="J22" s="35" t="inlineStr">
         <is>
           <t>HR to confirm limits and switch them on.</t>
         </is>
       </c>
-      <c r="J22" s="35" t="inlineStr">
+      <c r="K22" s="35" t="inlineStr">
         <is>
           <t>monthly_leave_policy.py</t>
         </is>
       </c>
-      <c r="K22" s="34" t="inlineStr">
+      <c r="L22" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -3805,25 +3916,30 @@
       </c>
       <c r="G23" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H23" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="35" t="inlineStr">
+      <c r="I23" s="35" t="inlineStr">
         <is>
           <t>Balance updates after approval (browser test APR-05). 22 Oct: the balances table shows Allocated / Taken / Waiting for approval / Left, and this month's half-day and work-from-home use.</t>
         </is>
       </c>
-      <c r="I23" s="35" t="inlineStr">
+      <c r="J23" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J23" s="35" t="inlineStr">
+      <c r="K23" s="35" t="inlineStr">
         <is>
           <t>employee_dashboard.py</t>
         </is>
       </c>
-      <c r="K23" s="34" t="inlineStr">
+      <c r="L23" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -3862,25 +3978,30 @@
       </c>
       <c r="G24" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H24" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H24" s="35" t="inlineStr">
+      <c r="I24" s="35" t="inlineStr">
         <is>
           <t>The client found the leave part confusing (22 Oct). Now one flow, in this order on the Employee Portal and in the HR menu: (1) Leave Plan - the employee plans dates; manager then department head approve; no balance is used. (2) Leave Application - only leave the employee holds, with the days left ('Annual Leave (21 days left)'), unpaid leave last; 'Apply now' on an approved plan opens it pre-filled and links the application to the plan. (3) Leave Return - the dashboard asks for it once a leave has ended; Expected Back On = the day after the leave; fitness certificate and occupational health only after sick leave; one return per leave, approved leave only. Unused sample types (Casual, Privilege, Compensatory Off, HRMS Sick Leave) hidden from employees. 5 unit tests; browser tests LV-01..07.</t>
         </is>
       </c>
-      <c r="I24" s="35" t="inlineStr">
+      <c r="J24" s="35" t="inlineStr">
         <is>
           <t>Employee and HR UAT of the leave flow (TC-LV-09..17).</t>
         </is>
       </c>
-      <c r="J24" s="35" t="inlineStr">
+      <c r="K24" s="35" t="inlineStr">
         <is>
           <t>self_service.py; leave_plan_request; leave_return_request; page/employee_dashboard; page/hr_dashboard</t>
         </is>
       </c>
-      <c r="K24" s="34" t="inlineStr">
+      <c r="L24" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -3919,25 +4040,30 @@
       </c>
       <c r="G25" s="34" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H25" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H25" s="35" t="inlineStr">
+      <c r="I25" s="35" t="inlineStr">
         <is>
           <t>Found 22 Oct by the new setup check on the development copy: no active leave period and no holiday list for Al Riyada College. (Correction 23 Oct: the '3 of 4 employees without a leave approver / annual leave' counted QA test hires; this copy has no real Al Riyada College staff, so the employee checks must be read on the live server.) Until the setup is done its employees have no leave to apply for.</t>
         </is>
       </c>
-      <c r="I25" s="35" t="inlineStr">
+      <c r="J25" s="35" t="inlineStr">
         <is>
           <t>On the live server: HR Portal &gt; Leave &gt; Yearly setup, steps 1-6, until the Leave setup check is green (Checklist CL-28 - CL-32).</t>
         </is>
       </c>
-      <c r="J25" s="35" t="inlineStr">
+      <c r="K25" s="35" t="inlineStr">
         <is>
           <t>HR Portal &gt; Leave setup check</t>
         </is>
       </c>
-      <c r="K25" s="34" t="inlineStr">
+      <c r="L25" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -3976,25 +4102,30 @@
       </c>
       <c r="G26" s="34" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H26" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="35" t="inlineStr">
+      <c r="I26" s="35" t="inlineStr">
         <is>
           <t>Demo weekend calendar only.</t>
         </is>
       </c>
-      <c r="I26" s="35" t="inlineStr">
+      <c r="J26" s="35" t="inlineStr">
         <is>
           <t>HR to give official holidays and carry-forward rules; set the Academic Holiday List in HR Settings.</t>
         </is>
       </c>
-      <c r="J26" s="35" t="inlineStr">
+      <c r="K26" s="35" t="inlineStr">
         <is>
           <t>HR Settings</t>
         </is>
       </c>
-      <c r="K26" s="34" t="inlineStr">
+      <c r="L26" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4033,25 +4164,30 @@
       </c>
       <c r="G27" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H27" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="35" t="inlineStr">
+      <c r="I27" s="35" t="inlineStr">
         <is>
           <t>Finance roles fixed on 19 Oct (Finance Manager or Accounts Manager accepted). HR approve/reject/issue tested.</t>
         </is>
       </c>
-      <c r="I27" s="35" t="inlineStr">
+      <c r="J27" s="35" t="inlineStr">
         <is>
           <t>Agree the approver per step with HR and Finance; build the workflow; label amounts in SAR (some messages say AED).</t>
         </is>
       </c>
-      <c r="J27" s="35" t="inlineStr">
+      <c r="K27" s="35" t="inlineStr">
         <is>
           <t>overrides/; HRM_APPROVAL_MATRIX.md</t>
         </is>
       </c>
-      <c r="K27" s="34" t="inlineStr">
+      <c r="L27" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4090,25 +4226,30 @@
       </c>
       <c r="G28" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H28" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="35" t="inlineStr">
+      <c r="I28" s="35" t="inlineStr">
         <is>
           <t>Changes are tracked (track_changes). E-mail sending fails on this copy (HR-47).</t>
         </is>
       </c>
-      <c r="I28" s="35" t="inlineStr">
+      <c r="J28" s="35" t="inlineStr">
         <is>
           <t>Add rejection reason; send submit/approve/reject e-mails once the mail account works.</t>
         </is>
       </c>
-      <c r="J28" s="35" t="inlineStr">
+      <c r="K28" s="35" t="inlineStr">
         <is>
           <t>HRM_UAT_SCENARIOS.md</t>
         </is>
       </c>
-      <c r="K28" s="34" t="inlineStr">
+      <c r="L28" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4147,25 +4288,30 @@
       </c>
       <c r="G29" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="35" t="inlineStr">
+      <c r="I29" s="35" t="inlineStr">
         <is>
           <t>Licence creation and own-licence visibility tested (LIC-01/02). Contract renewal is HR-only.</t>
         </is>
       </c>
-      <c r="I29" s="35" t="inlineStr">
+      <c r="J29" s="35" t="inlineStr">
         <is>
           <t>UAT of expiry reminders and separation.</t>
         </is>
       </c>
-      <c r="J29" s="35" t="inlineStr">
+      <c r="K29" s="35" t="inlineStr">
         <is>
           <t>Employee Medical License</t>
         </is>
       </c>
-      <c r="K29" s="34" t="inlineStr">
+      <c r="L29" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4204,25 +4350,30 @@
       </c>
       <c r="G30" s="34" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H30" s="35" t="inlineStr">
+      <c r="I30" s="35" t="inlineStr">
         <is>
           <t>Linking tool and HR data sheet done (19 Oct). Only 1 of 216 instructors is linked to an Employee.</t>
         </is>
       </c>
-      <c r="I30" s="35" t="inlineStr">
+      <c r="J30" s="35" t="inlineStr">
         <is>
           <t>HR fills the Instructor data sheet, then run the import (HR-55).</t>
         </is>
       </c>
-      <c r="J30" s="35" t="inlineStr">
+      <c r="K30" s="35" t="inlineStr">
         <is>
           <t>link_existing_instructors.py; instructor_data_sheet.py</t>
         </is>
       </c>
-      <c r="K30" s="34" t="inlineStr">
+      <c r="L30" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4261,25 +4412,30 @@
       </c>
       <c r="G31" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H31" s="34" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="35" t="inlineStr">
+      <c r="I31" s="35" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="I31" s="35" t="inlineStr">
+      <c r="J31" s="35" t="inlineStr">
         <is>
           <t>Decide which record (Employee or Instructor) owns each field, then build the sync in Medical HRMS.</t>
         </is>
       </c>
-      <c r="J31" s="35" t="inlineStr">
+      <c r="K31" s="35" t="inlineStr">
         <is>
           <t>JAMEAH_HRMS_IMPLEMENTATION_PLAN.md</t>
         </is>
       </c>
-      <c r="K31" s="34" t="inlineStr">
+      <c r="L31" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -4318,25 +4474,30 @@
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H32" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="35" t="inlineStr">
+      <c r="I32" s="35" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="I32" s="35" t="inlineStr">
+      <c r="J32" s="35" t="inlineStr">
         <is>
           <t>Define the handoff with Finance.</t>
         </is>
       </c>
-      <c r="J32" s="35" t="inlineStr">
+      <c r="K32" s="35" t="inlineStr">
         <is>
           <t>HRM and Finance Module Integration Roadmap.html</t>
         </is>
       </c>
-      <c r="K32" s="34" t="inlineStr">
+      <c r="L32" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -4375,25 +4536,30 @@
       </c>
       <c r="G33" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H33" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="35" t="inlineStr">
+      <c r="I33" s="35" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="I33" s="35" t="inlineStr">
+      <c r="J33" s="35" t="inlineStr">
         <is>
           <t>Validate salary slips and partial-pay leave with Finance.</t>
         </is>
       </c>
-      <c r="J33" s="35" t="inlineStr">
+      <c r="K33" s="35" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="K33" s="34" t="inlineStr">
+      <c r="L33" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -4432,25 +4598,30 @@
       </c>
       <c r="G34" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H34" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H34" s="35" t="inlineStr">
+      <c r="I34" s="35" t="inlineStr">
         <is>
           <t>Browser end-to-end rounds on 19, 20 and 21 Oct (latest: see Test Report). 26 unit tests pass. Jameah views verified value by value.</t>
         </is>
       </c>
-      <c r="I34" s="35" t="inlineStr">
+      <c r="J34" s="35" t="inlineStr">
         <is>
           <t>Client UAT with the Test Cases workbook.</t>
         </is>
       </c>
-      <c r="J34" s="35" t="inlineStr">
+      <c r="K34" s="35" t="inlineStr">
         <is>
           <t>Test Report; Test Cases workbook</t>
         </is>
       </c>
-      <c r="K34" s="34" t="inlineStr">
+      <c r="L34" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4489,25 +4660,30 @@
       </c>
       <c r="G35" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H35" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="35" t="inlineStr">
+      <c r="I35" s="35" t="inlineStr">
         <is>
           <t>This tracker, the test cases workbook, the test report, Jameah README and VIEWS mapping.</t>
         </is>
       </c>
-      <c r="I35" s="35" t="inlineStr">
+      <c r="J35" s="35" t="inlineStr">
         <is>
           <t>HR / Finance sign-off after UAT.</t>
         </is>
       </c>
-      <c r="J35" s="35" t="inlineStr">
+      <c r="K35" s="35" t="inlineStr">
         <is>
           <t>docs/</t>
         </is>
       </c>
-      <c r="K35" s="34" t="inlineStr">
+      <c r="L35" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4546,25 +4722,30 @@
       </c>
       <c r="G36" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H36" s="34" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H36" s="35" t="inlineStr">
+      <c r="I36" s="35" t="inlineStr">
         <is>
           <t>A guest could get System Manager through the public form. Fixed with an allow-list of hireable roles, checked again before conversion.</t>
         </is>
       </c>
-      <c r="I36" s="35" t="inlineStr">
+      <c r="J36" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J36" s="35" t="inlineStr">
+      <c r="K36" s="35" t="inlineStr">
         <is>
           <t>0ab539e</t>
         </is>
       </c>
-      <c r="K36" s="34" t="inlineStr">
+      <c r="L36" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4603,25 +4784,30 @@
       </c>
       <c r="G37" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H37" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="35" t="inlineStr">
+      <c r="I37" s="35" t="inlineStr">
         <is>
           <t>Instructor, Academic Advisor (+ Instructor) and Head of Department records created and linked; every hire gets the Employee role.</t>
         </is>
       </c>
-      <c r="I37" s="35" t="inlineStr">
+      <c r="J37" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J37" s="35" t="inlineStr">
+      <c r="K37" s="35" t="inlineStr">
         <is>
           <t>8390598</t>
         </is>
       </c>
-      <c r="K37" s="34" t="inlineStr">
+      <c r="L37" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4660,25 +4846,30 @@
       </c>
       <c r="G38" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H38" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H38" s="35" t="inlineStr">
+      <c r="I38" s="35" t="inlineStr">
         <is>
           <t>Dated bilingual export/import sheet with checks and a colour-coded result file.</t>
         </is>
       </c>
-      <c r="I38" s="35" t="inlineStr">
+      <c r="J38" s="35" t="inlineStr">
         <is>
           <t>HR to fill it (HR-55).</t>
         </is>
       </c>
-      <c r="J38" s="35" t="inlineStr">
+      <c r="K38" s="35" t="inlineStr">
         <is>
           <t>02f978e; instructor_data_sheet.py</t>
         </is>
       </c>
-      <c r="K38" s="34" t="inlineStr">
+      <c r="L38" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4717,25 +4908,30 @@
       </c>
       <c r="G39" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H39" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H39" s="35" t="inlineStr">
+      <c r="I39" s="35" t="inlineStr">
         <is>
           <t>Every teaching session per faculty member, room and mode; faculty filter; CSV export. Tested: 390 sessions, 58 faculty for 6–12 Sep 2026.</t>
         </is>
       </c>
-      <c r="I39" s="35" t="inlineStr">
+      <c r="J39" s="35" t="inlineStr">
         <is>
           <t>HR UAT.</t>
         </is>
       </c>
-      <c r="J39" s="35" t="inlineStr">
+      <c r="K39" s="35" t="inlineStr">
         <is>
           <t>0578d3d; page/hr_academic_presence</t>
         </is>
       </c>
-      <c r="K39" s="34" t="inlineStr">
+      <c r="L39" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4774,25 +4970,30 @@
       </c>
       <c r="G40" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H40" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H40" s="35" t="inlineStr">
+      <c r="I40" s="35" t="inlineStr">
         <is>
           <t>Exam Committee proctor assignments by date, time and room.</t>
         </is>
       </c>
-      <c r="I40" s="35" t="inlineStr">
+      <c r="J40" s="35" t="inlineStr">
         <is>
           <t>Needs real exam committees in the system to show data.</t>
         </is>
       </c>
-      <c r="J40" s="35" t="inlineStr">
+      <c r="K40" s="35" t="inlineStr">
         <is>
           <t>0578d3d</t>
         </is>
       </c>
-      <c r="K40" s="34" t="inlineStr">
+      <c r="L40" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4831,25 +5032,30 @@
       </c>
       <c r="G41" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H41" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H41" s="35" t="inlineStr">
+      <c r="I41" s="35" t="inlineStr">
         <is>
           <t>Hourly expected / present / absent. Tested: 8 Sep 2026 = 858 expected, 397 present (matches attendance).</t>
         </is>
       </c>
-      <c r="I41" s="35" t="inlineStr">
+      <c r="J41" s="35" t="inlineStr">
         <is>
           <t>HR UAT.</t>
         </is>
       </c>
-      <c r="J41" s="35" t="inlineStr">
+      <c r="K41" s="35" t="inlineStr">
         <is>
           <t>0578d3d</t>
         </is>
       </c>
-      <c r="K41" s="34" t="inlineStr">
+      <c r="L41" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4888,25 +5094,30 @@
       </c>
       <c r="G42" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H42" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H42" s="35" t="inlineStr">
+      <c r="I42" s="35" t="inlineStr">
         <is>
           <t>Daily list with evidence (device / class attendance / timetable); cut-off configurable in HR Settings. Tested: 27 people, 47 person-days in the test week.</t>
         </is>
       </c>
-      <c r="I42" s="35" t="inlineStr">
+      <c r="J42" s="35" t="inlineStr">
         <is>
           <t>Connect attendance devices for exact times (HR-56).</t>
         </is>
       </c>
-      <c r="J42" s="35" t="inlineStr">
+      <c r="K42" s="35" t="inlineStr">
         <is>
           <t>bfac883</t>
         </is>
       </c>
-      <c r="K42" s="34" t="inlineStr">
+      <c r="L42" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -4945,25 +5156,30 @@
       </c>
       <c r="G43" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H43" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="35" t="inlineStr">
+      <c r="I43" s="35" t="inlineStr">
         <is>
           <t>68 browser tests, 8 real bugs found and fixed (see Bugs sheet B-13..B-21).</t>
         </is>
       </c>
-      <c r="I43" s="35" t="inlineStr">
+      <c r="J43" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J43" s="35" t="inlineStr">
+      <c r="K43" s="35" t="inlineStr">
         <is>
           <t>7f0c5fc</t>
         </is>
       </c>
-      <c r="K43" s="34" t="inlineStr">
+      <c r="L43" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5002,25 +5218,30 @@
       </c>
       <c r="G44" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H44" s="34" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H44" s="35" t="inlineStr">
+      <c r="I44" s="35" t="inlineStr">
         <is>
           <t>'Could not find Gender: Gender::1' on every save of an employee with a login. Fixed in the Employee controller.</t>
         </is>
       </c>
-      <c r="I44" s="35" t="inlineStr">
+      <c r="J44" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J44" s="35" t="inlineStr">
+      <c r="K44" s="35" t="inlineStr">
         <is>
           <t>7f0c5fc; overrides/employee.py</t>
         </is>
       </c>
-      <c r="K44" s="34" t="inlineStr">
+      <c r="L44" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5059,25 +5280,30 @@
       </c>
       <c r="G45" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H45" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="35" t="inlineStr">
+      <c r="I45" s="35" t="inlineStr">
         <is>
           <t>Frappe rejects queries on a doctype named with ' from '. Renamed 'Return from Leave Request' -&gt; 'Leave Return Request' (migration patch moves the data).</t>
         </is>
       </c>
-      <c r="I45" s="35" t="inlineStr">
+      <c r="J45" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J45" s="35" t="inlineStr">
+      <c r="K45" s="35" t="inlineStr">
         <is>
           <t>7f0c5fc; patches/rename_return_from_leave_request.py</t>
         </is>
       </c>
-      <c r="K45" s="34" t="inlineStr">
+      <c r="L45" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5116,25 +5342,30 @@
       </c>
       <c r="G46" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H46" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H46" s="35" t="inlineStr">
+      <c r="I46" s="35" t="inlineStr">
         <is>
           <t>HR read access to Company, Instructor, Department Edu; select-only Role; Travel Request. Applied on migrate.</t>
         </is>
       </c>
-      <c r="I46" s="35" t="inlineStr">
+      <c r="J46" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J46" s="35" t="inlineStr">
+      <c r="K46" s="35" t="inlineStr">
         <is>
           <t>hr_core_permissions.py</t>
         </is>
       </c>
-      <c r="K46" s="34" t="inlineStr">
+      <c r="L46" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5173,25 +5404,30 @@
       </c>
       <c r="G47" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H47" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="35" t="inlineStr">
+      <c r="I47" s="35" t="inlineStr">
         <is>
           <t>Work phone, extension, application category, expected salary, ID/passport and resume were dropped. Fields added to Employee.</t>
         </is>
       </c>
-      <c r="I47" s="35" t="inlineStr">
+      <c r="J47" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J47" s="35" t="inlineStr">
+      <c r="K47" s="35" t="inlineStr">
         <is>
           <t>d690cb7</t>
         </is>
       </c>
-      <c r="K47" s="34" t="inlineStr">
+      <c r="L47" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5230,27 +5466,32 @@
       </c>
       <c r="G48" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H48" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H48" s="35" t="inlineStr">
-        <is>
-          <t>Education's master branch has no HR roles in its landing list, so HR stayed on /app. Fixed from medical_hrms; browser-tested.</t>
-        </is>
-      </c>
       <c r="I48" s="35" t="inlineStr">
         <is>
+          <t>The education app's master branch has no HR roles in its landing list, so HR stayed on /app. Fixed from medical_hrms; browser-tested.</t>
+        </is>
+      </c>
+      <c r="J48" s="35" t="inlineStr">
+        <is>
           <t>Deploy (HR-58).</t>
         </is>
       </c>
-      <c r="J48" s="35" t="inlineStr">
+      <c r="K48" s="35" t="inlineStr">
         <is>
           <t>1ee80cd</t>
         </is>
       </c>
-      <c r="K48" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
+      <c r="L48" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -5287,25 +5528,30 @@
       </c>
       <c r="G49" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H49" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H49" s="35" t="inlineStr">
+      <c r="I49" s="35" t="inlineStr">
         <is>
           <t>Found by the 21 Oct error sweep: the top-bar breadcrumb on the Employee Dashboard and lists pointed employees to the HR-only workspace; one click showed 'Not permitted - No permission for Page'. Breadcrumbs now only point to workspaces the user can open (employees get 'Employee Self Service').</t>
         </is>
       </c>
-      <c r="I49" s="35" t="inlineStr">
+      <c r="J49" s="35" t="inlineStr">
         <is>
           <t>Deploy (HR-58). Likely one source of the error the client reported.</t>
         </is>
       </c>
-      <c r="J49" s="35" t="inlineStr">
+      <c r="K49" s="35" t="inlineStr">
         <is>
           <t>workspace_access.py</t>
         </is>
       </c>
-      <c r="K49" s="34" t="inlineStr">
+      <c r="L49" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5344,25 +5590,30 @@
       </c>
       <c r="G50" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H50" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H50" s="35" t="inlineStr">
+      <c r="I50" s="35" t="inlineStr">
         <is>
           <t>Found by the 21 Oct error sweep: a new Expense Claim fills in the default cost center, which HR could not select. HR User and HR Manager now get select-only access to Cost Center and Project (as employees already have). Applied on migrate.</t>
         </is>
       </c>
-      <c r="I50" s="35" t="inlineStr">
+      <c r="J50" s="35" t="inlineStr">
         <is>
           <t>Deploy (HR-58). Likely one source of the error the client reported.</t>
         </is>
       </c>
-      <c r="J50" s="35" t="inlineStr">
+      <c r="K50" s="35" t="inlineStr">
         <is>
           <t>hr_core_permissions.py</t>
         </is>
       </c>
-      <c r="K50" s="34" t="inlineStr">
+      <c r="L50" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5401,27 +5652,32 @@
       </c>
       <c r="G51" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H51" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="35" t="inlineStr">
-        <is>
-          <t>Education's master branch now requires Instructor e-mails ending in @alriyada.edu.sa. Converting an Instructor/Academic Advisor applicant with a personal e-mail created the Employee and then showed an orange 'Instructor record not created' warning. Now refused up front with 'College E-mail Needed' before anything is created; the Create Employee dialog says which address to use.</t>
-        </is>
-      </c>
       <c r="I51" s="35" t="inlineStr">
         <is>
+          <t>The education app's master branch now requires Instructor e-mails ending in @alriyada.edu.sa. Converting an Instructor/Academic Advisor applicant with a personal e-mail created the Employee and then showed an orange 'Instructor record not created' warning. Now refused up front with 'College E-mail Needed' before anything is created; the Create Employee dialog says which address to use.</t>
+        </is>
+      </c>
+      <c r="J51" s="35" t="inlineStr">
+        <is>
           <t>Deploy (HR-58). HR must enter the official college e-mail as Company Email for academic hires.</t>
         </is>
       </c>
-      <c r="J51" s="35" t="inlineStr">
+      <c r="K51" s="35" t="inlineStr">
         <is>
           <t>job_application.py; employee_job_applicant.js</t>
         </is>
       </c>
-      <c r="K51" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
+      <c r="L51" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -5458,25 +5714,30 @@
       </c>
       <c r="G52" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H52" s="34" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H52" s="35" t="inlineStr">
+      <c r="I52" s="35" t="inlineStr">
         <is>
           <t>Found 21 Oct: the 19 Oct identity fix (HR-05, bug B-11) changed the server rule (Iqama mandatory for residents, home-country ID optional) but the Employee form script still had the old rule. Opening a non-Saudi employee hid and cleared the Iqama number and demanded the home-country ID, so HR could not save the record at all. Form now matches the Ministry rule; browser-tested with an Iqama holder.</t>
         </is>
       </c>
-      <c r="I52" s="35" t="inlineStr">
+      <c r="J52" s="35" t="inlineStr">
         <is>
           <t>Deploy (HR-58). Very likely one source of the error the client reported (any HR user opening a non-Saudi employee).</t>
         </is>
       </c>
-      <c r="J52" s="35" t="inlineStr">
+      <c r="K52" s="35" t="inlineStr">
         <is>
           <t>employee_ministry_lookup.js</t>
         </is>
       </c>
-      <c r="K52" s="34" t="inlineStr">
+      <c r="L52" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5515,25 +5776,30 @@
       </c>
       <c r="G53" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H53" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H53" s="35" t="inlineStr">
+      <c r="I53" s="35" t="inlineStr">
         <is>
           <t>The public form lets an applicant pick a special-needs type with 'Has special needs = No' and a Saudi enter a home-country ID. Those values were copied to the Employee; the form then cleared them on opening (record marked 'Not Saved', 'Leave site?' prompt) and the Ministry view would have sent a special-needs code for someone without special needs. The server now drops values that do not apply on every save; the views only send a special-needs type when the flag is set.</t>
         </is>
       </c>
-      <c r="I53" s="35" t="inlineStr">
+      <c r="J53" s="35" t="inlineStr">
         <is>
           <t>Deploy (HR-58).</t>
         </is>
       </c>
-      <c r="J53" s="35" t="inlineStr">
+      <c r="K53" s="35" t="inlineStr">
         <is>
           <t>ministry_lookup_validation.py; jameah/views.py</t>
         </is>
       </c>
-      <c r="K53" s="34" t="inlineStr">
+      <c r="L53" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5572,25 +5838,30 @@
       </c>
       <c r="G54" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H54" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H54" s="35" t="inlineStr">
+      <c r="I54" s="35" t="inlineStr">
         <is>
           <t>New hires could not be saved again ('Missing Fields': Department, Work Location). The dialog now asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application) and Gender / Date of Birth when the applicant left them empty. Browser-tested: the new Employee saves straight away (REC-10).</t>
         </is>
       </c>
-      <c r="I54" s="35" t="inlineStr">
+      <c r="J54" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J54" s="35" t="inlineStr">
+      <c r="K54" s="35" t="inlineStr">
         <is>
           <t>employee_job_applicant.js; job_application.py</t>
         </is>
       </c>
-      <c r="K54" s="34" t="inlineStr">
+      <c r="L54" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -5629,25 +5900,30 @@
       </c>
       <c r="G55" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H55" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="35" t="inlineStr">
+      <c r="I55" s="35" t="inlineStr">
         <is>
           <t>The end-to-end browser tests, QA data scripts and a results-to-workbook helper are in tests/e2e with a README. The QA scripts create test logins with known passwords, so they refuse to run unless the site is named in QA_TEST_SITE (never production). 22 Oct: the QA reset now removes a deleted QA user's shares at once (B-41).</t>
         </is>
       </c>
-      <c r="I55" s="35" t="inlineStr">
+      <c r="J55" s="35" t="inlineStr">
         <is>
           <t>Run before every release; results go into the Test Cases workbook.</t>
         </is>
       </c>
-      <c r="J55" s="35" t="inlineStr">
+      <c r="K55" s="35" t="inlineStr">
         <is>
           <t>tests/e2e/README.md</t>
         </is>
       </c>
-      <c r="K55" s="34" t="inlineStr">
+      <c r="L55" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -5666,7 +5942,7 @@
       </c>
       <c r="C56" s="35" t="inlineStr">
         <is>
-          <t>Job application page update (Fathir) merged into the test branch</t>
+          <t>Job application page update (assigned to Fathir) merged into the test branch</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
@@ -5681,30 +5957,35 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G56" s="34" t="inlineStr">
+        <is>
           <t>Fathir</t>
         </is>
       </c>
-      <c r="G56" s="34" t="inlineStr">
+      <c r="H56" s="34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H56" s="35" t="inlineStr">
-        <is>
-          <t>Fathir's update (22 Oct, PR #2 to develop): grouped form sections, country codes on phone numbers, a PDF receipt after sending, English/Arabic name checks, 194 Arabic texts. Merged into feature/uat-2026-10-22 the same day; conflicts resolved keeping both sides (phone check and Ministry identity check both run; Identity Type and Number stay required; 'Job Rank' in Arabic stays المرتبة الوظيفية). Two clashes Git could not see were fixed (B-42, B-44). Our browser tests now go through the steps of the form. Browser tests re-run: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries.</t>
-        </is>
-      </c>
       <c r="I56" s="35" t="inlineStr">
         <is>
+          <t>The update assigned to Fathir (22 Oct, PR #2 to develop): grouped form sections, country codes on phone numbers, a PDF receipt after sending, English/Arabic name checks, 194 Arabic texts. Merged into feature/uat-2026-10-22 the same day; conflicts resolved keeping both sides (phone check and Ministry identity check both run; Identity Type and Number stay required; 'Job Rank' in Arabic stays المرتبة الوظيفية). Two clashes Git could not see were fixed (B-42, B-44). Our browser tests now go through the steps of the form. Browser tests re-run: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries.</t>
+        </is>
+      </c>
+      <c r="J56" s="35" t="inlineStr">
+        <is>
           <t>Client UAT of the application form and the receipt (TC-REC-13, TC-REC-14). Fathir: the phone error message gives a Sri Lankan example (+94 77 123 4567); use a Saudi one (+966 5x xxx xxxx).</t>
         </is>
       </c>
-      <c r="J56" s="35" t="inlineStr">
+      <c r="K56" s="35" t="inlineStr">
         <is>
           <t>www/job-application.html; www/job_application.py; recruitment/receipt.py</t>
         </is>
       </c>
-      <c r="K56" s="34" t="inlineStr">
+      <c r="L56" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -5743,25 +6024,30 @@
       </c>
       <c r="G57" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H57" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H57" s="35" t="inlineStr">
-        <is>
-          <t>In this order: our work (feature/uat-2026-10-22, which already held fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views and the portal design), then feature/hr-portal-design, then employee-applicant, then ministry-lookup last (Fathir's 22 Oct update was already in). Conflicts: feature/hr-portal-design's own 22 Oct merge had dropped the Ministry identity check from the application form and kept an old Create Employee signature; develop's tested versions kept. employee-applicant (Dinesh, May-Jul prototype of recruitment, replaced by his September rebuild) recorded as merged without taking its files (decision of the HR lead, 23 Oct): its 17 old patches, second /job-application controller and old Return from Leave doctype would have broken recruitment, leave returns and migrate. The merged code is identical to the code tested on 22 Oct. Re-tested: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
-        </is>
-      </c>
       <c r="I57" s="35" t="inlineStr">
         <is>
+          <t>In this order: our work (feature/uat-2026-10-22, which already held fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views and the portal design), then feature/hr-portal-design, then employee-applicant, then ministry-lookup last (the 22 Oct job-application update was already in). Conflicts: feature/hr-portal-design's own 22 Oct merge had dropped the Ministry identity check from the application form and kept an old Create Employee signature; develop's tested versions kept. employee-applicant (May-Jul prototype of recruitment, assigned to Dinesh, replaced by the September rebuild) recorded as merged without taking its files (decision of the HR lead, 23 Oct): its 17 old patches, second /job-application controller and old Return from Leave doctype would have broken recruitment, leave returns and migrate. The merged code is identical to the code tested on 22 Oct. Re-tested: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+        </is>
+      </c>
+      <c r="J57" s="35" t="inlineStr">
+        <is>
           <t>Delete the merged branches on GitHub after UAT (Checklist CL-34). New work: a branch from develop and a pull request (README).</t>
         </is>
       </c>
-      <c r="J57" s="35" t="inlineStr">
+      <c r="K57" s="35" t="inlineStr">
         <is>
           <t>develop; README.md</t>
         </is>
       </c>
-      <c r="K57" s="34" t="inlineStr">
+      <c r="L57" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -5800,25 +6086,30 @@
       </c>
       <c r="G58" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H58" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H58" s="35" t="inlineStr">
+      <c r="I58" s="35" t="inlineStr">
         <is>
           <t>Files: 177 Python files compile, no undefined names (pyflakes); 26 JS files and the job form's 3 inline scripts parse; 26 JSON files load; 571 Arabic translations keep their placeholders. Site: 109 hooks / scheduler jobs / overrides / assets / patches resolve; 29 Medical HRMS doctypes, 73 custom link fields, the newest saved records (validate), the report, 4 pages and 2 workspaces. Server: all 29 methods called as visitor, employee and HR User (87 calls, none open to the wrong role, no server error). Unit tests: 19 files, 37 tests. Browser: the full suite, with the error sweep now opening every Medical HRMS doctype (list, new form, newest record), the report and both workspaces for HR, and employees' own request lists. The checks are kept as tests/checks/files.py, site.py and api_methods.py; each records its result in the Test Cases workbook (Last automated run). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
-      <c r="I58" s="35" t="inlineStr">
+      <c r="J58" s="35" t="inlineStr">
         <is>
           <t>Run tests/checks and the browser suite before every release (Checklist CL-36).</t>
         </is>
       </c>
-      <c r="J58" s="35" t="inlineStr">
+      <c r="K58" s="35" t="inlineStr">
         <is>
           <t>tests/checks; tests/e2e</t>
         </is>
       </c>
-      <c r="K58" s="34" t="inlineStr">
+      <c r="L58" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -5852,30 +6143,35 @@
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G59" s="34" t="inlineStr">
+        <is>
           <t>To assign</t>
         </is>
       </c>
-      <c r="G59" s="34" t="inlineStr">
+      <c r="H59" s="34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H59" s="35" t="inlineStr">
+      <c r="I59" s="35" t="inlineStr">
         <is>
           <t>Found 23 Oct: 39 of the 79 scripts in medical_hrms/ are not used by hooks, patches or other code (run by hand in the past): add_fields, apply_hr_workspace_layout, check_hrm_readiness, check_local_leave_flows, cleanup_duplicate_employee_ministry_fields, configure_hr_workspace_access, configure_hrm_request_governance, configure_instructor_handoff_permissions, create_company_car, create_education_allowance, create_medical_license, create_overtime_request, create_permission_request, create_remaining_doctypes, create_remote_work, create_return_from_leave, create_salary_cert, create_training_request, create_workspace, ensure_notification_settings, fill_jameah_arabic_fallback, fix_assessment_group_doctype, fix_child_table_column_widths, fix_return_from_leave_list_view, fix_swapped_ministry_code_rows, grant_hr_login_access, grant_hr_module_permissions, migrate_jameah_dummy_data, normalize_jameah_ministry_codes, quick_grant_hr_permissions, rebuild_workspace, rename_children_medical_allowance_doctype, rename_employee_jameah_labels, report_hr_permissions, run_hrm_demo_verification, translate_jameah_ministry_names_to_arabic, unify_workspace, update_workspace_db (+ a duplicate removed, B-45). Some are risky to run again (configure_hrm_request_governance replaces the request doctypes' permissions; create_* and rename_* recreate or rename doctypes).</t>
         </is>
       </c>
-      <c r="I59" s="35" t="inlineStr">
+      <c r="J59" s="35" t="inlineStr">
         <is>
           <t>Keep the useful tools (check_hrm_readiness, report_hr_permissions, run_hrm_demo_verification) in a tools/ folder; delete the one-offs already applied; never run configure_hrm_request_governance.</t>
         </is>
       </c>
-      <c r="J59" s="35" t="inlineStr">
+      <c r="K59" s="35" t="inlineStr">
         <is>
           <t>medical_hrms/*.py</t>
         </is>
       </c>
-      <c r="K59" s="34" t="inlineStr">
+      <c r="L59" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -5914,25 +6210,30 @@
       </c>
       <c r="G60" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H60" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H60" s="35" t="inlineStr">
-        <is>
-          <t>Same look as the college's new Education portals (Instructor Portal): left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so Education's changes cannot break these pages.</t>
-        </is>
-      </c>
       <c r="I60" s="35" t="inlineStr">
         <is>
+          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
+        </is>
+      </c>
+      <c r="J60" s="35" t="inlineStr">
+        <is>
           <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
         </is>
       </c>
-      <c r="J60" s="35" t="inlineStr">
+      <c r="K60" s="35" t="inlineStr">
         <is>
           <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
         </is>
       </c>
-      <c r="K60" s="34" t="inlineStr">
+      <c r="L60" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -5971,25 +6272,30 @@
       </c>
       <c r="G61" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H61" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H61" s="35" t="inlineStr">
+      <c r="I61" s="35" t="inlineStr">
         <is>
           <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
         </is>
       </c>
-      <c r="I61" s="35" t="inlineStr">
+      <c r="J61" s="35" t="inlineStr">
         <is>
           <t>Deploy (HR-58).</t>
         </is>
       </c>
-      <c r="J61" s="35" t="inlineStr">
+      <c r="K61" s="35" t="inlineStr">
         <is>
           <t>hr_core_permissions.py</t>
         </is>
       </c>
-      <c r="K61" s="34" t="inlineStr">
+      <c r="L61" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6028,25 +6334,30 @@
       </c>
       <c r="G62" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H62" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H62" s="35" t="inlineStr">
+      <c r="I62" s="35" t="inlineStr">
         <is>
           <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
         </is>
       </c>
-      <c r="I62" s="35" t="inlineStr">
+      <c r="J62" s="35" t="inlineStr">
         <is>
           <t>Client UAT.</t>
         </is>
       </c>
-      <c r="J62" s="35" t="inlineStr">
+      <c r="K62" s="35" t="inlineStr">
         <is>
           <t>Test Report</t>
         </is>
       </c>
-      <c r="K62" s="34" t="inlineStr">
+      <c r="L62" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6085,25 +6396,30 @@
       </c>
       <c r="G63" s="34" t="inlineStr">
         <is>
+          <t>Server admin</t>
+        </is>
+      </c>
+      <c r="H63" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H63" s="35" t="inlineStr">
+      <c r="I63" s="35" t="inlineStr">
         <is>
           <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
         </is>
       </c>
-      <c r="I63" s="35" t="inlineStr">
+      <c r="J63" s="35" t="inlineStr">
         <is>
           <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
         </is>
       </c>
-      <c r="J63" s="35" t="inlineStr">
+      <c r="K63" s="35" t="inlineStr">
         <is>
           <t>Error Log; Email Queue</t>
         </is>
       </c>
-      <c r="K63" s="34" t="inlineStr">
+      <c r="L63" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6142,25 +6458,30 @@
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H64" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H64" s="35" t="inlineStr">
+      <c r="I64" s="35" t="inlineStr">
         <is>
           <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
         </is>
       </c>
-      <c r="I64" s="35" t="inlineStr">
-        <is>
-          <t>Fix it from Medical HRMS, without changing the Education app: give the Instructor form the matching value when it copies gender / department from the Employee.</t>
-        </is>
-      </c>
       <c r="J64" s="35" t="inlineStr">
         <is>
+          <t>Fix it from Medical HRMS: give the Instructor form the matching value when it copies gender / department from the Employee.</t>
+        </is>
+      </c>
+      <c r="K64" s="35" t="inlineStr">
+        <is>
           <t>Instructor form; medical_hrms</t>
         </is>
       </c>
-      <c r="K64" s="34" t="inlineStr">
+      <c r="L64" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -6199,25 +6520,30 @@
       </c>
       <c r="G65" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H65" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H65" s="35" t="inlineStr">
+      <c r="I65" s="35" t="inlineStr">
         <is>
           <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
         </is>
       </c>
-      <c r="I65" s="35" t="inlineStr">
+      <c r="J65" s="35" t="inlineStr">
         <is>
           <t>HR to use it to complete the data (HR-50 sheet).</t>
         </is>
       </c>
-      <c r="J65" s="35" t="inlineStr">
+      <c r="K65" s="35" t="inlineStr">
         <is>
           <t>report/employees_missing_ministry_data</t>
         </is>
       </c>
-      <c r="K65" s="34" t="inlineStr">
+      <c r="L65" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6256,25 +6582,30 @@
       </c>
       <c r="G66" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H66" s="35" t="inlineStr">
+      <c r="I66" s="35" t="inlineStr">
         <is>
           <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
         </is>
       </c>
-      <c r="I66" s="35" t="inlineStr">
+      <c r="J66" s="35" t="inlineStr">
         <is>
           <t>HR to fill the sheet for all non-academic staff.</t>
         </is>
       </c>
-      <c r="J66" s="35" t="inlineStr">
+      <c r="K66" s="35" t="inlineStr">
         <is>
           <t>employee_data_sheet.py</t>
         </is>
       </c>
-      <c r="K66" s="34" t="inlineStr">
+      <c r="L66" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6313,25 +6644,30 @@
       </c>
       <c r="G67" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H67" s="34" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H67" s="35" t="inlineStr">
+      <c r="I67" s="35" t="inlineStr">
         <is>
           <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
         </is>
       </c>
-      <c r="I67" s="35" t="inlineStr">
+      <c r="J67" s="35" t="inlineStr">
         <is>
           <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
         </is>
       </c>
-      <c r="J67" s="35" t="inlineStr">
+      <c r="K67" s="35" t="inlineStr">
         <is>
           <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
         </is>
       </c>
-      <c r="K67" s="34" t="inlineStr">
+      <c r="L67" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6370,25 +6706,30 @@
       </c>
       <c r="G68" s="34" t="inlineStr">
         <is>
+          <t>HR + Ministry contact</t>
+        </is>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H68" s="35" t="inlineStr">
+      <c r="I68" s="35" t="inlineStr">
         <is>
           <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
         </is>
       </c>
-      <c r="I68" s="35" t="inlineStr">
+      <c r="J68" s="35" t="inlineStr">
         <is>
           <t>Confirm whether 9-digit numbers must be accepted.</t>
         </is>
       </c>
-      <c r="J68" s="35" t="inlineStr">
+      <c r="K68" s="35" t="inlineStr">
         <is>
           <t>ministry_lookup_validation.py</t>
         </is>
       </c>
-      <c r="K68" s="34" t="inlineStr">
+      <c r="L68" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6427,25 +6768,30 @@
       </c>
       <c r="G69" s="34" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H69" s="35" t="inlineStr">
+      <c r="I69" s="35" t="inlineStr">
         <is>
           <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
         </is>
       </c>
-      <c r="I69" s="35" t="inlineStr">
+      <c r="J69" s="35" t="inlineStr">
         <is>
           <t>Complete or delete the demo record before go-live.</t>
         </is>
       </c>
-      <c r="J69" s="35" t="inlineStr">
+      <c r="K69" s="35" t="inlineStr">
         <is>
           <t>Employee EMP-00001</t>
         </is>
       </c>
-      <c r="K69" s="34" t="inlineStr">
+      <c r="L69" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6484,25 +6830,30 @@
       </c>
       <c r="G70" s="34" t="inlineStr">
         <is>
+          <t>Server admin</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H70" s="35" t="inlineStr">
+      <c r="I70" s="35" t="inlineStr">
         <is>
           <t>Missing on the local copy; every page requests it.</t>
         </is>
       </c>
-      <c r="I70" s="35" t="inlineStr">
+      <c r="J70" s="35" t="inlineStr">
         <is>
           <t>Check the file exists on the live server.</t>
         </is>
       </c>
-      <c r="J70" s="35" t="inlineStr">
+      <c r="K70" s="35" t="inlineStr">
         <is>
           <t>Website Settings</t>
         </is>
       </c>
-      <c r="K70" s="34" t="inlineStr">
+      <c r="L70" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6541,25 +6892,30 @@
       </c>
       <c r="G71" s="34" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H71" s="35" t="inlineStr">
+      <c r="I71" s="35" t="inlineStr">
         <is>
           <t>Tool ready (HR-35). 1 of 216 linked.</t>
         </is>
       </c>
-      <c r="I71" s="35" t="inlineStr">
+      <c r="J71" s="35" t="inlineStr">
         <is>
           <t>HR fills the Instructor data sheet; run the import with commit.</t>
         </is>
       </c>
-      <c r="J71" s="35" t="inlineStr">
+      <c r="K71" s="35" t="inlineStr">
         <is>
           <t>instructor_data_sheet.py</t>
         </is>
       </c>
-      <c r="K71" s="34" t="inlineStr">
+      <c r="L71" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6598,25 +6954,30 @@
       </c>
       <c r="G72" s="34" t="inlineStr">
         <is>
+          <t>HR + IT</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H72" s="35" t="inlineStr">
+      <c r="I72" s="35" t="inlineStr">
         <is>
           <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
         </is>
       </c>
-      <c r="I72" s="35" t="inlineStr">
+      <c r="J72" s="35" t="inlineStr">
         <is>
           <t>Connect devices; map device user IDs to Employees.</t>
         </is>
       </c>
-      <c r="J72" s="35" t="inlineStr">
+      <c r="K72" s="35" t="inlineStr">
         <is>
           <t>bfac883</t>
         </is>
       </c>
-      <c r="K72" s="34" t="inlineStr">
+      <c r="L72" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6655,25 +7016,30 @@
       </c>
       <c r="G73" s="34" t="inlineStr">
         <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H73" s="35" t="inlineStr">
+      <c r="I73" s="35" t="inlineStr">
         <is>
           <t>Not set; the page warns about it.</t>
         </is>
       </c>
-      <c r="I73" s="35" t="inlineStr">
+      <c r="J73" s="35" t="inlineStr">
         <is>
           <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
         </is>
       </c>
-      <c r="J73" s="35" t="inlineStr">
+      <c r="K73" s="35" t="inlineStr">
         <is>
           <t>academic_presence_setup.py</t>
         </is>
       </c>
-      <c r="K73" s="34" t="inlineStr">
+      <c r="L73" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6712,25 +7078,30 @@
       </c>
       <c r="G74" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H74" s="35" t="inlineStr">
+      <c r="I74" s="35" t="inlineStr">
         <is>
           <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
         </is>
       </c>
-      <c r="I74" s="35" t="inlineStr">
+      <c r="J74" s="35" t="inlineStr">
         <is>
           <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
         </is>
       </c>
-      <c r="J74" s="35" t="inlineStr">
+      <c r="K74" s="35" t="inlineStr">
         <is>
           <t>GitHub phpdevpro/edu-alriyada-hrm</t>
         </is>
       </c>
-      <c r="K74" s="34" t="inlineStr">
+      <c r="L74" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -6769,25 +7140,30 @@
       </c>
       <c r="G75" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H75" s="35" t="inlineStr">
+      <c r="I75" s="35" t="inlineStr">
         <is>
           <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
         </is>
       </c>
-      <c r="I75" s="35" t="inlineStr">
+      <c r="J75" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J75" s="35" t="inlineStr">
+      <c r="K75" s="35" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="K75" s="34" t="inlineStr">
+      <c r="L75" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6826,25 +7202,30 @@
       </c>
       <c r="G76" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H76" s="35" t="inlineStr">
+      <c r="I76" s="35" t="inlineStr">
         <is>
           <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
         </is>
       </c>
-      <c r="I76" s="35" t="inlineStr">
+      <c r="J76" s="35" t="inlineStr">
         <is>
           <t>Deploy (HR-58).</t>
         </is>
       </c>
-      <c r="J76" s="35" t="inlineStr">
+      <c r="K76" s="35" t="inlineStr">
         <is>
           <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
         </is>
       </c>
-      <c r="K76" s="34" t="inlineStr">
+      <c r="L76" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6883,27 +7264,32 @@
       </c>
       <c r="G77" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>299 college values mapped to official codes by meaning; wrong codes in Education masters (City 90, REL001...) no longer reach the Ministry.</t>
-        </is>
-      </c>
       <c r="I77" s="35" t="inlineStr">
         <is>
+          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
+        </is>
+      </c>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
           <t>Review 3 values (JM-11).</t>
         </is>
       </c>
-      <c r="J77" s="35" t="inlineStr">
+      <c r="K77" s="35" t="inlineStr">
         <is>
           <t>jameah/code_map.py</t>
         </is>
       </c>
-      <c r="K77" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
+      <c r="L77" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6940,25 +7326,30 @@
       </c>
       <c r="G78" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H78" s="35" t="inlineStr">
+      <c r="I78" s="35" t="inlineStr">
         <is>
           <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
         </is>
       </c>
-      <c r="I78" s="35" t="inlineStr">
+      <c r="J78" s="35" t="inlineStr">
         <is>
           <t>Fill 6 values (JM-10).</t>
         </is>
       </c>
-      <c r="J78" s="35" t="inlineStr">
+      <c r="K78" s="35" t="inlineStr">
         <is>
           <t>Jameah Settings</t>
         </is>
       </c>
-      <c r="K78" s="34" t="inlineStr">
+      <c r="L78" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -6997,25 +7388,30 @@
       </c>
       <c r="G79" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H79" s="35" t="inlineStr">
+      <c r="I79" s="35" t="inlineStr">
         <is>
           <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
         </is>
       </c>
-      <c r="I79" s="35" t="inlineStr">
+      <c r="J79" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J79" s="35" t="inlineStr">
+      <c r="K79" s="35" t="inlineStr">
         <is>
           <t>jameah/summary.py</t>
         </is>
       </c>
-      <c r="K79" s="34" t="inlineStr">
+      <c r="L79" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -7054,27 +7450,32 @@
       </c>
       <c r="G80" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the Education update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
-        </is>
-      </c>
       <c r="I80" s="35" t="inlineStr">
         <is>
+          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
+        </is>
+      </c>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
           <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
-      <c r="J80" s="35" t="inlineStr">
+      <c r="K80" s="35" t="inlineStr">
         <is>
           <t>jameah/verify.py; test_jameah.py</t>
         </is>
       </c>
-      <c r="K80" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
+      <c r="L80" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -7111,27 +7512,32 @@
       </c>
       <c r="G81" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>Found 21 Oct: Education's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads Education's official functions (read only, no change to Education); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
-        </is>
-      </c>
       <c r="I81" s="35" t="inlineStr">
         <is>
-          <t>Deploy together with the Education master update (HR-58); re-run verify on the live server.</t>
+          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
         </is>
       </c>
       <c r="J81" s="35" t="inlineStr">
         <is>
+          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
+        </is>
+      </c>
+      <c r="K81" s="35" t="inlineStr">
+        <is>
           <t>jameah/summary.py; jameah/verify.py</t>
         </is>
       </c>
-      <c r="K81" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
+      <c r="L81" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -7168,25 +7574,30 @@
       </c>
       <c r="G82" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H82" s="35" t="inlineStr">
+      <c r="I82" s="35" t="inlineStr">
         <is>
           <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
         </is>
       </c>
-      <c r="I82" s="35" t="inlineStr">
+      <c r="J82" s="35" t="inlineStr">
         <is>
           <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
         </is>
       </c>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="K82" s="35" t="inlineStr">
         <is>
           <t>jameah/summary.py; hooks.py hourly_long</t>
         </is>
       </c>
-      <c r="K82" s="34" t="inlineStr">
+      <c r="L82" s="34" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
@@ -7225,25 +7636,30 @@
       </c>
       <c r="G83" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H83" s="35" t="inlineStr">
+      <c r="I83" s="35" t="inlineStr">
         <is>
           <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
         </is>
       </c>
-      <c r="I83" s="35" t="inlineStr">
+      <c r="J83" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J83" s="35" t="inlineStr">
+      <c r="K83" s="35" t="inlineStr">
         <is>
           <t>page/jameah_data_check</t>
         </is>
       </c>
-      <c r="K83" s="34" t="inlineStr">
+      <c r="L83" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -7282,25 +7698,30 @@
       </c>
       <c r="G84" s="34" t="inlineStr">
         <is>
+          <t>Server admin</t>
+        </is>
+      </c>
+      <c r="H84" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H84" s="35" t="inlineStr">
+      <c r="I84" s="35" t="inlineStr">
         <is>
           <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
         </is>
       </c>
-      <c r="I84" s="35" t="inlineStr">
+      <c r="J84" s="35" t="inlineStr">
         <is>
           <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
         </is>
       </c>
-      <c r="J84" s="35" t="inlineStr">
+      <c r="K84" s="35" t="inlineStr">
         <is>
           <t>jameah/README.md</t>
         </is>
       </c>
-      <c r="K84" s="34" t="inlineStr">
+      <c r="L84" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -7339,25 +7760,30 @@
       </c>
       <c r="G85" s="34" t="inlineStr">
         <is>
+          <t>Ministry contact (Ms. Najah)</t>
+        </is>
+      </c>
+      <c r="H85" s="34" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="H85" s="35" t="inlineStr">
+      <c r="I85" s="35" t="inlineStr">
         <is>
           <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
         </is>
       </c>
-      <c r="I85" s="35" t="inlineStr">
+      <c r="J85" s="35" t="inlineStr">
         <is>
           <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
         </is>
       </c>
-      <c r="J85" s="35" t="inlineStr">
+      <c r="K85" s="35" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="K85" s="34" t="inlineStr">
+      <c r="L85" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -7396,25 +7822,30 @@
       </c>
       <c r="G86" s="34" t="inlineStr">
         <is>
+          <t>Academic Affairs</t>
+        </is>
+      </c>
+      <c r="H86" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H86" s="35" t="inlineStr">
+      <c r="I86" s="35" t="inlineStr">
         <is>
           <t>Empty values are sent as empty.</t>
         </is>
       </c>
-      <c r="I86" s="35" t="inlineStr">
+      <c r="J86" s="35" t="inlineStr">
         <is>
           <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
         </is>
       </c>
-      <c r="J86" s="35" t="inlineStr">
+      <c r="K86" s="35" t="inlineStr">
         <is>
           <t>/app/jameah-settings</t>
         </is>
       </c>
-      <c r="K86" s="34" t="inlineStr">
+      <c r="L86" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -7453,25 +7884,30 @@
       </c>
       <c r="G87" s="34" t="inlineStr">
         <is>
+          <t>Academic Affairs</t>
+        </is>
+      </c>
+      <c r="H87" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H87" s="35" t="inlineStr">
+      <c r="I87" s="35" t="inlineStr">
         <is>
           <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
         </is>
       </c>
-      <c r="I87" s="35" t="inlineStr">
+      <c r="J87" s="35" t="inlineStr">
         <is>
           <t>Pick the code in Jameah Code Map and set Verified.</t>
         </is>
       </c>
-      <c r="J87" s="35" t="inlineStr">
+      <c r="K87" s="35" t="inlineStr">
         <is>
           <t>/app/jameah-code-map</t>
         </is>
       </c>
-      <c r="K87" s="34" t="inlineStr">
+      <c r="L87" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -7510,25 +7946,30 @@
       </c>
       <c r="G88" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H88" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H88" s="35" t="inlineStr">
+      <c r="I88" s="35" t="inlineStr">
         <is>
           <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
         </is>
       </c>
-      <c r="I88" s="35" t="inlineStr">
+      <c r="J88" s="35" t="inlineStr">
         <is>
           <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
         </is>
       </c>
-      <c r="J88" s="35" t="inlineStr">
+      <c r="K88" s="35" t="inlineStr">
         <is>
           <t>Jameah report; VIEWS.md</t>
         </is>
       </c>
-      <c r="K88" s="34" t="inlineStr">
+      <c r="L88" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -7567,25 +8008,30 @@
       </c>
       <c r="G89" s="34" t="inlineStr">
         <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="H89" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H89" s="35" t="inlineStr">
+      <c r="I89" s="35" t="inlineStr">
         <is>
           <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
         </is>
       </c>
-      <c r="I89" s="35" t="inlineStr">
+      <c r="J89" s="35" t="inlineStr">
         <is>
           <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
         </is>
       </c>
-      <c r="J89" s="35" t="inlineStr">
+      <c r="K89" s="35" t="inlineStr">
         <is>
           <t>/app/jameah-data-check</t>
         </is>
       </c>
-      <c r="K89" s="34" t="inlineStr">
+      <c r="L89" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -7624,25 +8070,30 @@
       </c>
       <c r="G90" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H90" s="34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H90" s="35" t="inlineStr">
+      <c r="I90" s="35" t="inlineStr">
         <is>
           <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
         </is>
       </c>
-      <c r="I90" s="35" t="inlineStr">
+      <c r="J90" s="35" t="inlineStr">
         <is>
           <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
         </is>
       </c>
-      <c r="J90" s="35" t="inlineStr">
+      <c r="K90" s="35" t="inlineStr">
         <is>
           <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
         </is>
       </c>
-      <c r="K90" s="34" t="inlineStr">
+      <c r="L90" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -7681,25 +8132,30 @@
       </c>
       <c r="G91" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H91" s="34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H91" s="35" t="inlineStr">
+      <c r="I91" s="35" t="inlineStr">
         <is>
           <t>Not started.</t>
         </is>
       </c>
-      <c r="I91" s="35" t="inlineStr">
+      <c r="J91" s="35" t="inlineStr">
         <is>
           <t>Build after Faculty; needs institute data from HR.</t>
         </is>
       </c>
-      <c r="J91" s="35" t="inlineStr">
+      <c r="K91" s="35" t="inlineStr">
         <is>
           <t>MINISTRY_FIELD_MAPPING.html</t>
         </is>
       </c>
-      <c r="K91" s="34" t="inlineStr">
+      <c r="L91" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
@@ -7718,7 +8174,7 @@
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>Old Education viewJameah* views (42)</t>
+          <t>Old viewJameah* views (42, earlier version)</t>
         </is>
       </c>
       <c r="D92" s="34" t="inlineStr">
@@ -7738,25 +8194,30 @@
       </c>
       <c r="G92" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H92" s="34" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H92" s="35" t="inlineStr">
+      <c r="I92" s="35" t="inlineStr">
         <is>
           <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
         </is>
       </c>
-      <c r="I92" s="35" t="inlineStr">
-        <is>
-          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped (they belong to the Education app, which we do not change).</t>
-        </is>
-      </c>
       <c r="J92" s="35" t="inlineStr">
         <is>
-          <t>education/jameah_system</t>
-        </is>
-      </c>
-      <c r="K92" s="34" t="inlineStr">
+          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+        </is>
+      </c>
+      <c r="K92" s="35" t="inlineStr">
+        <is>
+          <t>jameah_system (old views)</t>
+        </is>
+      </c>
+      <c r="L92" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
@@ -7795,32 +8256,37 @@
       </c>
       <c r="G93" s="34" t="inlineStr">
         <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H93" s="34" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H93" s="35" t="inlineStr">
+      <c r="I93" s="35" t="inlineStr">
         <is>
           <t>Resolved by the college's official GPA calculation (exact half-up rounding); the Ministry views use it (JM-18).</t>
         </is>
       </c>
-      <c r="I93" s="35" t="inlineStr">
+      <c r="J93" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="J93" s="35" t="inlineStr">
+      <c r="K93" s="35" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="K93" s="34" t="inlineStr">
+      <c r="L93" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K93"/>
+  <autoFilter ref="A1:L93"/>
   <conditionalFormatting sqref="E2:E293">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$E2="Done"</formula>
@@ -7847,26 +8313,29 @@
       <formula>$E2="Planned"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G293">
+  <conditionalFormatting sqref="H2:H293">
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
-      <formula>$G2="Critical"</formula>
+      <formula>$H2="Critical"</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="9" stopIfTrue="1">
-      <formula>$G2="High"</formula>
+      <formula>$H2="High"</formula>
     </cfRule>
     <cfRule type="expression" priority="11" dxfId="10" stopIfTrue="1">
-      <formula>$G2="Medium"</formula>
+      <formula>$H2="Medium"</formula>
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="11" stopIfTrue="1">
-      <formula>$G2="Low"</formula>
+      <formula>$H2="Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="E2:E293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
       <formula1>"Done,Done – client UAT pending,In progress,Pending – decision needed,Pending – data / setup,Pending – development,Pending – other team,Planned"</formula1>
     </dataValidation>
+    <dataValidation sqref="H2:H293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Critical,High,Medium,Low"</formula1>
+    </dataValidation>
     <dataValidation sqref="G2:G293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Critical,High,Medium,Low"</formula1>
+      <formula1>"Abdul Hakeem,Fathir,Dinesh,To assign"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9165,7 +9634,7 @@
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Education master has no HR roles in its landing list</t>
+          <t>The education app (master) has no HR roles in its landing list</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
@@ -9190,7 +9659,7 @@
       </c>
       <c r="J25" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9738,7 @@
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Education master requires @alriyada.edu.sa for Instructors</t>
+          <t>The education app (master) requires @alriyada.edu.sa for Instructors</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
@@ -9294,7 +9763,7 @@
       </c>
       <c r="J27" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9941,7 @@
       </c>
       <c r="D31" s="35" t="inlineStr">
         <is>
-          <t>Ministry GPA differed from the transcript for 1,197 students after the Education update</t>
+          <t>Ministry GPA differed from the transcript for 1,197 students after the GPA calculation update</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -9482,7 +9951,7 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Use Education's official GPA and credit-hour functions</t>
+          <t>Use the college's official GPA and credit-hour functions</t>
         </is>
       </c>
       <c r="G31" s="34" t="inlineStr">
@@ -9502,7 +9971,7 @@
       </c>
       <c r="J31" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -11326,12 +11795,12 @@
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>HR-04 - HR-06, HR-11, HR-28 - HR-30, HR-48, HR-66, HR-70, JM-12, JM-13, JM-16, JM-17, B-26</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
         <is>
-          <t>Owners corrected: Medical HRMS and Jameah are built by the HRMS team only, so no task is owned by the Education team (HR-11, HR-28, HR-48, JM-16, JM-17 now Abdul Hakeem; JM-12 Academic Affairs + Abdul Hakeem; JM-13 Registrar). Employee application: Dinesh + Abdul Hakeem built it (HR-06); Fathir handles its UI (HR-70) and Dinesh's open items (HR-04, HR-05). Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E2" s="34" t="inlineStr">
@@ -11547,7 +12016,7 @@
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">

--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -15,10 +15,10 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$293,A5)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$294,A5)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$293,A6)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$294,A6)</f>
         <v/>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$293,A7)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$294,A7)</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="B8" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$293,A8)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$294,A8)</f>
         <v/>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$293,A9)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$294,A9)</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$293,A10)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$294,A10)</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$293,A11)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$294,A11)</f>
         <v/>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B12" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$293,A12)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$294,A12)</f>
         <v/>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B16" s="23">
-        <f>COUNTIFS(Tasks!$A$2:$A$293,"HR-*",Tasks!$E$2:$E$293,"Done")+COUNTIFS(Tasks!$A$2:$A$293,"HR-*",Tasks!$E$2:$E$293,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$294,"HR-*",Tasks!$E$2:$E$294,"Done")+COUNTIFS(Tasks!$A$2:$A$294,"HR-*",Tasks!$E$2:$E$294,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C16" s="23">
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>COUNTIF(Tasks!$A$2:$A$293,"HR-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$294,"HR-*")</f>
         <v/>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="B17" s="23">
-        <f>COUNTIFS(Tasks!$A$2:$A$293,"JM-*",Tasks!$E$2:$E$293,"Done")+COUNTIFS(Tasks!$A$2:$A$293,"JM-*",Tasks!$E$2:$E$293,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$294,"JM-*",Tasks!$E$2:$E$294,"Done")+COUNTIFS(Tasks!$A$2:$A$294,"JM-*",Tasks!$E$2:$E$294,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C17" s="23">
@@ -1298,7 +1298,7 @@
         <v/>
       </c>
       <c r="D17" s="23">
-        <f>COUNTIF(Tasks!$A$2:$A$293,"JM-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$294,"JM-*")</f>
         <v/>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B20" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$293,"Earlier (May – 5 Oct 2026)")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$294,"Earlier (May – 5 Oct 2026)")</f>
         <v/>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B21" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$293,"19 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$294,"19 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B22" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$293,"20 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$294,"20 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B23" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$293,"21 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$294,"21 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="B24" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$293,"22 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$294,"22 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="B25" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$293,"23 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$294,"23 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B26" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$293,"—")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$294,"—")</f>
         <v/>
       </c>
     </row>
@@ -1452,39 +1452,39 @@
         </is>
       </c>
       <c r="B29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A29,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J29" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A29)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A29)</f>
         <v/>
       </c>
     </row>
@@ -1495,39 +1495,39 @@
         </is>
       </c>
       <c r="B30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A30,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J30" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A30)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A30)</f>
         <v/>
       </c>
     </row>
@@ -1538,39 +1538,39 @@
         </is>
       </c>
       <c r="B31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A31,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J31" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A31)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A31)</f>
         <v/>
       </c>
     </row>
@@ -1581,39 +1581,39 @@
         </is>
       </c>
       <c r="B32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A32,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J32" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A32)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A32)</f>
         <v/>
       </c>
     </row>
@@ -1624,39 +1624,39 @@
         </is>
       </c>
       <c r="B33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A33,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J33" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A33)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A33)</f>
         <v/>
       </c>
     </row>
@@ -1667,39 +1667,39 @@
         </is>
       </c>
       <c r="B34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A34,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J34" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A34)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A34)</f>
         <v/>
       </c>
     </row>
@@ -1710,39 +1710,39 @@
         </is>
       </c>
       <c r="B35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A35,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J35" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A35)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A35)</f>
         <v/>
       </c>
     </row>
@@ -1753,39 +1753,39 @@
         </is>
       </c>
       <c r="B36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A36,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J36" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A36)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A36)</f>
         <v/>
       </c>
     </row>
@@ -1796,39 +1796,39 @@
         </is>
       </c>
       <c r="B37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A37,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J37" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A37)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A37)</f>
         <v/>
       </c>
     </row>
@@ -1839,39 +1839,39 @@
         </is>
       </c>
       <c r="B38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A38,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J38" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A38)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A38)</f>
         <v/>
       </c>
     </row>
@@ -1882,39 +1882,39 @@
         </is>
       </c>
       <c r="B39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A39,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J39" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A39)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A39)</f>
         <v/>
       </c>
     </row>
@@ -1925,39 +1925,39 @@
         </is>
       </c>
       <c r="B40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A40,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J40" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A40)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A40)</f>
         <v/>
       </c>
     </row>
@@ -1968,39 +1968,39 @@
         </is>
       </c>
       <c r="B41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A41,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J41" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A41)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A41)</f>
         <v/>
       </c>
     </row>
@@ -2011,39 +2011,39 @@
         </is>
       </c>
       <c r="B42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A42,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J42" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A42)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A42)</f>
         <v/>
       </c>
     </row>
@@ -2054,39 +2054,39 @@
         </is>
       </c>
       <c r="B43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A43,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J43" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A43)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A43)</f>
         <v/>
       </c>
     </row>
@@ -2097,39 +2097,39 @@
         </is>
       </c>
       <c r="B44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A44,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J44" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A44)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A44)</f>
         <v/>
       </c>
     </row>
@@ -2140,39 +2140,39 @@
         </is>
       </c>
       <c r="B45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A45,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J45" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A45)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A45)</f>
         <v/>
       </c>
     </row>
@@ -2183,39 +2183,39 @@
         </is>
       </c>
       <c r="B46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A46,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J46" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A46)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A46)</f>
         <v/>
       </c>
     </row>
@@ -2226,39 +2226,39 @@
         </is>
       </c>
       <c r="B47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A47,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J47" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A47)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A47)</f>
         <v/>
       </c>
     </row>
@@ -2269,39 +2269,39 @@
         </is>
       </c>
       <c r="B48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A48,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J48" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A48)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A48)</f>
         <v/>
       </c>
     </row>
@@ -2312,39 +2312,39 @@
         </is>
       </c>
       <c r="B49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A49,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J49" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A49)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A49)</f>
         <v/>
       </c>
     </row>
@@ -2355,39 +2355,39 @@
         </is>
       </c>
       <c r="B50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A50,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J50" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A50)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A50)</f>
         <v/>
       </c>
     </row>
@@ -2398,39 +2398,39 @@
         </is>
       </c>
       <c r="B51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,B$28)</f>
         <v/>
       </c>
       <c r="C51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,C$28)</f>
         <v/>
       </c>
       <c r="D51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,D$28)</f>
         <v/>
       </c>
       <c r="E51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,E$28)</f>
         <v/>
       </c>
       <c r="F51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,F$28)</f>
         <v/>
       </c>
       <c r="G51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,G$28)</f>
         <v/>
       </c>
       <c r="H51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,H$28)</f>
         <v/>
       </c>
       <c r="I51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$293,$A51,Tasks!$E$2:$E$293,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,I$28)</f>
         <v/>
       </c>
       <c r="J51" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$293,$A51)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$294,$A51)</f>
         <v/>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="B54" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$154,A54)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$156,A54)</f>
         <v/>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="B55" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$154,A55)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$156,A55)</f>
         <v/>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="B56" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$154,A56)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$156,A56)</f>
         <v/>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B57" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$154,A57)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$156,A57)</f>
         <v/>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6180,22 +6180,22 @@
     <row r="60">
       <c r="A60" s="33" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-74</t>
         </is>
       </c>
       <c r="B60" s="34" t="inlineStr">
         <is>
-          <t>HR dashboard</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C60" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college design</t>
+          <t>Installation and Setup Guide and User Guide (PDF)</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
@@ -6220,17 +6220,17 @@
       </c>
       <c r="I60" s="35" t="inlineStr">
         <is>
-          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
+          <t>Two PDF guides in docs/guides: Installation and Setup Guide (21 pages: install, update, checks, first-time setup, leave year, sick leave, Jameah setup, Ministry agent account, staff data sheets, testing, troubleshooting, commands) and User Guide (30 pages: Employee Portal and the leave flow, every request, HR Portal, leave approvals and returns, recruitment, Ministry data, Academic Presence, Jameah pages, approvers, how to test and report bugs, Q&amp;A). 31 screenshots from the test site with QA test data only. Sources (HTML) and build.py kept in docs/guides/src so the guides can be rebuilt after changes. Writing them found two bugs (B-54, B-55). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="J60" s="35" t="inlineStr">
         <is>
-          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
+          <t>HR, managers and the testing team read the User Guide; the server admin the Installation Guide (Checklist CL-37). Rebuild after changes: python docs/guides/src/build.py.</t>
         </is>
       </c>
       <c r="K60" s="35" t="inlineStr">
         <is>
-          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
+          <t>docs/guides</t>
         </is>
       </c>
       <c r="L60" s="34" t="inlineStr">
@@ -6242,17 +6242,17 @@
     <row r="61">
       <c r="A61" s="33" t="inlineStr">
         <is>
-          <t>HR-62</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="B61" s="34" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="C61" s="35" t="inlineStr">
         <is>
-          <t>HR User could not open the Holiday List ('Not permitted')</t>
+          <t>HR Portal and Employee Portal in the new college design</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
@@ -6277,44 +6277,44 @@
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I61" s="35" t="inlineStr">
         <is>
-          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
+          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
         </is>
       </c>
       <c r="J61" s="35" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
         </is>
       </c>
       <c r="K61" s="35" t="inlineStr">
         <is>
-          <t>hr_core_permissions.py</t>
+          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
         </is>
       </c>
       <c r="L61" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="33" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-62</t>
         </is>
       </c>
       <c r="B62" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C62" s="35" t="inlineStr">
         <is>
-          <t>Full end-to-end test with error sweep (round 3)</t>
+          <t>HR User could not open the Holiday List ('Not permitted')</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
@@ -6339,22 +6339,22 @@
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I62" s="35" t="inlineStr">
         <is>
-          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
+          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
         </is>
       </c>
       <c r="J62" s="35" t="inlineStr">
         <is>
-          <t>Client UAT.</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="K62" s="35" t="inlineStr">
         <is>
-          <t>Test Report</t>
+          <t>hr_core_permissions.py</t>
         </is>
       </c>
       <c r="L62" s="34" t="inlineStr">
@@ -6366,37 +6366,37 @@
     <row r="63">
       <c r="A63" s="33" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-46</t>
         </is>
       </c>
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C63" s="35" t="inlineStr">
         <is>
-          <t>System e-mail account password cannot be decrypted</t>
+          <t>Full end-to-end test with error sweep (round 3)</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G63" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H63" s="34" t="inlineStr">
@@ -6406,17 +6406,17 @@
       </c>
       <c r="I63" s="35" t="inlineStr">
         <is>
-          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
+          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
         </is>
       </c>
       <c r="J63" s="35" t="inlineStr">
         <is>
-          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
+          <t>Client UAT.</t>
         </is>
       </c>
       <c r="K63" s="35" t="inlineStr">
         <is>
-          <t>Error Log; Email Queue</t>
+          <t>Test Report</t>
         </is>
       </c>
       <c r="L63" s="34" t="inlineStr">
@@ -6428,17 +6428,17 @@
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-47</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C64" s="35" t="inlineStr">
         <is>
-          <t>Instructor form: linking an Employee fails on save</t>
+          <t>System e-mail account password cannot be decrypted</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
@@ -6448,69 +6448,69 @@
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I64" s="35" t="inlineStr">
         <is>
-          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
+          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
         </is>
       </c>
       <c r="J64" s="35" t="inlineStr">
         <is>
-          <t>Fix it from Medical HRMS: give the Instructor form the matching value when it copies gender / department from the Employee.</t>
+          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
         </is>
       </c>
       <c r="K64" s="35" t="inlineStr">
         <is>
-          <t>Instructor form; medical_hrms</t>
+          <t>Error Log; Email Queue</t>
         </is>
       </c>
       <c r="L64" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="33" t="inlineStr">
         <is>
-          <t>HR-49</t>
+          <t>HR-48</t>
         </is>
       </c>
       <c r="B65" s="34" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C65" s="35" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Instructor form: linking an Employee fails on save</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – development</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="I65" s="35" t="inlineStr">
         <is>
-          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
+          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
         </is>
       </c>
       <c r="J65" s="35" t="inlineStr">
         <is>
-          <t>HR to use it to complete the data (HR-50 sheet).</t>
+          <t>Fix it from Medical HRMS: give the Instructor form the matching value when it copies gender / department from the Employee.</t>
         </is>
       </c>
       <c r="K65" s="35" t="inlineStr">
         <is>
-          <t>report/employees_missing_ministry_data</t>
+          <t>Instructor form; medical_hrms</t>
         </is>
       </c>
       <c r="L65" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>HR-50</t>
+          <t>HR-49</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="C66" s="35" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
@@ -6592,17 +6592,17 @@
       </c>
       <c r="I66" s="35" t="inlineStr">
         <is>
-          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
+          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
         </is>
       </c>
       <c r="J66" s="35" t="inlineStr">
         <is>
-          <t>HR to fill the sheet for all non-academic staff.</t>
+          <t>HR to use it to complete the data (HR-50 sheet).</t>
         </is>
       </c>
       <c r="K66" s="35" t="inlineStr">
         <is>
-          <t>employee_data_sheet.py</t>
+          <t>report/employees_missing_ministry_data</t>
         </is>
       </c>
       <c r="L66" s="34" t="inlineStr">
@@ -6614,17 +6614,17 @@
     <row r="67">
       <c r="A67" s="33" t="inlineStr">
         <is>
-          <t>HR-51</t>
+          <t>HR-50</t>
         </is>
       </c>
       <c r="B67" s="34" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C67" s="35" t="inlineStr">
         <is>
-          <t>Unused duplicate of the applicant Ministry fields removed</t>
+          <t>Data sheet for non-academic staff</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
@@ -6649,22 +6649,22 @@
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I67" s="35" t="inlineStr">
         <is>
-          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
+          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
         </is>
       </c>
       <c r="J67" s="35" t="inlineStr">
         <is>
-          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
+          <t>HR to fill the sheet for all non-academic staff.</t>
         </is>
       </c>
       <c r="K67" s="35" t="inlineStr">
         <is>
-          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
+          <t>employee_data_sheet.py</t>
         </is>
       </c>
       <c r="L67" s="34" t="inlineStr">
@@ -6676,57 +6676,57 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>HR-52</t>
+          <t>HR-51</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C68" s="35" t="inlineStr">
         <is>
-          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
+          <t>Unused duplicate of the applicant Ministry fields removed</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G68" s="34" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I68" s="35" t="inlineStr">
         <is>
-          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
+          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
         </is>
       </c>
       <c r="J68" s="35" t="inlineStr">
         <is>
-          <t>Confirm whether 9-digit numbers must be accepted.</t>
+          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
         </is>
       </c>
       <c r="K68" s="35" t="inlineStr">
         <is>
-          <t>ministry_lookup_validation.py</t>
+          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
         </is>
       </c>
       <c r="L68" s="34" t="inlineStr">
@@ -6738,17 +6738,17 @@
     <row r="69">
       <c r="A69" s="33" t="inlineStr">
         <is>
-          <t>HR-53</t>
+          <t>HR-52</t>
         </is>
       </c>
       <c r="B69" s="34" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C69" s="35" t="inlineStr">
         <is>
-          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
+          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
@@ -6758,37 +6758,37 @@
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I69" s="35" t="inlineStr">
         <is>
-          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
+          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
         </is>
       </c>
       <c r="J69" s="35" t="inlineStr">
         <is>
-          <t>Complete or delete the demo record before go-live.</t>
+          <t>Confirm whether 9-digit numbers must be accepted.</t>
         </is>
       </c>
       <c r="K69" s="35" t="inlineStr">
         <is>
-          <t>Employee EMP-00001</t>
+          <t>ministry_lookup_validation.py</t>
         </is>
       </c>
       <c r="L69" s="34" t="inlineStr">
@@ -6800,7 +6800,7 @@
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>HR-54</t>
+          <t>HR-53</t>
         </is>
       </c>
       <c r="B70" s="34" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C70" s="35" t="inlineStr">
         <is>
-          <t>Website logo file missing (/files/rchs-logo.png)</t>
+          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H70" s="34" t="inlineStr">
@@ -6840,17 +6840,17 @@
       </c>
       <c r="I70" s="35" t="inlineStr">
         <is>
-          <t>Missing on the local copy; every page requests it.</t>
+          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
         </is>
       </c>
       <c r="J70" s="35" t="inlineStr">
         <is>
-          <t>Check the file exists on the live server.</t>
+          <t>Complete or delete the demo record before go-live.</t>
         </is>
       </c>
       <c r="K70" s="35" t="inlineStr">
         <is>
-          <t>Website Settings</t>
+          <t>Employee EMP-00001</t>
         </is>
       </c>
       <c r="L70" s="34" t="inlineStr">
@@ -6862,7 +6862,7 @@
     <row r="71">
       <c r="A71" s="33" t="inlineStr">
         <is>
-          <t>HR-55</t>
+          <t>HR-54</t>
         </is>
       </c>
       <c r="B71" s="34" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="C71" s="35" t="inlineStr">
         <is>
-          <t>Link the 216 existing Instructors to Employees</t>
+          <t>Website logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I71" s="35" t="inlineStr">
         <is>
-          <t>Tool ready (HR-35). 1 of 216 linked.</t>
+          <t>Missing on the local copy; every page requests it.</t>
         </is>
       </c>
       <c r="J71" s="35" t="inlineStr">
         <is>
-          <t>HR fills the Instructor data sheet; run the import with commit.</t>
+          <t>Check the file exists on the live server.</t>
         </is>
       </c>
       <c r="K71" s="35" t="inlineStr">
         <is>
-          <t>instructor_data_sheet.py</t>
+          <t>Website Settings</t>
         </is>
       </c>
       <c r="L71" s="34" t="inlineStr">
@@ -6924,17 +6924,17 @@
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-55</t>
         </is>
       </c>
       <c r="B72" s="34" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C72" s="35" t="inlineStr">
         <is>
-          <t>Connect attendance devices</t>
+          <t>Link the 216 existing Instructors to Employees</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I72" s="35" t="inlineStr">
         <is>
-          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
+          <t>Tool ready (HR-35). 1 of 216 linked.</t>
         </is>
       </c>
       <c r="J72" s="35" t="inlineStr">
         <is>
-          <t>Connect devices; map device user IDs to Employees.</t>
+          <t>HR fills the Instructor data sheet; run the import with commit.</t>
         </is>
       </c>
       <c r="K72" s="35" t="inlineStr">
         <is>
-          <t>bfac883</t>
+          <t>instructor_data_sheet.py</t>
         </is>
       </c>
       <c r="L72" s="34" t="inlineStr">
@@ -6986,7 +6986,7 @@
     <row r="73">
       <c r="A73" s="33" t="inlineStr">
         <is>
-          <t>HR-57</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="B73" s="34" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C73" s="35" t="inlineStr">
         <is>
-          <t>Set the Academic Holiday List</t>
+          <t>Connect attendance devices</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="H73" s="34" t="inlineStr">
@@ -7026,17 +7026,17 @@
       </c>
       <c r="I73" s="35" t="inlineStr">
         <is>
-          <t>Not set; the page warns about it.</t>
+          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
         </is>
       </c>
       <c r="J73" s="35" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
+          <t>Connect devices; map device user IDs to Employees.</t>
         </is>
       </c>
       <c r="K73" s="35" t="inlineStr">
         <is>
-          <t>academic_presence_setup.py</t>
+          <t>bfac883</t>
         </is>
       </c>
       <c r="L73" s="34" t="inlineStr">
@@ -7048,17 +7048,17 @@
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>HR-58</t>
+          <t>HR-57</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C74" s="35" t="inlineStr">
         <is>
-          <t>Deploy to the live server</t>
+          <t>Set the Academic Holiday List</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
@@ -7073,69 +7073,69 @@
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I74" s="35" t="inlineStr">
         <is>
-          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
+          <t>Not set; the page warns about it.</t>
         </is>
       </c>
       <c r="J74" s="35" t="inlineStr">
         <is>
-          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
+          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
         </is>
       </c>
       <c r="K74" s="35" t="inlineStr">
         <is>
-          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
+          <t>academic_presence_setup.py</t>
         </is>
       </c>
       <c r="L74" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="33" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>HR-58</t>
         </is>
       </c>
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C75" s="35" t="inlineStr">
         <is>
-          <t>Research: Jameah system, Ministry documents, view contract</t>
+          <t>Deploy to the live server</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E75" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
@@ -7150,29 +7150,29 @@
       </c>
       <c r="I75" s="35" t="inlineStr">
         <is>
-          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
+          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
         </is>
       </c>
       <c r="J75" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
         </is>
       </c>
       <c r="K75" s="35" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
         </is>
       </c>
       <c r="L75" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="B76" s="34" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="C76" s="35" t="inlineStr">
         <is>
-          <t>Ministry views for Employees (5) and Students (10)</t>
+          <t>Research: Jameah system, Ministry documents, view contract</t>
         </is>
       </c>
       <c r="D76" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="E76" s="34" t="inlineStr">
@@ -7207,22 +7207,22 @@
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I76" s="35" t="inlineStr">
         <is>
-          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
+          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
         </is>
       </c>
       <c r="J76" s="35" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K76" s="35" t="inlineStr">
         <is>
-          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="L76" s="34" t="inlineStr">
@@ -7234,7 +7234,7 @@
     <row r="77">
       <c r="A77" s="33" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="B77" s="34" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="C77" s="35" t="inlineStr">
         <is>
-          <t>Code crosswalk (Jameah Code Map)</t>
+          <t>Ministry views for Employees (5) and Students (10)</t>
         </is>
       </c>
       <c r="D77" s="34" t="inlineStr">
@@ -7269,34 +7269,34 @@
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I77" s="35" t="inlineStr">
         <is>
-          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
+          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
         </is>
       </c>
       <c r="J77" s="35" t="inlineStr">
         <is>
-          <t>Review 3 values (JM-11).</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="K77" s="35" t="inlineStr">
         <is>
-          <t>jameah/code_map.py</t>
+          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
         </is>
       </c>
       <c r="L77" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>JM-04</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="B78" s="34" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C78" s="35" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>Code crosswalk (Jameah Code Map)</t>
         </is>
       </c>
       <c r="D78" s="34" t="inlineStr">
@@ -7336,29 +7336,29 @@
       </c>
       <c r="I78" s="35" t="inlineStr">
         <is>
-          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
+          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
         </is>
       </c>
       <c r="J78" s="35" t="inlineStr">
         <is>
-          <t>Fill 6 values (JM-10).</t>
+          <t>Review 3 values (JM-11).</t>
         </is>
       </c>
       <c r="K78" s="35" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>jameah/code_map.py</t>
         </is>
       </c>
       <c r="L78" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="33" t="inlineStr">
         <is>
-          <t>JM-05</t>
+          <t>JM-04</t>
         </is>
       </c>
       <c r="B79" s="34" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="C79" s="35" t="inlineStr">
         <is>
-          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="D79" s="34" t="inlineStr">
@@ -7398,29 +7398,29 @@
       </c>
       <c r="I79" s="35" t="inlineStr">
         <is>
-          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
+          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
         </is>
       </c>
       <c r="J79" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Fill 6 values (JM-10).</t>
         </is>
       </c>
       <c r="K79" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="L79" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>JM-06</t>
+          <t>JM-05</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="C80" s="35" t="inlineStr">
         <is>
-          <t>Independent verification of every view</t>
+          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
         </is>
       </c>
       <c r="D80" s="34" t="inlineStr">
@@ -7455,34 +7455,34 @@
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I80" s="35" t="inlineStr">
         <is>
-          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
+          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
         </is>
       </c>
       <c r="J80" s="35" t="inlineStr">
         <is>
-          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K80" s="35" t="inlineStr">
         <is>
-          <t>jameah/verify.py; test_jameah.py</t>
+          <t>jameah/summary.py</t>
         </is>
       </c>
       <c r="L80" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="33" t="inlineStr">
         <is>
-          <t>JM-18</t>
+          <t>JM-06</t>
         </is>
       </c>
       <c r="B81" s="34" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="C81" s="35" t="inlineStr">
         <is>
-          <t>Ministry GPA and credit hours = the college's official figures</t>
+          <t>Independent verification of every view</t>
         </is>
       </c>
       <c r="D81" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E81" s="34" t="inlineStr">
@@ -7522,17 +7522,17 @@
       </c>
       <c r="I81" s="35" t="inlineStr">
         <is>
-          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
+          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
         </is>
       </c>
       <c r="J81" s="35" t="inlineStr">
         <is>
-          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
+          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="K81" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py; jameah/verify.py</t>
+          <t>jameah/verify.py; test_jameah.py</t>
         </is>
       </c>
       <c r="L81" s="34" t="inlineStr">
@@ -7544,7 +7544,7 @@
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>JM-19</t>
+          <t>JM-18</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
@@ -7554,22 +7554,22 @@
       </c>
       <c r="C82" s="35" t="inlineStr">
         <is>
-          <t>Hourly academic summary refresh slows the site while it runs</t>
+          <t>Ministry GPA and credit hours = the college's official figures</t>
         </is>
       </c>
       <c r="D82" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E82" s="34" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G82" s="34" t="inlineStr">
@@ -7579,34 +7579,34 @@
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I82" s="35" t="inlineStr">
         <is>
-          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
+          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
         </is>
       </c>
       <c r="J82" s="35" t="inlineStr">
         <is>
-          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
+          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
         </is>
       </c>
       <c r="K82" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py; hooks.py hourly_long</t>
+          <t>jameah/summary.py; jameah/verify.py</t>
         </is>
       </c>
       <c r="L82" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="33" t="inlineStr">
         <is>
-          <t>JM-07</t>
+          <t>JM-19</t>
         </is>
       </c>
       <c r="B83" s="34" t="inlineStr">
@@ -7616,22 +7616,22 @@
       </c>
       <c r="C83" s="35" t="inlineStr">
         <is>
-          <t>Jameah Data Check page and Employee preview</t>
+          <t>Hourly academic summary refresh slows the site while it runs</t>
         </is>
       </c>
       <c r="D83" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E83" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G83" s="34" t="inlineStr">
@@ -7641,34 +7641,34 @@
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I83" s="35" t="inlineStr">
         <is>
-          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
+          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
         </is>
       </c>
       <c r="J83" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
         </is>
       </c>
       <c r="K83" s="35" t="inlineStr">
         <is>
-          <t>page/jameah_data_check</t>
+          <t>jameah/summary.py; hooks.py hourly_long</t>
         </is>
       </c>
       <c r="L83" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>JM-08</t>
+          <t>JM-07</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
@@ -7678,27 +7678,27 @@
       </c>
       <c r="C84" s="35" t="inlineStr">
         <is>
-          <t>Read-only database account for the Ministry agent</t>
+          <t>Jameah Data Check page and Employee preview</t>
         </is>
       </c>
       <c r="D84" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E84" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G84" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H84" s="34" t="inlineStr">
@@ -7708,17 +7708,17 @@
       </c>
       <c r="I84" s="35" t="inlineStr">
         <is>
-          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
+          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
         </is>
       </c>
       <c r="J84" s="35" t="inlineStr">
         <is>
-          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K84" s="35" t="inlineStr">
         <is>
-          <t>jameah/README.md</t>
+          <t>page/jameah_data_check</t>
         </is>
       </c>
       <c r="L84" s="34" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="85">
       <c r="A85" s="33" t="inlineStr">
         <is>
-          <t>JM-09</t>
+          <t>JM-08</t>
         </is>
       </c>
       <c r="B85" s="34" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="C85" s="35" t="inlineStr">
         <is>
-          <t>Confirm view and column names with the Ministry</t>
+          <t>Read-only database account for the Ministry agent</t>
         </is>
       </c>
       <c r="D85" s="34" t="inlineStr">
@@ -7750,37 +7750,37 @@
       </c>
       <c r="E85" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G85" s="34" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I85" s="35" t="inlineStr">
         <is>
-          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
+          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
         </is>
       </c>
       <c r="J85" s="35" t="inlineStr">
         <is>
-          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
+          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
         </is>
       </c>
       <c r="K85" s="35" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>jameah/README.md</t>
         </is>
       </c>
       <c r="L85" s="34" t="inlineStr">
@@ -7792,7 +7792,7 @@
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>JM-10</t>
+          <t>JM-09</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="C86" s="35" t="inlineStr">
         <is>
-          <t>Fill Jameah Settings (6 values)</t>
+          <t>Confirm view and column names with the Ministry</t>
         </is>
       </c>
       <c r="D86" s="34" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="G86" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I86" s="35" t="inlineStr">
         <is>
-          <t>Empty values are sent as empty.</t>
+          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
         </is>
       </c>
       <c r="J86" s="35" t="inlineStr">
         <is>
-          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
+          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
         </is>
       </c>
       <c r="K86" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-settings</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="L86" s="34" t="inlineStr">
@@ -7854,7 +7854,7 @@
     <row r="87">
       <c r="A87" s="33" t="inlineStr">
         <is>
-          <t>JM-11</t>
+          <t>JM-10</t>
         </is>
       </c>
       <c r="B87" s="34" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="C87" s="35" t="inlineStr">
         <is>
-          <t>Map 3 college values to Ministry codes</t>
+          <t>Fill Jameah Settings (6 values)</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="I87" s="35" t="inlineStr">
         <is>
-          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
+          <t>Empty values are sent as empty.</t>
         </is>
       </c>
       <c r="J87" s="35" t="inlineStr">
         <is>
-          <t>Pick the code in Jameah Code Map and set Verified.</t>
+          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
         </is>
       </c>
       <c r="K87" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-code-map</t>
+          <t>/app/jameah-settings</t>
         </is>
       </c>
       <c r="L87" s="34" t="inlineStr">
@@ -7916,7 +7916,7 @@
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>JM-12</t>
+          <t>JM-11</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="C88" s="35" t="inlineStr">
         <is>
-          <t>Ministry fields with no source in the college system</t>
+          <t>Map 3 college values to Ministry codes</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
@@ -7941,44 +7941,44 @@
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs + Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G88" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I88" s="35" t="inlineStr">
         <is>
-          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
+          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
         </is>
       </c>
       <c r="J88" s="35" t="inlineStr">
         <is>
-          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
+          <t>Pick the code in Jameah Code Map and set Verified.</t>
         </is>
       </c>
       <c r="K88" s="35" t="inlineStr">
         <is>
-          <t>Jameah report; VIEWS.md</t>
+          <t>/app/jameah-code-map</t>
         </is>
       </c>
       <c r="L88" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="33" t="inlineStr">
         <is>
-          <t>JM-13</t>
+          <t>JM-12</t>
         </is>
       </c>
       <c r="B89" s="34" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="C89" s="35" t="inlineStr">
         <is>
-          <t>Correct source data found by the checks</t>
+          <t>Ministry fields with no source in the college system</t>
         </is>
       </c>
       <c r="D89" s="34" t="inlineStr">
@@ -7998,37 +7998,37 @@
       </c>
       <c r="E89" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Academic Affairs + Abdul Hakeem</t>
         </is>
       </c>
       <c r="G89" s="34" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I89" s="35" t="inlineStr">
         <is>
-          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
+          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
         </is>
       </c>
       <c r="J89" s="35" t="inlineStr">
         <is>
-          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
+          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
         </is>
       </c>
       <c r="K89" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-data-check</t>
+          <t>Jameah report; VIEWS.md</t>
         </is>
       </c>
       <c r="L89" s="34" t="inlineStr">
@@ -8040,7 +8040,7 @@
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>JM-14</t>
+          <t>JM-13</t>
         </is>
       </c>
       <c r="B90" s="34" t="inlineStr">
@@ -8050,27 +8050,27 @@
       </c>
       <c r="C90" s="35" t="inlineStr">
         <is>
-          <t>Faculty views (8 sections)</t>
+          <t>Correct source data found by the checks</t>
         </is>
       </c>
       <c r="D90" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E90" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="G90" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="H90" s="34" t="inlineStr">
@@ -8080,29 +8080,29 @@
       </c>
       <c r="I90" s="35" t="inlineStr">
         <is>
-          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
+          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
         </is>
       </c>
       <c r="J90" s="35" t="inlineStr">
         <is>
-          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
+          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
         </is>
       </c>
       <c r="K90" s="35" t="inlineStr">
         <is>
-          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
+          <t>/app/jameah-data-check</t>
         </is>
       </c>
       <c r="L90" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="33" t="inlineStr">
         <is>
-          <t>JM-15</t>
+          <t>JM-14</t>
         </is>
       </c>
       <c r="B91" s="34" t="inlineStr">
@@ -8112,17 +8112,17 @@
       </c>
       <c r="C91" s="35" t="inlineStr">
         <is>
-          <t>Institute views (20 sections)</t>
+          <t>Faculty views (8 sections)</t>
         </is>
       </c>
       <c r="D91" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E91" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F91" s="34" t="inlineStr">
@@ -8137,22 +8137,22 @@
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I91" s="35" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
         </is>
       </c>
       <c r="J91" s="35" t="inlineStr">
         <is>
-          <t>Build after Faculty; needs institute data from HR.</t>
+          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
         </is>
       </c>
       <c r="K91" s="35" t="inlineStr">
         <is>
-          <t>MINISTRY_FIELD_MAPPING.html</t>
+          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
         </is>
       </c>
       <c r="L91" s="34" t="inlineStr">
@@ -8164,7 +8164,7 @@
     <row r="92">
       <c r="A92" s="33" t="inlineStr">
         <is>
-          <t>JM-16</t>
+          <t>JM-15</t>
         </is>
       </c>
       <c r="B92" s="34" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>Old viewJameah* views (42, earlier version)</t>
+          <t>Institute views (20 sections)</t>
         </is>
       </c>
       <c r="D92" s="34" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="E92" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – development</t>
         </is>
       </c>
       <c r="F92" s="34" t="inlineStr">
@@ -8199,95 +8199,157 @@
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I92" s="35" t="inlineStr">
         <is>
-          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="J92" s="35" t="inlineStr">
         <is>
-          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+          <t>Build after Faculty; needs institute data from HR.</t>
         </is>
       </c>
       <c r="K92" s="35" t="inlineStr">
         <is>
-          <t>jameah_system (old views)</t>
+          <t>MINISTRY_FIELD_MAPPING.html</t>
         </is>
       </c>
       <c r="L92" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="33" t="inlineStr">
         <is>
+          <t>JM-16</t>
+        </is>
+      </c>
+      <c r="B93" s="34" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C93" s="35" t="inlineStr">
+        <is>
+          <t>Old viewJameah* views (42, earlier version)</t>
+        </is>
+      </c>
+      <c r="D93" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="34" t="inlineStr">
+        <is>
+          <t>Pending – decision needed</t>
+        </is>
+      </c>
+      <c r="F93" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G93" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H93" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I93" s="35" t="inlineStr">
+        <is>
+          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+        </is>
+      </c>
+      <c r="J93" s="35" t="inlineStr">
+        <is>
+          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+        </is>
+      </c>
+      <c r="K93" s="35" t="inlineStr">
+        <is>
+          <t>jameah_system (old views)</t>
+        </is>
+      </c>
+      <c r="L93" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="33" t="inlineStr">
+        <is>
           <t>JM-17</t>
         </is>
       </c>
-      <c r="B93" s="34" t="inlineStr">
+      <c r="B94" s="34" t="inlineStr">
         <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="C93" s="35" t="inlineStr">
+      <c r="C94" s="35" t="inlineStr">
         <is>
           <t>Transcript GPA rounding at exact ties</t>
         </is>
       </c>
-      <c r="D93" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E93" s="34" t="inlineStr">
+      <c r="D94" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E94" s="34" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F93" s="34" t="inlineStr">
-        <is>
-          <t>Abdul Hakeem</t>
-        </is>
-      </c>
-      <c r="G93" s="34" t="inlineStr">
-        <is>
-          <t>Abdul Hakeem</t>
-        </is>
-      </c>
-      <c r="H93" s="34" t="inlineStr">
+      <c r="F94" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G94" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H94" s="34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I93" s="35" t="inlineStr">
+      <c r="I94" s="35" t="inlineStr">
         <is>
           <t>Resolved by the college's official GPA calculation (exact half-up rounding); the Ministry views use it (JM-18).</t>
         </is>
       </c>
-      <c r="J93" s="35" t="inlineStr">
+      <c r="J94" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="K93" s="35" t="inlineStr">
+      <c r="K94" s="35" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="L93" s="34" t="inlineStr">
+      <c r="L94" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L93"/>
-  <conditionalFormatting sqref="E2:E293">
+  <autoFilter ref="A1:L94"/>
+  <conditionalFormatting sqref="E2:E294">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$E2="Done"</formula>
     </cfRule>
@@ -8313,7 +8375,7 @@
       <formula>$E2="Planned"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H293">
+  <conditionalFormatting sqref="H2:H294">
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
       <formula>$H2="Critical"</formula>
     </cfRule>
@@ -8328,13 +8390,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E2:E293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
+    <dataValidation sqref="E2:E294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
       <formula1>"Done,Done – client UAT pending,In progress,Pending – decision needed,Pending – data / setup,Pending – development,Pending – other team,Planned"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G293" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Abdul Hakeem,Fathir,Dinesh,To assign"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8348,7 +8410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10966,37 +11028,37 @@
     <row r="51">
       <c r="A51" s="34" t="inlineStr">
         <is>
-          <t>B-28</t>
+          <t>B-54</t>
         </is>
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Remote Work Request</t>
         </is>
       </c>
       <c r="D51" s="35" t="inlineStr">
         <is>
-          <t>Employees clicking the 'Medical HRMS' breadcrumb got 'Not permitted - No permission for Page'</t>
+          <t>Duration (Days) always showed 0</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Frappe chooses the breadcrumb workspace without a permission check</t>
+          <t>Read-only field that nothing calculated</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Keep only workspaces the user can open</t>
+          <t>Counted on save: working days as the monthly work-from-home limit counts them (calendar days when HR has no holiday list for the dates); a patch fills in the requests already saved</t>
         </is>
       </c>
       <c r="G51" s="34" t="inlineStr">
         <is>
-          <t>HR-59</t>
+          <t>HR-74</t>
         </is>
       </c>
       <c r="H51" s="34" t="inlineStr">
@@ -11006,71 +11068,71 @@
       </c>
       <c r="I51" s="35" t="inlineStr">
         <is>
-          <t>E2E NAV-01/02</t>
+          <t>Unit tests; E2E ESS-06</t>
         </is>
       </c>
       <c r="J51" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="34" t="inlineStr">
         <is>
-          <t>B-25</t>
+          <t>B-55</t>
         </is>
       </c>
       <c r="B52" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Permission Request</t>
         </is>
       </c>
       <c r="D52" s="35" t="inlineStr">
         <is>
-          <t>System e-mails fail: password cannot be decrypted</t>
+          <t>Duration (Hours) always showed 0, and a To Time before the From Time was accepted</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
         <is>
-          <t>Email Account 'Notifications' password encrypted with another key</t>
+          <t>Read-only field that nothing calculated; no time check</t>
         </is>
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>Re-enter the password on the server</t>
+          <t>Hours counted on save; To Time must be after From Time; a patch fills in the requests already saved</t>
         </is>
       </c>
       <c r="G52" s="34" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-74</t>
         </is>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I52" s="35" t="inlineStr">
         <is>
-          <t>Error Log</t>
+          <t>Unit tests; E2E ESS-04</t>
         </is>
       </c>
       <c r="J52" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
-          <t>B-26</t>
+          <t>B-28</t>
         </is>
       </c>
       <c r="B53" s="34" t="inlineStr">
@@ -11080,100 +11142,204 @@
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>Instructor form</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="D53" s="35" t="inlineStr">
         <is>
-          <t>Linking an Employee in the Instructor form fails</t>
+          <t>Employees clicking the 'Medical HRMS' breadcrumb got 'Not permitted - No permission for Page'</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>The form copies Ministry codes into lists that expect other values</t>
+          <t>Frappe chooses the breadcrumb workspace without a permission check</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Fix from Medical HRMS (HR-48)</t>
+          <t>Keep only workspaces the user can open</t>
         </is>
       </c>
       <c r="G53" s="34" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-59</t>
         </is>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I53" s="35" t="inlineStr">
         <is>
-          <t>Reproduced 21 Oct</t>
+          <t>E2E NAV-01/02</t>
         </is>
       </c>
       <c r="J53" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="34" t="inlineStr">
         <is>
+          <t>B-25</t>
+        </is>
+      </c>
+      <c r="B54" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C54" s="34" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="inlineStr">
+        <is>
+          <t>System e-mails fail: password cannot be decrypted</t>
+        </is>
+      </c>
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>Email Account 'Notifications' password encrypted with another key</t>
+        </is>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
+        <is>
+          <t>Re-enter the password on the server</t>
+        </is>
+      </c>
+      <c r="G54" s="34" t="inlineStr">
+        <is>
+          <t>HR-47</t>
+        </is>
+      </c>
+      <c r="H54" s="34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I54" s="35" t="inlineStr">
+        <is>
+          <t>Error Log</t>
+        </is>
+      </c>
+      <c r="J54" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>B-26</t>
+        </is>
+      </c>
+      <c r="B55" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C55" s="34" t="inlineStr">
+        <is>
+          <t>Instructor form</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="inlineStr">
+        <is>
+          <t>Linking an Employee in the Instructor form fails</t>
+        </is>
+      </c>
+      <c r="E55" s="35" t="inlineStr">
+        <is>
+          <t>The form copies Ministry codes into lists that expect other values</t>
+        </is>
+      </c>
+      <c r="F55" s="35" t="inlineStr">
+        <is>
+          <t>Fix from Medical HRMS (HR-48)</t>
+        </is>
+      </c>
+      <c r="G55" s="34" t="inlineStr">
+        <is>
+          <t>HR-48</t>
+        </is>
+      </c>
+      <c r="H55" s="34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I55" s="35" t="inlineStr">
+        <is>
+          <t>Reproduced 21 Oct</t>
+        </is>
+      </c>
+      <c r="J55" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
           <t>B-27</t>
         </is>
       </c>
-      <c r="B54" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C54" s="34" t="inlineStr">
+      <c r="B56" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="D54" s="35" t="inlineStr">
+      <c r="D56" s="35" t="inlineStr">
         <is>
           <t>Logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
-      <c r="E54" s="35" t="inlineStr">
+      <c r="E56" s="35" t="inlineStr">
         <is>
           <t>File not on this copy</t>
         </is>
       </c>
-      <c r="F54" s="35" t="inlineStr">
+      <c r="F56" s="35" t="inlineStr">
         <is>
           <t>Check on the live server</t>
         </is>
       </c>
-      <c r="G54" s="34" t="inlineStr">
+      <c r="G56" s="34" t="inlineStr">
         <is>
           <t>HR-54</t>
         </is>
       </c>
-      <c r="H54" s="34" t="inlineStr">
+      <c r="H56" s="34" t="inlineStr">
         <is>
           <t>Open – check server</t>
         </is>
       </c>
-      <c r="I54" s="35" t="inlineStr">
+      <c r="I56" s="35" t="inlineStr">
         <is>
           <t>Error sweep</t>
         </is>
       </c>
-      <c r="J54" s="34" t="inlineStr">
+      <c r="J56" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J54"/>
-  <conditionalFormatting sqref="H2:H154">
+  <autoFilter ref="A1:J56"/>
+  <conditionalFormatting sqref="H2:H156">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="Fixed"</formula>
     </cfRule>
@@ -11188,7 +11354,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Fixed,Open,Open – other team,Open – check server"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11745,7 +11911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11790,17 +11956,17 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E2" s="34" t="inlineStr">
@@ -11822,12 +11988,12 @@
       </c>
       <c r="C3" s="35" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E3" s="34" t="inlineStr">
@@ -11844,17 +12010,17 @@
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D4" s="35" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E4" s="34" t="inlineStr">
@@ -11866,7 +12032,7 @@
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="34" t="inlineStr">
@@ -11876,12 +12042,12 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -11903,12 +12069,12 @@
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -11925,17 +12091,17 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -11947,22 +12113,22 @@
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -11979,17 +12145,17 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -12006,17 +12172,17 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -12028,7 +12194,7 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
@@ -12038,12 +12204,12 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -12055,7 +12221,7 @@
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
@@ -12065,12 +12231,12 @@
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -12082,32 +12248,59 @@
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4980,12 +4980,12 @@
       </c>
       <c r="I40" s="35" t="inlineStr">
         <is>
-          <t>Exam Committee proctor assignments by date, time and room.</t>
+          <t>Exam Committee proctor assignments by date, time and room. 23 Oct: the system has no exam committees yet, so the tab is empty (shown in the User Guide).</t>
         </is>
       </c>
       <c r="J40" s="35" t="inlineStr">
         <is>
-          <t>Needs real exam committees in the system to show data.</t>
+          <t>Enter the exam committees with their proctors (Checklist CL-38).</t>
         </is>
       </c>
       <c r="K40" s="35" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L40" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="I41" s="35" t="inlineStr">
         <is>
-          <t>Hourly expected / present / absent. Tested: 8 Sep 2026 = 858 expected, 397 present (matches attendance).</t>
+          <t>Hourly expected / present / absent (one-hour slots, 7:00-22:00). Tested: 8 Sep 2026 = 858 expected, 397 present (matches attendance).</t>
         </is>
       </c>
       <c r="J41" s="35" t="inlineStr">
         <is>
-          <t>HR UAT.</t>
+          <t>HR UAT; the client asked for each period: one-hour slots or the college's own periods (DEC-15).</t>
         </is>
       </c>
       <c r="K41" s="35" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="L41" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11899,8 +11899,42 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>DEC-15</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Students on Campus: keep one-hour slots (as built, 7:00-22:00) or count by the college's own teaching periods? The client's request says 'during each period'.</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>HR (client)</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Review at the progress meeting; periods would need their start and end times.</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>HR-38</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="inlineStr"/>
+      <c r="G16" s="37" t="inlineStr"/>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11911,7 +11945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11961,12 +11995,12 @@
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E2" s="34" t="inlineStr">
@@ -11983,17 +12017,17 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C3" s="35" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E3" s="34" t="inlineStr">
@@ -12015,12 +12049,12 @@
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D4" s="35" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E4" s="34" t="inlineStr">
@@ -12037,17 +12071,17 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -12059,7 +12093,7 @@
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
@@ -12069,12 +12103,12 @@
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -12096,12 +12130,12 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -12118,17 +12152,17 @@
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -12140,22 +12174,22 @@
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -12172,17 +12206,17 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -12199,17 +12233,17 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -12221,7 +12255,7 @@
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
@@ -12231,12 +12265,12 @@
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -12248,7 +12282,7 @@
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
@@ -12258,12 +12292,12 @@
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
@@ -12275,32 +12309,59 @@
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -15,10 +15,10 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -791,7 +791,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Al-Riyada College for Health Sciences · last updated 23 Oct 2026</t>
+          <t>Al-Riyada College for Health Sciences · last updated 27 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Counts are formulas over the Tasks and Bugs sheets. As of 23 Oct 2026.</t>
+          <t>Counts are formulas over the Tasks and Bugs sheets. As of 27 Oct 2026.</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$294,A5)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$295,A5)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$294,A6)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$295,A6)</f>
         <v/>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$294,A7)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$295,A7)</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="B8" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$294,A8)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$295,A8)</f>
         <v/>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$294,A9)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$295,A9)</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$294,A10)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$295,A10)</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$294,A11)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$295,A11)</f>
         <v/>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B12" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$294,A12)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$295,A12)</f>
         <v/>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B16" s="23">
-        <f>COUNTIFS(Tasks!$A$2:$A$294,"HR-*",Tasks!$E$2:$E$294,"Done")+COUNTIFS(Tasks!$A$2:$A$294,"HR-*",Tasks!$E$2:$E$294,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$295,"HR-*",Tasks!$E$2:$E$295,"Done")+COUNTIFS(Tasks!$A$2:$A$295,"HR-*",Tasks!$E$2:$E$295,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C16" s="23">
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>COUNTIF(Tasks!$A$2:$A$294,"HR-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$295,"HR-*")</f>
         <v/>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="B17" s="23">
-        <f>COUNTIFS(Tasks!$A$2:$A$294,"JM-*",Tasks!$E$2:$E$294,"Done")+COUNTIFS(Tasks!$A$2:$A$294,"JM-*",Tasks!$E$2:$E$294,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$295,"JM-*",Tasks!$E$2:$E$295,"Done")+COUNTIFS(Tasks!$A$2:$A$295,"JM-*",Tasks!$E$2:$E$295,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C17" s="23">
@@ -1298,7 +1298,7 @@
         <v/>
       </c>
       <c r="D17" s="23">
-        <f>COUNTIF(Tasks!$A$2:$A$294,"JM-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$295,"JM-*")</f>
         <v/>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B20" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$294,"Earlier (May – 5 Oct 2026)")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$295,"Earlier (May – 5 Oct 2026)")</f>
         <v/>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B21" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$294,"19 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$295,"19 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B22" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$294,"20 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$295,"20 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B23" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$294,"21 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$295,"21 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="B24" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$294,"22 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$295,"22 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1377,1091 +1377,1091 @@
         </is>
       </c>
       <c r="B25" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$294,"23 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$295,"23 Oct 2026")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B26" s="23">
+        <f>COUNTIF(Tasks!$D$2:$D$295,"27 Oct 2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
           <t>— (not done yet)</t>
         </is>
       </c>
-      <c r="B26" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$294,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="B27" s="23">
+        <f>COUNTIF(Tasks!$D$2:$D$295,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>Done – client UAT pending</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>Pending – decision needed</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>Pending – data / setup</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>Pending – development</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Pending – other team</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J29" s="21" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="B29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,B$28)</f>
-        <v/>
-      </c>
-      <c r="C29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,C$28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,D$28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,E$28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,F$28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,G$28)</f>
-        <v/>
-      </c>
-      <c r="H29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,H$28)</f>
-        <v/>
-      </c>
-      <c r="I29" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A29,Tasks!$E$2:$E$294,I$28)</f>
-        <v/>
-      </c>
-      <c r="J29" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A29)</f>
-        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>Master data</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="B30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A30,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J30" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A30)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Master data</t>
         </is>
       </c>
       <c r="B31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A31,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J31" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A31)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="B32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A32,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J32" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A32)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>HR dashboard</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="B33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A33,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J33" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A33)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Self-service</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="B34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A34,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J34" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A34)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Self-service</t>
         </is>
       </c>
       <c r="B35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A35,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J35" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A35)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="23" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A36,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J36" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A36)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="B37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A37,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J37" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A37)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="23" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="B38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A38,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J38" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A38)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="B39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A39,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J39" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A39)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="B40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A40,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J40" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A40)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="B41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A41,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J41" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A41)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="B42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A42,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J42" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A42)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="B43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A43,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J43" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A43)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
         <is>
-          <t>Employee master</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="B44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A44,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J44" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A44)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>Requests</t>
+          <t>Employee master</t>
         </is>
       </c>
       <c r="B45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A45,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J45" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A45)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="23" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Requests</t>
         </is>
       </c>
       <c r="B46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A46,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J46" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A46)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A47,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J47" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A47)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="23" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="B48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A48,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J48" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A48)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A49,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J49" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A49)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,B$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,B$29)</f>
         <v/>
       </c>
       <c r="C50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,C$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,C$29)</f>
         <v/>
       </c>
       <c r="D50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,D$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,D$29)</f>
         <v/>
       </c>
       <c r="E50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,E$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,E$29)</f>
         <v/>
       </c>
       <c r="F50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,F$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,F$29)</f>
         <v/>
       </c>
       <c r="G50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,G$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,G$29)</f>
         <v/>
       </c>
       <c r="H50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,H$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,H$29)</f>
         <v/>
       </c>
       <c r="I50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A50,Tasks!$E$2:$E$294,I$28)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,I$29)</f>
         <v/>
       </c>
       <c r="J50" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A50)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B51" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,B$29)</f>
+        <v/>
+      </c>
+      <c r="C51" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,C$29)</f>
+        <v/>
+      </c>
+      <c r="D51" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,D$29)</f>
+        <v/>
+      </c>
+      <c r="E51" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,E$29)</f>
+        <v/>
+      </c>
+      <c r="F51" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,F$29)</f>
+        <v/>
+      </c>
+      <c r="G51" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,G$29)</f>
+        <v/>
+      </c>
+      <c r="H51" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,H$29)</f>
+        <v/>
+      </c>
+      <c r="I51" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,I$29)</f>
+        <v/>
+      </c>
+      <c r="J51" s="23">
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="B51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,B$28)</f>
-        <v/>
-      </c>
-      <c r="C51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,C$28)</f>
-        <v/>
-      </c>
-      <c r="D51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,D$28)</f>
-        <v/>
-      </c>
-      <c r="E51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,E$28)</f>
-        <v/>
-      </c>
-      <c r="F51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,F$28)</f>
-        <v/>
-      </c>
-      <c r="G51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,G$28)</f>
-        <v/>
-      </c>
-      <c r="H51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,H$28)</f>
-        <v/>
-      </c>
-      <c r="I51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$294,$A51,Tasks!$E$2:$E$294,I$28)</f>
-        <v/>
-      </c>
-      <c r="J51" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$294,$A51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="B52" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,B$29)</f>
+        <v/>
+      </c>
+      <c r="C52" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,C$29)</f>
+        <v/>
+      </c>
+      <c r="D52" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,D$29)</f>
+        <v/>
+      </c>
+      <c r="E52" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,E$29)</f>
+        <v/>
+      </c>
+      <c r="F52" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,F$29)</f>
+        <v/>
+      </c>
+      <c r="G52" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,G$29)</f>
+        <v/>
+      </c>
+      <c r="H52" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,H$29)</f>
+        <v/>
+      </c>
+      <c r="I52" s="23">
+        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,I$29)</f>
+        <v/>
+      </c>
+      <c r="J52" s="23">
+        <f>COUNTIF(Tasks!$B$2:$B$295,$A52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>Bugs</t>
         </is>
       </c>
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B54" s="21" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>Fixed</t>
-        </is>
-      </c>
-      <c r="B54" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$156,A54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="32" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="B55" s="23">
@@ -2470,9 +2470,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
-        <is>
-          <t>Open – other team</t>
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="B56" s="23">
@@ -2481,13 +2481,24 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>Open – check server</t>
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>Open – other team</t>
         </is>
       </c>
       <c r="B57" s="23">
         <f>COUNTIF(Bugs!$H$2:$H$156,A57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>Open – check server</t>
+        </is>
+      </c>
+      <c r="B58" s="23">
+        <f>COUNTIF(Bugs!$H$2:$H$156,A58)</f>
         <v/>
       </c>
     </row>
@@ -2502,7 +2513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6180,27 +6191,27 @@
     <row r="60">
       <c r="A60" s="33" t="inlineStr">
         <is>
-          <t>HR-74</t>
+          <t>HR-75</t>
         </is>
       </c>
       <c r="B60" s="34" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C60" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide and User Guide (PDF)</t>
+          <t>Testing team UAT round: test cases and guides</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr">
@@ -6210,7 +6221,7 @@
       </c>
       <c r="G60" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Testing team</t>
         </is>
       </c>
       <c r="H60" s="34" t="inlineStr">
@@ -6220,44 +6231,44 @@
       </c>
       <c r="I60" s="35" t="inlineStr">
         <is>
-          <t>Two PDF guides in docs/guides: Installation and Setup Guide (21 pages: install, update, checks, first-time setup, leave year, sick leave, Jameah setup, Ministry agent account, staff data sheets, testing, troubleshooting, commands) and User Guide (30 pages: Employee Portal and the leave flow, every request, HR Portal, leave approvals and returns, recruitment, Ministry data, Academic Presence, Jameah pages, approvers, how to test and report bugs, Q&amp;A). 31 screenshots from the test site with QA test data only. Sources (HTML) and build.py kept in docs/guides/src so the guides can be rebuilt after changes. Writing them found two bugs (B-54, B-55). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>27 Oct: Abdul Hakeem gave the testing team the Test Cases workbook (130 cases, 12 modules) and both PDF guides (User Guide, Installation and Setup Guide); testing started. They record each result and any bug in the Test Cases workbook.</t>
         </is>
       </c>
       <c r="J60" s="35" t="inlineStr">
         <is>
-          <t>HR, managers and the testing team read the User Guide; the server admin the Installation Guide (Checklist CL-37). Rebuild after changes: python docs/guides/src/build.py.</t>
+          <t>Collect their results and bug reports; fix the bugs, retest and mark them in the Bugs sheet (Checklist CL-23).</t>
         </is>
       </c>
       <c r="K60" s="35" t="inlineStr">
         <is>
-          <t>docs/guides</t>
+          <t>Test Cases workbook; docs/guides</t>
         </is>
       </c>
       <c r="L60" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="33" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-74</t>
         </is>
       </c>
       <c r="B61" s="34" t="inlineStr">
         <is>
-          <t>HR dashboard</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C61" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college design</t>
+          <t>Installation and Setup Guide and User Guide (PDF)</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
@@ -6282,17 +6293,17 @@
       </c>
       <c r="I61" s="35" t="inlineStr">
         <is>
-          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
+          <t>Two PDF guides in docs/guides: Installation and Setup Guide (21 pages: install, update, checks, first-time setup, leave year, sick leave, Jameah setup, Ministry agent account, staff data sheets, testing, troubleshooting, commands) and User Guide (30 pages: Employee Portal and the leave flow, every request, HR Portal, leave approvals and returns, recruitment, Ministry data, Academic Presence, Jameah pages, approvers, how to test and report bugs, Q&amp;A). 31 screenshots from the test site with QA test data only. Sources (HTML) and build.py kept in docs/guides/src so the guides can be rebuilt after changes. Writing them found two bugs (B-54, B-55). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="J61" s="35" t="inlineStr">
         <is>
-          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
+          <t>HR, managers and the testing team read the User Guide; the server admin the Installation Guide (Checklist CL-37). Rebuild after changes: python docs/guides/src/build.py.</t>
         </is>
       </c>
       <c r="K61" s="35" t="inlineStr">
         <is>
-          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
+          <t>docs/guides</t>
         </is>
       </c>
       <c r="L61" s="34" t="inlineStr">
@@ -6304,17 +6315,17 @@
     <row r="62">
       <c r="A62" s="33" t="inlineStr">
         <is>
-          <t>HR-62</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="B62" s="34" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="C62" s="35" t="inlineStr">
         <is>
-          <t>HR User could not open the Holiday List ('Not permitted')</t>
+          <t>HR Portal and Employee Portal in the new college design</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
@@ -6339,44 +6350,44 @@
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I62" s="35" t="inlineStr">
         <is>
-          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
+          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
         </is>
       </c>
       <c r="J62" s="35" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
         </is>
       </c>
       <c r="K62" s="35" t="inlineStr">
         <is>
-          <t>hr_core_permissions.py</t>
+          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
         </is>
       </c>
       <c r="L62" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="33" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-62</t>
         </is>
       </c>
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C63" s="35" t="inlineStr">
         <is>
-          <t>Full end-to-end test with error sweep (round 3)</t>
+          <t>HR User could not open the Holiday List ('Not permitted')</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
@@ -6401,22 +6412,22 @@
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I63" s="35" t="inlineStr">
         <is>
-          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
+          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
         </is>
       </c>
       <c r="J63" s="35" t="inlineStr">
         <is>
-          <t>Client UAT.</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="K63" s="35" t="inlineStr">
         <is>
-          <t>Test Report</t>
+          <t>hr_core_permissions.py</t>
         </is>
       </c>
       <c r="L63" s="34" t="inlineStr">
@@ -6428,37 +6439,37 @@
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-46</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C64" s="35" t="inlineStr">
         <is>
-          <t>System e-mail account password cannot be decrypted</t>
+          <t>Full end-to-end test with error sweep (round 3)</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H64" s="34" t="inlineStr">
@@ -6468,17 +6479,17 @@
       </c>
       <c r="I64" s="35" t="inlineStr">
         <is>
-          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
+          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
         </is>
       </c>
       <c r="J64" s="35" t="inlineStr">
         <is>
-          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
+          <t>Client UAT.</t>
         </is>
       </c>
       <c r="K64" s="35" t="inlineStr">
         <is>
-          <t>Error Log; Email Queue</t>
+          <t>Test Report</t>
         </is>
       </c>
       <c r="L64" s="34" t="inlineStr">
@@ -6490,17 +6501,17 @@
     <row r="65">
       <c r="A65" s="33" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-47</t>
         </is>
       </c>
       <c r="B65" s="34" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C65" s="35" t="inlineStr">
         <is>
-          <t>Instructor form: linking an Employee fails on save</t>
+          <t>System e-mail account password cannot be decrypted</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
@@ -6510,69 +6521,69 @@
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G65" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I65" s="35" t="inlineStr">
         <is>
-          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
+          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
         </is>
       </c>
       <c r="J65" s="35" t="inlineStr">
         <is>
-          <t>Fix it from Medical HRMS: give the Instructor form the matching value when it copies gender / department from the Employee.</t>
+          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
         </is>
       </c>
       <c r="K65" s="35" t="inlineStr">
         <is>
-          <t>Instructor form; medical_hrms</t>
+          <t>Error Log; Email Queue</t>
         </is>
       </c>
       <c r="L65" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>HR-49</t>
+          <t>HR-48</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C66" s="35" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Instructor form: linking an Employee fails on save</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E66" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – development</t>
         </is>
       </c>
       <c r="F66" s="34" t="inlineStr">
@@ -6592,29 +6603,29 @@
       </c>
       <c r="I66" s="35" t="inlineStr">
         <is>
-          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
+          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
         </is>
       </c>
       <c r="J66" s="35" t="inlineStr">
         <is>
-          <t>HR to use it to complete the data (HR-50 sheet).</t>
+          <t>Fix it from Medical HRMS: give the Instructor form the matching value when it copies gender / department from the Employee.</t>
         </is>
       </c>
       <c r="K66" s="35" t="inlineStr">
         <is>
-          <t>report/employees_missing_ministry_data</t>
+          <t>Instructor form; medical_hrms</t>
         </is>
       </c>
       <c r="L66" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="33" t="inlineStr">
         <is>
-          <t>HR-50</t>
+          <t>HR-49</t>
         </is>
       </c>
       <c r="B67" s="34" t="inlineStr">
@@ -6624,7 +6635,7 @@
       </c>
       <c r="C67" s="35" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
@@ -6654,17 +6665,17 @@
       </c>
       <c r="I67" s="35" t="inlineStr">
         <is>
-          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
+          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
         </is>
       </c>
       <c r="J67" s="35" t="inlineStr">
         <is>
-          <t>HR to fill the sheet for all non-academic staff.</t>
+          <t>HR to use it to complete the data (HR-50 sheet).</t>
         </is>
       </c>
       <c r="K67" s="35" t="inlineStr">
         <is>
-          <t>employee_data_sheet.py</t>
+          <t>report/employees_missing_ministry_data</t>
         </is>
       </c>
       <c r="L67" s="34" t="inlineStr">
@@ -6676,17 +6687,17 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>HR-51</t>
+          <t>HR-50</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C68" s="35" t="inlineStr">
         <is>
-          <t>Unused duplicate of the applicant Ministry fields removed</t>
+          <t>Data sheet for non-academic staff</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
@@ -6711,22 +6722,22 @@
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I68" s="35" t="inlineStr">
         <is>
-          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
+          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
         </is>
       </c>
       <c r="J68" s="35" t="inlineStr">
         <is>
-          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
+          <t>HR to fill the sheet for all non-academic staff.</t>
         </is>
       </c>
       <c r="K68" s="35" t="inlineStr">
         <is>
-          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
+          <t>employee_data_sheet.py</t>
         </is>
       </c>
       <c r="L68" s="34" t="inlineStr">
@@ -6738,57 +6749,57 @@
     <row r="69">
       <c r="A69" s="33" t="inlineStr">
         <is>
-          <t>HR-52</t>
+          <t>HR-51</t>
         </is>
       </c>
       <c r="B69" s="34" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C69" s="35" t="inlineStr">
         <is>
-          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
+          <t>Unused duplicate of the applicant Ministry fields removed</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I69" s="35" t="inlineStr">
         <is>
-          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
+          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
         </is>
       </c>
       <c r="J69" s="35" t="inlineStr">
         <is>
-          <t>Confirm whether 9-digit numbers must be accepted.</t>
+          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
         </is>
       </c>
       <c r="K69" s="35" t="inlineStr">
         <is>
-          <t>ministry_lookup_validation.py</t>
+          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
         </is>
       </c>
       <c r="L69" s="34" t="inlineStr">
@@ -6800,17 +6811,17 @@
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>HR-53</t>
+          <t>HR-52</t>
         </is>
       </c>
       <c r="B70" s="34" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C70" s="35" t="inlineStr">
         <is>
-          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
+          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
@@ -6820,37 +6831,37 @@
       </c>
       <c r="E70" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I70" s="35" t="inlineStr">
         <is>
-          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
+          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
         </is>
       </c>
       <c r="J70" s="35" t="inlineStr">
         <is>
-          <t>Complete or delete the demo record before go-live.</t>
+          <t>Confirm whether 9-digit numbers must be accepted.</t>
         </is>
       </c>
       <c r="K70" s="35" t="inlineStr">
         <is>
-          <t>Employee EMP-00001</t>
+          <t>ministry_lookup_validation.py</t>
         </is>
       </c>
       <c r="L70" s="34" t="inlineStr">
@@ -6862,7 +6873,7 @@
     <row r="71">
       <c r="A71" s="33" t="inlineStr">
         <is>
-          <t>HR-54</t>
+          <t>HR-53</t>
         </is>
       </c>
       <c r="B71" s="34" t="inlineStr">
@@ -6872,7 +6883,7 @@
       </c>
       <c r="C71" s="35" t="inlineStr">
         <is>
-          <t>Website logo file missing (/files/rchs-logo.png)</t>
+          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
@@ -6887,12 +6898,12 @@
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H71" s="34" t="inlineStr">
@@ -6902,17 +6913,17 @@
       </c>
       <c r="I71" s="35" t="inlineStr">
         <is>
-          <t>Missing on the local copy; every page requests it.</t>
+          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
         </is>
       </c>
       <c r="J71" s="35" t="inlineStr">
         <is>
-          <t>Check the file exists on the live server.</t>
+          <t>Complete or delete the demo record before go-live.</t>
         </is>
       </c>
       <c r="K71" s="35" t="inlineStr">
         <is>
-          <t>Website Settings</t>
+          <t>Employee EMP-00001</t>
         </is>
       </c>
       <c r="L71" s="34" t="inlineStr">
@@ -6924,7 +6935,7 @@
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>HR-55</t>
+          <t>HR-54</t>
         </is>
       </c>
       <c r="B72" s="34" t="inlineStr">
@@ -6934,7 +6945,7 @@
       </c>
       <c r="C72" s="35" t="inlineStr">
         <is>
-          <t>Link the 216 existing Instructors to Employees</t>
+          <t>Website logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
@@ -6949,32 +6960,32 @@
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I72" s="35" t="inlineStr">
         <is>
-          <t>Tool ready (HR-35). 1 of 216 linked.</t>
+          <t>Missing on the local copy; every page requests it.</t>
         </is>
       </c>
       <c r="J72" s="35" t="inlineStr">
         <is>
-          <t>HR fills the Instructor data sheet; run the import with commit.</t>
+          <t>Check the file exists on the live server.</t>
         </is>
       </c>
       <c r="K72" s="35" t="inlineStr">
         <is>
-          <t>instructor_data_sheet.py</t>
+          <t>Website Settings</t>
         </is>
       </c>
       <c r="L72" s="34" t="inlineStr">
@@ -6986,17 +6997,17 @@
     <row r="73">
       <c r="A73" s="33" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-55</t>
         </is>
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C73" s="35" t="inlineStr">
         <is>
-          <t>Connect attendance devices</t>
+          <t>Link the 216 existing Instructors to Employees</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
@@ -7011,32 +7022,32 @@
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I73" s="35" t="inlineStr">
         <is>
-          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
+          <t>Tool ready (HR-35). 1 of 216 linked.</t>
         </is>
       </c>
       <c r="J73" s="35" t="inlineStr">
         <is>
-          <t>Connect devices; map device user IDs to Employees.</t>
+          <t>HR fills the Instructor data sheet; run the import with commit.</t>
         </is>
       </c>
       <c r="K73" s="35" t="inlineStr">
         <is>
-          <t>bfac883</t>
+          <t>instructor_data_sheet.py</t>
         </is>
       </c>
       <c r="L73" s="34" t="inlineStr">
@@ -7048,7 +7059,7 @@
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>HR-57</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
@@ -7058,7 +7069,7 @@
       </c>
       <c r="C74" s="35" t="inlineStr">
         <is>
-          <t>Set the Academic Holiday List</t>
+          <t>Connect attendance devices</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
@@ -7073,12 +7084,12 @@
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="H74" s="34" t="inlineStr">
@@ -7088,17 +7099,17 @@
       </c>
       <c r="I74" s="35" t="inlineStr">
         <is>
-          <t>Not set; the page warns about it.</t>
+          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
         </is>
       </c>
       <c r="J74" s="35" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
+          <t>Connect devices; map device user IDs to Employees.</t>
         </is>
       </c>
       <c r="K74" s="35" t="inlineStr">
         <is>
-          <t>academic_presence_setup.py</t>
+          <t>bfac883</t>
         </is>
       </c>
       <c r="L74" s="34" t="inlineStr">
@@ -7110,17 +7121,17 @@
     <row r="75">
       <c r="A75" s="33" t="inlineStr">
         <is>
-          <t>HR-58</t>
+          <t>HR-57</t>
         </is>
       </c>
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C75" s="35" t="inlineStr">
         <is>
-          <t>Deploy to the live server</t>
+          <t>Set the Academic Holiday List</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
@@ -7135,69 +7146,69 @@
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I75" s="35" t="inlineStr">
         <is>
-          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
+          <t>Not set; the page warns about it.</t>
         </is>
       </c>
       <c r="J75" s="35" t="inlineStr">
         <is>
-          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
+          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
         </is>
       </c>
       <c r="K75" s="35" t="inlineStr">
         <is>
-          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
+          <t>academic_presence_setup.py</t>
         </is>
       </c>
       <c r="L75" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>HR-58</t>
         </is>
       </c>
       <c r="B76" s="34" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C76" s="35" t="inlineStr">
         <is>
-          <t>Research: Jameah system, Ministry documents, view contract</t>
+          <t>Deploy to the live server</t>
         </is>
       </c>
       <c r="D76" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E76" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
@@ -7212,29 +7223,29 @@
       </c>
       <c r="I76" s="35" t="inlineStr">
         <is>
-          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
+          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
         </is>
       </c>
       <c r="J76" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
         </is>
       </c>
       <c r="K76" s="35" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
         </is>
       </c>
       <c r="L76" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="33" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="B77" s="34" t="inlineStr">
@@ -7244,12 +7255,12 @@
       </c>
       <c r="C77" s="35" t="inlineStr">
         <is>
-          <t>Ministry views for Employees (5) and Students (10)</t>
+          <t>Research: Jameah system, Ministry documents, view contract</t>
         </is>
       </c>
       <c r="D77" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="E77" s="34" t="inlineStr">
@@ -7269,22 +7280,22 @@
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I77" s="35" t="inlineStr">
         <is>
-          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
+          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
         </is>
       </c>
       <c r="J77" s="35" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K77" s="35" t="inlineStr">
         <is>
-          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="L77" s="34" t="inlineStr">
@@ -7296,7 +7307,7 @@
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="B78" s="34" t="inlineStr">
@@ -7306,7 +7317,7 @@
       </c>
       <c r="C78" s="35" t="inlineStr">
         <is>
-          <t>Code crosswalk (Jameah Code Map)</t>
+          <t>Ministry views for Employees (5) and Students (10)</t>
         </is>
       </c>
       <c r="D78" s="34" t="inlineStr">
@@ -7331,34 +7342,34 @@
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I78" s="35" t="inlineStr">
         <is>
-          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
+          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
         </is>
       </c>
       <c r="J78" s="35" t="inlineStr">
         <is>
-          <t>Review 3 values (JM-11).</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="K78" s="35" t="inlineStr">
         <is>
-          <t>jameah/code_map.py</t>
+          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
         </is>
       </c>
       <c r="L78" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="33" t="inlineStr">
         <is>
-          <t>JM-04</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="B79" s="34" t="inlineStr">
@@ -7368,7 +7379,7 @@
       </c>
       <c r="C79" s="35" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>Code crosswalk (Jameah Code Map)</t>
         </is>
       </c>
       <c r="D79" s="34" t="inlineStr">
@@ -7398,29 +7409,29 @@
       </c>
       <c r="I79" s="35" t="inlineStr">
         <is>
-          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
+          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
         </is>
       </c>
       <c r="J79" s="35" t="inlineStr">
         <is>
-          <t>Fill 6 values (JM-10).</t>
+          <t>Review 3 values (JM-11).</t>
         </is>
       </c>
       <c r="K79" s="35" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>jameah/code_map.py</t>
         </is>
       </c>
       <c r="L79" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>JM-05</t>
+          <t>JM-04</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
@@ -7430,7 +7441,7 @@
       </c>
       <c r="C80" s="35" t="inlineStr">
         <is>
-          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="D80" s="34" t="inlineStr">
@@ -7460,29 +7471,29 @@
       </c>
       <c r="I80" s="35" t="inlineStr">
         <is>
-          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
+          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
         </is>
       </c>
       <c r="J80" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Fill 6 values (JM-10).</t>
         </is>
       </c>
       <c r="K80" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="L80" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="33" t="inlineStr">
         <is>
-          <t>JM-06</t>
+          <t>JM-05</t>
         </is>
       </c>
       <c r="B81" s="34" t="inlineStr">
@@ -7492,7 +7503,7 @@
       </c>
       <c r="C81" s="35" t="inlineStr">
         <is>
-          <t>Independent verification of every view</t>
+          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
         </is>
       </c>
       <c r="D81" s="34" t="inlineStr">
@@ -7517,34 +7528,34 @@
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I81" s="35" t="inlineStr">
         <is>
-          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
+          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
         </is>
       </c>
       <c r="J81" s="35" t="inlineStr">
         <is>
-          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K81" s="35" t="inlineStr">
         <is>
-          <t>jameah/verify.py; test_jameah.py</t>
+          <t>jameah/summary.py</t>
         </is>
       </c>
       <c r="L81" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>JM-18</t>
+          <t>JM-06</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
@@ -7554,12 +7565,12 @@
       </c>
       <c r="C82" s="35" t="inlineStr">
         <is>
-          <t>Ministry GPA and credit hours = the college's official figures</t>
+          <t>Independent verification of every view</t>
         </is>
       </c>
       <c r="D82" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E82" s="34" t="inlineStr">
@@ -7584,17 +7595,17 @@
       </c>
       <c r="I82" s="35" t="inlineStr">
         <is>
-          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
+          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
         </is>
       </c>
       <c r="J82" s="35" t="inlineStr">
         <is>
-          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
+          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="K82" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py; jameah/verify.py</t>
+          <t>jameah/verify.py; test_jameah.py</t>
         </is>
       </c>
       <c r="L82" s="34" t="inlineStr">
@@ -7606,7 +7617,7 @@
     <row r="83">
       <c r="A83" s="33" t="inlineStr">
         <is>
-          <t>JM-19</t>
+          <t>JM-18</t>
         </is>
       </c>
       <c r="B83" s="34" t="inlineStr">
@@ -7616,22 +7627,22 @@
       </c>
       <c r="C83" s="35" t="inlineStr">
         <is>
-          <t>Hourly academic summary refresh slows the site while it runs</t>
+          <t>Ministry GPA and credit hours = the college's official figures</t>
         </is>
       </c>
       <c r="D83" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E83" s="34" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G83" s="34" t="inlineStr">
@@ -7641,34 +7652,34 @@
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I83" s="35" t="inlineStr">
         <is>
-          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
+          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
         </is>
       </c>
       <c r="J83" s="35" t="inlineStr">
         <is>
-          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
+          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
         </is>
       </c>
       <c r="K83" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py; hooks.py hourly_long</t>
+          <t>jameah/summary.py; jameah/verify.py</t>
         </is>
       </c>
       <c r="L83" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>JM-07</t>
+          <t>JM-19</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
@@ -7678,22 +7689,22 @@
       </c>
       <c r="C84" s="35" t="inlineStr">
         <is>
-          <t>Jameah Data Check page and Employee preview</t>
+          <t>Hourly academic summary refresh slows the site while it runs</t>
         </is>
       </c>
       <c r="D84" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E84" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G84" s="34" t="inlineStr">
@@ -7703,34 +7714,34 @@
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I84" s="35" t="inlineStr">
         <is>
-          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
+          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
         </is>
       </c>
       <c r="J84" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
         </is>
       </c>
       <c r="K84" s="35" t="inlineStr">
         <is>
-          <t>page/jameah_data_check</t>
+          <t>jameah/summary.py; hooks.py hourly_long</t>
         </is>
       </c>
       <c r="L84" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="33" t="inlineStr">
         <is>
-          <t>JM-08</t>
+          <t>JM-07</t>
         </is>
       </c>
       <c r="B85" s="34" t="inlineStr">
@@ -7740,27 +7751,27 @@
       </c>
       <c r="C85" s="35" t="inlineStr">
         <is>
-          <t>Read-only database account for the Ministry agent</t>
+          <t>Jameah Data Check page and Employee preview</t>
         </is>
       </c>
       <c r="D85" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E85" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G85" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H85" s="34" t="inlineStr">
@@ -7770,17 +7781,17 @@
       </c>
       <c r="I85" s="35" t="inlineStr">
         <is>
-          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
+          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
         </is>
       </c>
       <c r="J85" s="35" t="inlineStr">
         <is>
-          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K85" s="35" t="inlineStr">
         <is>
-          <t>jameah/README.md</t>
+          <t>page/jameah_data_check</t>
         </is>
       </c>
       <c r="L85" s="34" t="inlineStr">
@@ -7792,7 +7803,7 @@
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>JM-09</t>
+          <t>JM-08</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -7802,7 +7813,7 @@
       </c>
       <c r="C86" s="35" t="inlineStr">
         <is>
-          <t>Confirm view and column names with the Ministry</t>
+          <t>Read-only database account for the Ministry agent</t>
         </is>
       </c>
       <c r="D86" s="34" t="inlineStr">
@@ -7812,37 +7823,37 @@
       </c>
       <c r="E86" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G86" s="34" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I86" s="35" t="inlineStr">
         <is>
-          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
+          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
         </is>
       </c>
       <c r="J86" s="35" t="inlineStr">
         <is>
-          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
+          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
         </is>
       </c>
       <c r="K86" s="35" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>jameah/README.md</t>
         </is>
       </c>
       <c r="L86" s="34" t="inlineStr">
@@ -7854,7 +7865,7 @@
     <row r="87">
       <c r="A87" s="33" t="inlineStr">
         <is>
-          <t>JM-10</t>
+          <t>JM-09</t>
         </is>
       </c>
       <c r="B87" s="34" t="inlineStr">
@@ -7864,7 +7875,7 @@
       </c>
       <c r="C87" s="35" t="inlineStr">
         <is>
-          <t>Fill Jameah Settings (6 values)</t>
+          <t>Confirm view and column names with the Ministry</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
@@ -7879,32 +7890,32 @@
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="G87" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I87" s="35" t="inlineStr">
         <is>
-          <t>Empty values are sent as empty.</t>
+          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
         </is>
       </c>
       <c r="J87" s="35" t="inlineStr">
         <is>
-          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
+          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
         </is>
       </c>
       <c r="K87" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-settings</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="L87" s="34" t="inlineStr">
@@ -7916,7 +7927,7 @@
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>JM-11</t>
+          <t>JM-10</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
@@ -7926,7 +7937,7 @@
       </c>
       <c r="C88" s="35" t="inlineStr">
         <is>
-          <t>Map 3 college values to Ministry codes</t>
+          <t>Fill Jameah Settings (6 values)</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
@@ -7956,17 +7967,17 @@
       </c>
       <c r="I88" s="35" t="inlineStr">
         <is>
-          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
+          <t>Empty values are sent as empty.</t>
         </is>
       </c>
       <c r="J88" s="35" t="inlineStr">
         <is>
-          <t>Pick the code in Jameah Code Map and set Verified.</t>
+          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
         </is>
       </c>
       <c r="K88" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-code-map</t>
+          <t>/app/jameah-settings</t>
         </is>
       </c>
       <c r="L88" s="34" t="inlineStr">
@@ -7978,7 +7989,7 @@
     <row r="89">
       <c r="A89" s="33" t="inlineStr">
         <is>
-          <t>JM-12</t>
+          <t>JM-11</t>
         </is>
       </c>
       <c r="B89" s="34" t="inlineStr">
@@ -7988,7 +7999,7 @@
       </c>
       <c r="C89" s="35" t="inlineStr">
         <is>
-          <t>Ministry fields with no source in the college system</t>
+          <t>Map 3 college values to Ministry codes</t>
         </is>
       </c>
       <c r="D89" s="34" t="inlineStr">
@@ -8003,44 +8014,44 @@
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs + Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G89" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I89" s="35" t="inlineStr">
         <is>
-          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
+          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
         </is>
       </c>
       <c r="J89" s="35" t="inlineStr">
         <is>
-          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
+          <t>Pick the code in Jameah Code Map and set Verified.</t>
         </is>
       </c>
       <c r="K89" s="35" t="inlineStr">
         <is>
-          <t>Jameah report; VIEWS.md</t>
+          <t>/app/jameah-code-map</t>
         </is>
       </c>
       <c r="L89" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>JM-13</t>
+          <t>JM-12</t>
         </is>
       </c>
       <c r="B90" s="34" t="inlineStr">
@@ -8050,7 +8061,7 @@
       </c>
       <c r="C90" s="35" t="inlineStr">
         <is>
-          <t>Correct source data found by the checks</t>
+          <t>Ministry fields with no source in the college system</t>
         </is>
       </c>
       <c r="D90" s="34" t="inlineStr">
@@ -8060,37 +8071,37 @@
       </c>
       <c r="E90" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Academic Affairs + Abdul Hakeem</t>
         </is>
       </c>
       <c r="G90" s="34" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I90" s="35" t="inlineStr">
         <is>
-          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
+          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
         </is>
       </c>
       <c r="J90" s="35" t="inlineStr">
         <is>
-          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
+          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
         </is>
       </c>
       <c r="K90" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-data-check</t>
+          <t>Jameah report; VIEWS.md</t>
         </is>
       </c>
       <c r="L90" s="34" t="inlineStr">
@@ -8102,7 +8113,7 @@
     <row r="91">
       <c r="A91" s="33" t="inlineStr">
         <is>
-          <t>JM-14</t>
+          <t>JM-13</t>
         </is>
       </c>
       <c r="B91" s="34" t="inlineStr">
@@ -8112,27 +8123,27 @@
       </c>
       <c r="C91" s="35" t="inlineStr">
         <is>
-          <t>Faculty views (8 sections)</t>
+          <t>Correct source data found by the checks</t>
         </is>
       </c>
       <c r="D91" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E91" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F91" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="G91" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="H91" s="34" t="inlineStr">
@@ -8142,29 +8153,29 @@
       </c>
       <c r="I91" s="35" t="inlineStr">
         <is>
-          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
+          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
         </is>
       </c>
       <c r="J91" s="35" t="inlineStr">
         <is>
-          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
+          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
         </is>
       </c>
       <c r="K91" s="35" t="inlineStr">
         <is>
-          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
+          <t>/app/jameah-data-check</t>
         </is>
       </c>
       <c r="L91" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="33" t="inlineStr">
         <is>
-          <t>JM-15</t>
+          <t>JM-14</t>
         </is>
       </c>
       <c r="B92" s="34" t="inlineStr">
@@ -8174,17 +8185,17 @@
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>Institute views (20 sections)</t>
+          <t>Faculty views (8 sections)</t>
         </is>
       </c>
       <c r="D92" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E92" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F92" s="34" t="inlineStr">
@@ -8199,22 +8210,22 @@
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I92" s="35" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
         </is>
       </c>
       <c r="J92" s="35" t="inlineStr">
         <is>
-          <t>Build after Faculty; needs institute data from HR.</t>
+          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
         </is>
       </c>
       <c r="K92" s="35" t="inlineStr">
         <is>
-          <t>MINISTRY_FIELD_MAPPING.html</t>
+          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
         </is>
       </c>
       <c r="L92" s="34" t="inlineStr">
@@ -8226,7 +8237,7 @@
     <row r="93">
       <c r="A93" s="33" t="inlineStr">
         <is>
-          <t>JM-16</t>
+          <t>JM-15</t>
         </is>
       </c>
       <c r="B93" s="34" t="inlineStr">
@@ -8236,7 +8247,7 @@
       </c>
       <c r="C93" s="35" t="inlineStr">
         <is>
-          <t>Old viewJameah* views (42, earlier version)</t>
+          <t>Institute views (20 sections)</t>
         </is>
       </c>
       <c r="D93" s="34" t="inlineStr">
@@ -8246,7 +8257,7 @@
       </c>
       <c r="E93" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – development</t>
         </is>
       </c>
       <c r="F93" s="34" t="inlineStr">
@@ -8261,95 +8272,157 @@
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I93" s="35" t="inlineStr">
         <is>
-          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="J93" s="35" t="inlineStr">
         <is>
-          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+          <t>Build after Faculty; needs institute data from HR.</t>
         </is>
       </c>
       <c r="K93" s="35" t="inlineStr">
         <is>
-          <t>jameah_system (old views)</t>
+          <t>MINISTRY_FIELD_MAPPING.html</t>
         </is>
       </c>
       <c r="L93" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="33" t="inlineStr">
         <is>
+          <t>JM-16</t>
+        </is>
+      </c>
+      <c r="B94" s="34" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C94" s="35" t="inlineStr">
+        <is>
+          <t>Old viewJameah* views (42, earlier version)</t>
+        </is>
+      </c>
+      <c r="D94" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="34" t="inlineStr">
+        <is>
+          <t>Pending – decision needed</t>
+        </is>
+      </c>
+      <c r="F94" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G94" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H94" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I94" s="35" t="inlineStr">
+        <is>
+          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+        </is>
+      </c>
+      <c r="J94" s="35" t="inlineStr">
+        <is>
+          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+        </is>
+      </c>
+      <c r="K94" s="35" t="inlineStr">
+        <is>
+          <t>jameah_system (old views)</t>
+        </is>
+      </c>
+      <c r="L94" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="33" t="inlineStr">
+        <is>
           <t>JM-17</t>
         </is>
       </c>
-      <c r="B94" s="34" t="inlineStr">
+      <c r="B95" s="34" t="inlineStr">
         <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="C94" s="35" t="inlineStr">
+      <c r="C95" s="35" t="inlineStr">
         <is>
           <t>Transcript GPA rounding at exact ties</t>
         </is>
       </c>
-      <c r="D94" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E94" s="34" t="inlineStr">
+      <c r="D95" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E95" s="34" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F94" s="34" t="inlineStr">
-        <is>
-          <t>Abdul Hakeem</t>
-        </is>
-      </c>
-      <c r="G94" s="34" t="inlineStr">
-        <is>
-          <t>Abdul Hakeem</t>
-        </is>
-      </c>
-      <c r="H94" s="34" t="inlineStr">
+      <c r="F95" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G95" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H95" s="34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I94" s="35" t="inlineStr">
+      <c r="I95" s="35" t="inlineStr">
         <is>
           <t>Resolved by the college's official GPA calculation (exact half-up rounding); the Ministry views use it (JM-18).</t>
         </is>
       </c>
-      <c r="J94" s="35" t="inlineStr">
+      <c r="J95" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="K94" s="35" t="inlineStr">
+      <c r="K95" s="35" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="L94" s="34" t="inlineStr">
+      <c r="L95" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L94"/>
-  <conditionalFormatting sqref="E2:E294">
+  <autoFilter ref="A1:L95"/>
+  <conditionalFormatting sqref="E2:E295">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$E2="Done"</formula>
     </cfRule>
@@ -8375,7 +8448,7 @@
       <formula>$E2="Planned"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H294">
+  <conditionalFormatting sqref="H2:H295">
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
       <formula>$H2="Critical"</formula>
     </cfRule>
@@ -8390,14 +8463,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E2:E294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
+    <dataValidation sqref="E2:E295" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
       <formula1>"Done,Done – client UAT pending,In progress,Pending – decision needed,Pending – data / setup,Pending – development,Pending – other team,Planned"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H295" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G294" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Abdul Hakeem,Fathir,Dinesh,To assign"</formula1>
+    <dataValidation sqref="G2:G295" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Abdul Hakeem,Fathir,Dinesh,Testing team,To assign"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11945,7 +12018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11985,22 +12058,22 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E2" s="34" t="inlineStr">
@@ -12022,12 +12095,12 @@
       </c>
       <c r="C3" s="35" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E3" s="34" t="inlineStr">
@@ -12044,17 +12117,17 @@
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D4" s="35" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E4" s="34" t="inlineStr">
@@ -12076,12 +12149,12 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -12098,17 +12171,17 @@
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -12120,7 +12193,7 @@
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
@@ -12130,12 +12203,12 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -12157,12 +12230,12 @@
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -12179,17 +12252,17 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -12201,22 +12274,22 @@
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -12233,17 +12306,17 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -12260,17 +12333,17 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -12282,7 +12355,7 @@
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
@@ -12292,12 +12365,12 @@
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
@@ -12309,7 +12382,7 @@
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
@@ -12319,12 +12392,12 @@
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
@@ -12336,32 +12409,59 @@
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -15,10 +15,10 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$95</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$295,A5)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$297,A5)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$295,A6)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$297,A6)</f>
         <v/>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$295,A7)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$297,A7)</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="B8" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$295,A8)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$297,A8)</f>
         <v/>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$295,A9)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$297,A9)</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$295,A10)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$297,A10)</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$295,A11)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$297,A11)</f>
         <v/>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B12" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$295,A12)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$297,A12)</f>
         <v/>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B16" s="23">
-        <f>COUNTIFS(Tasks!$A$2:$A$295,"HR-*",Tasks!$E$2:$E$295,"Done")+COUNTIFS(Tasks!$A$2:$A$295,"HR-*",Tasks!$E$2:$E$295,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$297,"HR-*",Tasks!$E$2:$E$297,"Done")+COUNTIFS(Tasks!$A$2:$A$297,"HR-*",Tasks!$E$2:$E$297,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C16" s="23">
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>COUNTIF(Tasks!$A$2:$A$295,"HR-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$297,"HR-*")</f>
         <v/>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="B17" s="23">
-        <f>COUNTIFS(Tasks!$A$2:$A$295,"JM-*",Tasks!$E$2:$E$295,"Done")+COUNTIFS(Tasks!$A$2:$A$295,"JM-*",Tasks!$E$2:$E$295,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$297,"JM-*",Tasks!$E$2:$E$297,"Done")+COUNTIFS(Tasks!$A$2:$A$297,"JM-*",Tasks!$E$2:$E$297,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C17" s="23">
@@ -1298,7 +1298,7 @@
         <v/>
       </c>
       <c r="D17" s="23">
-        <f>COUNTIF(Tasks!$A$2:$A$295,"JM-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$297,"JM-*")</f>
         <v/>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B20" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$295,"Earlier (May – 5 Oct 2026)")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$297,"Earlier (May – 5 Oct 2026)")</f>
         <v/>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B21" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$295,"19 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$297,"19 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="B22" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$295,"20 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$297,"20 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1355,40 +1355,40 @@
         </is>
       </c>
       <c r="B23" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$295,"21 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$297,"21 Oct 2026")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B24" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$295,"22 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$297,"27 Oct 2026")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B25" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$295,"23 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$297,"22 Oct 2026")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B26" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$295,"27 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$297,"23 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="B27" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$295,"—")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$297,"—")</f>
         <v/>
       </c>
     </row>
@@ -1463,39 +1463,39 @@
         </is>
       </c>
       <c r="B30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A30,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J30" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A30)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A30)</f>
         <v/>
       </c>
     </row>
@@ -1506,39 +1506,39 @@
         </is>
       </c>
       <c r="B31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A31,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J31" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A31)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A31)</f>
         <v/>
       </c>
     </row>
@@ -1549,39 +1549,39 @@
         </is>
       </c>
       <c r="B32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A32,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J32" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A32)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A32)</f>
         <v/>
       </c>
     </row>
@@ -1592,39 +1592,39 @@
         </is>
       </c>
       <c r="B33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A33,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J33" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A33)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A33)</f>
         <v/>
       </c>
     </row>
@@ -1635,39 +1635,39 @@
         </is>
       </c>
       <c r="B34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A34,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J34" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A34)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A34)</f>
         <v/>
       </c>
     </row>
@@ -1678,39 +1678,39 @@
         </is>
       </c>
       <c r="B35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A35,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J35" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A35)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A35)</f>
         <v/>
       </c>
     </row>
@@ -1721,39 +1721,39 @@
         </is>
       </c>
       <c r="B36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A36,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J36" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A36)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A36)</f>
         <v/>
       </c>
     </row>
@@ -1764,39 +1764,39 @@
         </is>
       </c>
       <c r="B37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A37,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J37" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A37)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A37)</f>
         <v/>
       </c>
     </row>
@@ -1807,39 +1807,39 @@
         </is>
       </c>
       <c r="B38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A38,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J38" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A38)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A38)</f>
         <v/>
       </c>
     </row>
@@ -1850,39 +1850,39 @@
         </is>
       </c>
       <c r="B39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A39,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J39" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A39)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A39)</f>
         <v/>
       </c>
     </row>
@@ -1893,39 +1893,39 @@
         </is>
       </c>
       <c r="B40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A40,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J40" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A40)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A40)</f>
         <v/>
       </c>
     </row>
@@ -1936,39 +1936,39 @@
         </is>
       </c>
       <c r="B41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A41,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J41" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A41)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A41)</f>
         <v/>
       </c>
     </row>
@@ -1979,39 +1979,39 @@
         </is>
       </c>
       <c r="B42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A42,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J42" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A42)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A42)</f>
         <v/>
       </c>
     </row>
@@ -2022,39 +2022,39 @@
         </is>
       </c>
       <c r="B43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A43,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J43" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A43)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A43)</f>
         <v/>
       </c>
     </row>
@@ -2065,39 +2065,39 @@
         </is>
       </c>
       <c r="B44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A44,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J44" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A44)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A44)</f>
         <v/>
       </c>
     </row>
@@ -2108,39 +2108,39 @@
         </is>
       </c>
       <c r="B45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A45,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J45" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A45)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A45)</f>
         <v/>
       </c>
     </row>
@@ -2151,39 +2151,39 @@
         </is>
       </c>
       <c r="B46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A46,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J46" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A46)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A46)</f>
         <v/>
       </c>
     </row>
@@ -2194,39 +2194,39 @@
         </is>
       </c>
       <c r="B47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A47,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J47" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A47)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A47)</f>
         <v/>
       </c>
     </row>
@@ -2237,39 +2237,39 @@
         </is>
       </c>
       <c r="B48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A48,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J48" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A48)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A48)</f>
         <v/>
       </c>
     </row>
@@ -2280,39 +2280,39 @@
         </is>
       </c>
       <c r="B49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A49,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J49" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A49)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A49)</f>
         <v/>
       </c>
     </row>
@@ -2323,39 +2323,39 @@
         </is>
       </c>
       <c r="B50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A50,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J50" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A50)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A50)</f>
         <v/>
       </c>
     </row>
@@ -2366,39 +2366,39 @@
         </is>
       </c>
       <c r="B51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A51,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J51" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A51)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A51)</f>
         <v/>
       </c>
     </row>
@@ -2409,39 +2409,39 @@
         </is>
       </c>
       <c r="B52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,B$29)</f>
         <v/>
       </c>
       <c r="C52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,C$29)</f>
         <v/>
       </c>
       <c r="D52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,D$29)</f>
         <v/>
       </c>
       <c r="E52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,E$29)</f>
         <v/>
       </c>
       <c r="F52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,F$29)</f>
         <v/>
       </c>
       <c r="G52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,G$29)</f>
         <v/>
       </c>
       <c r="H52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,H$29)</f>
         <v/>
       </c>
       <c r="I52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$295,$A52,Tasks!$E$2:$E$295,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,I$29)</f>
         <v/>
       </c>
       <c r="J52" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$295,$A52)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$297,$A52)</f>
         <v/>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="B55" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$156,A55)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$158,A55)</f>
         <v/>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="B56" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$156,A56)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$158,A56)</f>
         <v/>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B57" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$156,A57)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$158,A57)</f>
         <v/>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="B58" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$156,A58)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$158,A58)</f>
         <v/>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="D17" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Done – client UAT pending</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
@@ -3565,22 +3565,22 @@
       </c>
       <c r="I17" s="35" t="inlineStr">
         <is>
-          <t>Drafts can be saved; employees cannot edit sent requests.</t>
+          <t>Round 2 (27 Oct): employees open a draft to change, send or delete it (Edit Draft / Delete Draft); a rejected request can be sent again once, as a new request filled in from it and linked to it (Sent Again From; Apply Again for leave). Sent requests still cannot be changed by the employee. Tested: unit tests (test_request_flow) and browser ESS-18, ESS-19, APR-11.</t>
         </is>
       </c>
       <c r="J17" s="35" t="inlineStr">
         <is>
-          <t>Let employees open their draft and send it; allow resubmitting a rejected request as a new one with history.</t>
+          <t>Testing team: Round 2 cases TC-ESS-17, 18, 20, 21, TC-APR-12, TC-LV-18.</t>
         </is>
       </c>
       <c r="K17" s="35" t="inlineStr">
         <is>
-          <t>HRM_UAT_SCENARIOS.md #3</t>
+          <t>self_service.py; request_flow.py; employee_dashboard.js</t>
         </is>
       </c>
       <c r="L17" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="J27" s="35" t="inlineStr">
         <is>
-          <t>Agree the approver per step with HR and Finance; build the workflow; label amounts in SAR (some messages say AED).</t>
+          <t>Agree the approver per step with HR and Finance (DEC-09); build the workflow. Amounts now say SAR (Round 2, 27 Oct, TC-APR-13).</t>
         </is>
       </c>
       <c r="K27" s="35" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L27" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Done – client UAT pending</t>
         </is>
       </c>
       <c r="F28" s="34" t="inlineStr">
@@ -4247,22 +4247,22 @@
       </c>
       <c r="I28" s="35" t="inlineStr">
         <is>
-          <t>Changes are tracked (track_changes). E-mail sending fails on this copy (HR-47).</t>
+          <t>Round 2 (27 Oct): Rejection Reason is required to reject (10 request types, including Leave Application) and the employee reads it; each request shows its history (every status change, who and when) on the Employee Portal; notifications in the bell, and by e-mail where the mail account works: HR when an employee sends a request, the employee at every later step, with a link that opens the request. Notifications are queued only after the save is committed. Tested: unit tests and browser APR-02, APR-09, APR-10, APR-11.</t>
         </is>
       </c>
       <c r="J28" s="35" t="inlineStr">
         <is>
-          <t>Add rejection reason; send submit/approve/reject e-mails once the mail account works.</t>
+          <t>Testing team: Round 2 cases. E-mails: check on the live server once HR-47 is fixed (Checklist CL-41). Who gets new-request notifications: DEC-16.</t>
         </is>
       </c>
       <c r="K28" s="35" t="inlineStr">
         <is>
-          <t>HRM_UAT_SCENARIOS.md</t>
+          <t>request_flow.py; self_service.py</t>
         </is>
       </c>
       <c r="L28" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="J56" s="35" t="inlineStr">
         <is>
-          <t>Client UAT of the application form and the receipt (TC-REC-13, TC-REC-14). Fathir: the phone error message gives a Sri Lankan example (+94 77 123 4567); use a Saudi one (+966 5x xxx xxxx).</t>
+          <t>Client UAT of the application form and the receipt (TC-REC-13, TC-REC-14). Saudi phone example: HR-77 (Fathir).</t>
         </is>
       </c>
       <c r="K56" s="35" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L56" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6253,22 +6253,22 @@
     <row r="61">
       <c r="A61" s="33" t="inlineStr">
         <is>
-          <t>HR-74</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="B61" s="34" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C61" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide and User Guide (PDF)</t>
+          <t>Round 2 feature document and test cases</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
@@ -6293,49 +6293,49 @@
       </c>
       <c r="I61" s="35" t="inlineStr">
         <is>
-          <t>Two PDF guides in docs/guides: Installation and Setup Guide (21 pages: install, update, checks, first-time setup, leave year, sick leave, Jameah setup, Ministry agent account, staff data sheets, testing, troubleshooting, commands) and User Guide (30 pages: Employee Portal and the leave flow, every request, HR Portal, leave approvals and returns, recruitment, Ministry data, Academic Presence, Jameah pages, approvers, how to test and report bugs, Q&amp;A). 31 screenshots from the test site with QA test data only. Sources (HTML) and build.py kept in docs/guides/src so the guides can be rebuilt after changes. Writing them found two bugs (B-54, B-55). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>docs/guides/Medical_HRMS_Round_2_Whats_New.pdf (8 pages, for the testing team): what changed, how to test each change, known limits, the 16 Round 2 test cases. The Test Cases workbook has a Round column (filter Round 2) and counts per round. User Guide and Installation and Setup Guide updated for Round 2 (new screenshots, QA data only). Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="J61" s="35" t="inlineStr">
         <is>
-          <t>HR, managers and the testing team read the User Guide; the server admin the Installation Guide (Checklist CL-37). Rebuild after changes: python docs/guides/src/build.py.</t>
+          <t>Give the document and the workbook to the testing team after Round 2 is on their test server (Checklist CL-39).</t>
         </is>
       </c>
       <c r="K61" s="35" t="inlineStr">
         <is>
-          <t>docs/guides</t>
+          <t>docs/guides; Test Cases workbook</t>
         </is>
       </c>
       <c r="L61" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="33" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-77</t>
         </is>
       </c>
       <c r="B62" s="34" t="inlineStr">
         <is>
-          <t>HR dashboard</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C62" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college design</t>
+          <t>Saudi phone example on the job application form</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – development</t>
         </is>
       </c>
       <c r="F62" s="34" t="inlineStr">
@@ -6345,54 +6345,54 @@
       </c>
       <c r="G62" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Fathir</t>
         </is>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I62" s="35" t="inlineStr">
         <is>
-          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
+          <t>The phone error message on the public application form gives a Sri Lankan example (+94 77 123 4567). Found in the HR-70 review.</t>
         </is>
       </c>
       <c r="J62" s="35" t="inlineStr">
         <is>
-          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
+          <t>Fathir: use a Saudi example (+966 5x xxx xxxx) in www/job-application.html and send a pull request to develop.</t>
         </is>
       </c>
       <c r="K62" s="35" t="inlineStr">
         <is>
-          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
+          <t>www/job-application.html</t>
         </is>
       </c>
       <c r="L62" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="33" t="inlineStr">
         <is>
-          <t>HR-62</t>
+          <t>HR-74</t>
         </is>
       </c>
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C63" s="35" t="inlineStr">
         <is>
-          <t>HR User could not open the Holiday List ('Not permitted')</t>
+          <t>Installation and Setup Guide and User Guide (PDF)</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
@@ -6412,44 +6412,44 @@
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I63" s="35" t="inlineStr">
         <is>
-          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
+          <t>Two PDF guides in docs/guides: Installation and Setup Guide (21 pages: install, update, checks, first-time setup, leave year, sick leave, Jameah setup, Ministry agent account, staff data sheets, testing, troubleshooting, commands) and User Guide (30 pages: Employee Portal and the leave flow, every request, HR Portal, leave approvals and returns, recruitment, Ministry data, Academic Presence, Jameah pages, approvers, how to test and report bugs, Q&amp;A). 31 screenshots from the test site with QA test data only. Sources (HTML) and build.py kept in docs/guides/src so the guides can be rebuilt after changes. Writing them found two bugs (B-54, B-55). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="J63" s="35" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>HR, managers and the testing team read the User Guide; the server admin the Installation Guide (Checklist CL-37). Rebuild after changes: python docs/guides/src/build.py.</t>
         </is>
       </c>
       <c r="K63" s="35" t="inlineStr">
         <is>
-          <t>hr_core_permissions.py</t>
+          <t>docs/guides</t>
         </is>
       </c>
       <c r="L63" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="C64" s="35" t="inlineStr">
         <is>
-          <t>Full end-to-end test with error sweep (round 3)</t>
+          <t>HR Portal and Employee Portal in the new college design</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
@@ -6479,79 +6479,79 @@
       </c>
       <c r="I64" s="35" t="inlineStr">
         <is>
-          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
+          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
         </is>
       </c>
       <c r="J64" s="35" t="inlineStr">
         <is>
-          <t>Client UAT.</t>
+          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
         </is>
       </c>
       <c r="K64" s="35" t="inlineStr">
         <is>
-          <t>Test Report</t>
+          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
         </is>
       </c>
       <c r="L64" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="33" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-62</t>
         </is>
       </c>
       <c r="B65" s="34" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C65" s="35" t="inlineStr">
         <is>
-          <t>System e-mail account password cannot be decrypted</t>
+          <t>HR User could not open the Holiday List ('Not permitted')</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G65" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I65" s="35" t="inlineStr">
         <is>
-          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
+          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
         </is>
       </c>
       <c r="J65" s="35" t="inlineStr">
         <is>
-          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="K65" s="35" t="inlineStr">
         <is>
-          <t>Error Log; Email Queue</t>
+          <t>hr_core_permissions.py</t>
         </is>
       </c>
       <c r="L65" s="34" t="inlineStr">
@@ -6563,27 +6563,27 @@
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-46</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C66" s="35" t="inlineStr">
         <is>
-          <t>Instructor form: linking an Employee fails on save</t>
+          <t>Full end-to-end test with error sweep (round 3)</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E66" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F66" s="34" t="inlineStr">
@@ -6598,84 +6598,84 @@
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I66" s="35" t="inlineStr">
         <is>
-          <t>Instructor copies gender/department from Employee into its own lists, which reject Ministry codes. Recruitment works around it.</t>
+          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
         </is>
       </c>
       <c r="J66" s="35" t="inlineStr">
         <is>
-          <t>Fix it from Medical HRMS: give the Instructor form the matching value when it copies gender / department from the Employee.</t>
+          <t>Client UAT.</t>
         </is>
       </c>
       <c r="K66" s="35" t="inlineStr">
         <is>
-          <t>Instructor form; medical_hrms</t>
+          <t>Test Report</t>
         </is>
       </c>
       <c r="L66" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="33" t="inlineStr">
         <is>
-          <t>HR-49</t>
+          <t>HR-47</t>
         </is>
       </c>
       <c r="B67" s="34" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C67" s="35" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>System e-mail account password cannot be decrypted</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G67" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I67" s="35" t="inlineStr">
         <is>
-          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
+          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
         </is>
       </c>
       <c r="J67" s="35" t="inlineStr">
         <is>
-          <t>HR to use it to complete the data (HR-50 sheet).</t>
+          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
         </is>
       </c>
       <c r="K67" s="35" t="inlineStr">
         <is>
-          <t>report/employees_missing_ministry_data</t>
+          <t>Error Log; Email Queue</t>
         </is>
       </c>
       <c r="L67" s="34" t="inlineStr">
@@ -6687,27 +6687,27 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>HR-50</t>
+          <t>HR-48</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C68" s="35" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff</t>
+          <t>Instructor form: linking an Employee fails on save</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Done – client UAT pending</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
@@ -6727,39 +6727,39 @@
       </c>
       <c r="I68" s="35" t="inlineStr">
         <is>
-          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
+          <t>Round 2 (27 Oct), fixed from Medical HRMS without touching the education app: the copy of gender / department from the Employee is switched off on Instructor and Academic Advisor (Property Setters) and the matching Gender Edu / Department Edu value is filled in instead, on the form and on save. The Academic Advisor form had the same problem (B-56). Tested: unit tests and browser REC-11.</t>
         </is>
       </c>
       <c r="J68" s="35" t="inlineStr">
         <is>
-          <t>HR to fill the sheet for all non-academic staff.</t>
+          <t>Testing team: TC-EMP-13, TC-EMP-14.</t>
         </is>
       </c>
       <c r="K68" s="35" t="inlineStr">
         <is>
-          <t>employee_data_sheet.py</t>
+          <t>staff_links.py; public/js/staff_employee_link.js</t>
         </is>
       </c>
       <c r="L68" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="33" t="inlineStr">
         <is>
-          <t>HR-51</t>
+          <t>HR-49</t>
         </is>
       </c>
       <c r="B69" s="34" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C69" s="35" t="inlineStr">
         <is>
-          <t>Unused duplicate of the applicant Ministry fields removed</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
@@ -6784,22 +6784,22 @@
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I69" s="35" t="inlineStr">
         <is>
-          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
+          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
         </is>
       </c>
       <c r="J69" s="35" t="inlineStr">
         <is>
-          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
+          <t>HR to use it to complete the data (HR-50 sheet).</t>
         </is>
       </c>
       <c r="K69" s="35" t="inlineStr">
         <is>
-          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
+          <t>report/employees_missing_ministry_data</t>
         </is>
       </c>
       <c r="L69" s="34" t="inlineStr">
@@ -6811,7 +6811,7 @@
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>HR-52</t>
+          <t>HR-50</t>
         </is>
       </c>
       <c r="B70" s="34" t="inlineStr">
@@ -6821,27 +6821,27 @@
       </c>
       <c r="C70" s="35" t="inlineStr">
         <is>
-          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
+          <t>Data sheet for non-academic staff</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E70" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H70" s="34" t="inlineStr">
@@ -6851,17 +6851,17 @@
       </c>
       <c r="I70" s="35" t="inlineStr">
         <is>
-          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
+          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
         </is>
       </c>
       <c r="J70" s="35" t="inlineStr">
         <is>
-          <t>Confirm whether 9-digit numbers must be accepted.</t>
+          <t>HR to fill the sheet for all non-academic staff.</t>
         </is>
       </c>
       <c r="K70" s="35" t="inlineStr">
         <is>
-          <t>ministry_lookup_validation.py</t>
+          <t>employee_data_sheet.py</t>
         </is>
       </c>
       <c r="L70" s="34" t="inlineStr">
@@ -6873,37 +6873,37 @@
     <row r="71">
       <c r="A71" s="33" t="inlineStr">
         <is>
-          <t>HR-53</t>
+          <t>HR-51</t>
         </is>
       </c>
       <c r="B71" s="34" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C71" s="35" t="inlineStr">
         <is>
-          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
+          <t>Unused duplicate of the applicant Ministry fields removed</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H71" s="34" t="inlineStr">
@@ -6913,17 +6913,17 @@
       </c>
       <c r="I71" s="35" t="inlineStr">
         <is>
-          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
+          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
         </is>
       </c>
       <c r="J71" s="35" t="inlineStr">
         <is>
-          <t>Complete or delete the demo record before go-live.</t>
+          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
         </is>
       </c>
       <c r="K71" s="35" t="inlineStr">
         <is>
-          <t>Employee EMP-00001</t>
+          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
         </is>
       </c>
       <c r="L71" s="34" t="inlineStr">
@@ -6935,17 +6935,17 @@
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>HR-54</t>
+          <t>HR-52</t>
         </is>
       </c>
       <c r="B72" s="34" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C72" s="35" t="inlineStr">
         <is>
-          <t>Website logo file missing (/files/rchs-logo.png)</t>
+          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
@@ -6955,37 +6955,37 @@
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I72" s="35" t="inlineStr">
         <is>
-          <t>Missing on the local copy; every page requests it.</t>
+          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
         </is>
       </c>
       <c r="J72" s="35" t="inlineStr">
         <is>
-          <t>Check the file exists on the live server.</t>
+          <t>Confirm whether 9-digit numbers must be accepted.</t>
         </is>
       </c>
       <c r="K72" s="35" t="inlineStr">
         <is>
-          <t>Website Settings</t>
+          <t>ministry_lookup_validation.py</t>
         </is>
       </c>
       <c r="L72" s="34" t="inlineStr">
@@ -6997,7 +6997,7 @@
     <row r="73">
       <c r="A73" s="33" t="inlineStr">
         <is>
-          <t>HR-55</t>
+          <t>HR-53</t>
         </is>
       </c>
       <c r="B73" s="34" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="C73" s="35" t="inlineStr">
         <is>
-          <t>Link the 216 existing Instructors to Employees</t>
+          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
@@ -7032,22 +7032,22 @@
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I73" s="35" t="inlineStr">
         <is>
-          <t>Tool ready (HR-35). 1 of 216 linked.</t>
+          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
         </is>
       </c>
       <c r="J73" s="35" t="inlineStr">
         <is>
-          <t>HR fills the Instructor data sheet; run the import with commit.</t>
+          <t>Complete or delete the demo record before go-live.</t>
         </is>
       </c>
       <c r="K73" s="35" t="inlineStr">
         <is>
-          <t>instructor_data_sheet.py</t>
+          <t>Employee EMP-00001</t>
         </is>
       </c>
       <c r="L73" s="34" t="inlineStr">
@@ -7059,17 +7059,17 @@
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-54</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C74" s="35" t="inlineStr">
         <is>
-          <t>Connect attendance devices</t>
+          <t>Website logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
@@ -7084,32 +7084,32 @@
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I74" s="35" t="inlineStr">
         <is>
-          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
+          <t>Missing on the local copy; every page requests it.</t>
         </is>
       </c>
       <c r="J74" s="35" t="inlineStr">
         <is>
-          <t>Connect devices; map device user IDs to Employees.</t>
+          <t>Check the file exists on the live server.</t>
         </is>
       </c>
       <c r="K74" s="35" t="inlineStr">
         <is>
-          <t>bfac883</t>
+          <t>Website Settings</t>
         </is>
       </c>
       <c r="L74" s="34" t="inlineStr">
@@ -7121,17 +7121,17 @@
     <row r="75">
       <c r="A75" s="33" t="inlineStr">
         <is>
-          <t>HR-57</t>
+          <t>HR-55</t>
         </is>
       </c>
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C75" s="35" t="inlineStr">
         <is>
-          <t>Set the Academic Holiday List</t>
+          <t>Link the 216 existing Instructors to Employees</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
@@ -7156,22 +7156,22 @@
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I75" s="35" t="inlineStr">
         <is>
-          <t>Not set; the page warns about it.</t>
+          <t>Tool ready (HR-35). 1 of 216 linked.</t>
         </is>
       </c>
       <c r="J75" s="35" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
+          <t>HR fills the Instructor data sheet; run the import with commit.</t>
         </is>
       </c>
       <c r="K75" s="35" t="inlineStr">
         <is>
-          <t>academic_presence_setup.py</t>
+          <t>instructor_data_sheet.py</t>
         </is>
       </c>
       <c r="L75" s="34" t="inlineStr">
@@ -7183,17 +7183,17 @@
     <row r="76">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>HR-58</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="B76" s="34" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C76" s="35" t="inlineStr">
         <is>
-          <t>Deploy to the live server</t>
+          <t>Connect attendance devices</t>
         </is>
       </c>
       <c r="D76" s="34" t="inlineStr">
@@ -7208,94 +7208,94 @@
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I76" s="35" t="inlineStr">
         <is>
-          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
+          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
         </is>
       </c>
       <c r="J76" s="35" t="inlineStr">
         <is>
-          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
+          <t>Connect devices; map device user IDs to Employees.</t>
         </is>
       </c>
       <c r="K76" s="35" t="inlineStr">
         <is>
-          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
+          <t>bfac883</t>
         </is>
       </c>
       <c r="L76" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="33" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>HR-57</t>
         </is>
       </c>
       <c r="B77" s="34" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C77" s="35" t="inlineStr">
         <is>
-          <t>Research: Jameah system, Ministry documents, view contract</t>
+          <t>Set the Academic Holiday List</t>
         </is>
       </c>
       <c r="D77" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E77" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G77" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I77" s="35" t="inlineStr">
         <is>
-          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
+          <t>Not set; the page warns about it.</t>
         </is>
       </c>
       <c r="J77" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
         </is>
       </c>
       <c r="K77" s="35" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>academic_presence_setup.py</t>
         </is>
       </c>
       <c r="L77" s="34" t="inlineStr">
@@ -7307,32 +7307,32 @@
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>HR-58</t>
         </is>
       </c>
       <c r="B78" s="34" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C78" s="35" t="inlineStr">
         <is>
-          <t>Ministry views for Employees (5) and Students (10)</t>
+          <t>Deploy to the live server</t>
         </is>
       </c>
       <c r="D78" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E78" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G78" s="34" t="inlineStr">
@@ -7342,34 +7342,34 @@
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I78" s="35" t="inlineStr">
         <is>
-          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
+          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
         </is>
       </c>
       <c r="J78" s="35" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
         </is>
       </c>
       <c r="K78" s="35" t="inlineStr">
         <is>
-          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
+          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
         </is>
       </c>
       <c r="L78" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="33" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="B79" s="34" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="C79" s="35" t="inlineStr">
         <is>
-          <t>Code crosswalk (Jameah Code Map)</t>
+          <t>Research: Jameah system, Ministry documents, view contract</t>
         </is>
       </c>
       <c r="D79" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="E79" s="34" t="inlineStr">
@@ -7409,29 +7409,29 @@
       </c>
       <c r="I79" s="35" t="inlineStr">
         <is>
-          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
+          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
         </is>
       </c>
       <c r="J79" s="35" t="inlineStr">
         <is>
-          <t>Review 3 values (JM-11).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K79" s="35" t="inlineStr">
         <is>
-          <t>jameah/code_map.py</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="L79" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>JM-04</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C80" s="35" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>Ministry views for Employees (5) and Students (10)</t>
         </is>
       </c>
       <c r="D80" s="34" t="inlineStr">
@@ -7466,22 +7466,22 @@
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I80" s="35" t="inlineStr">
         <is>
-          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
+          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
         </is>
       </c>
       <c r="J80" s="35" t="inlineStr">
         <is>
-          <t>Fill 6 values (JM-10).</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="K80" s="35" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
         </is>
       </c>
       <c r="L80" s="34" t="inlineStr">
@@ -7493,7 +7493,7 @@
     <row r="81">
       <c r="A81" s="33" t="inlineStr">
         <is>
-          <t>JM-05</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="B81" s="34" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C81" s="35" t="inlineStr">
         <is>
-          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
+          <t>Code crosswalk (Jameah Code Map)</t>
         </is>
       </c>
       <c r="D81" s="34" t="inlineStr">
@@ -7533,29 +7533,29 @@
       </c>
       <c r="I81" s="35" t="inlineStr">
         <is>
-          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
+          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
         </is>
       </c>
       <c r="J81" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Review 3 values (JM-11).</t>
         </is>
       </c>
       <c r="K81" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py</t>
+          <t>jameah/code_map.py</t>
         </is>
       </c>
       <c r="L81" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>JM-06</t>
+          <t>JM-04</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C82" s="35" t="inlineStr">
         <is>
-          <t>Independent verification of every view</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="D82" s="34" t="inlineStr">
@@ -7590,34 +7590,34 @@
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I82" s="35" t="inlineStr">
         <is>
-          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
+          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
         </is>
       </c>
       <c r="J82" s="35" t="inlineStr">
         <is>
-          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
+          <t>Fill 6 values (JM-10).</t>
         </is>
       </c>
       <c r="K82" s="35" t="inlineStr">
         <is>
-          <t>jameah/verify.py; test_jameah.py</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="L82" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="33" t="inlineStr">
         <is>
-          <t>JM-18</t>
+          <t>JM-05</t>
         </is>
       </c>
       <c r="B83" s="34" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="C83" s="35" t="inlineStr">
         <is>
-          <t>Ministry GPA and credit hours = the college's official figures</t>
+          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
         </is>
       </c>
       <c r="D83" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E83" s="34" t="inlineStr">
@@ -7652,34 +7652,34 @@
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I83" s="35" t="inlineStr">
         <is>
-          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
+          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
         </is>
       </c>
       <c r="J83" s="35" t="inlineStr">
         <is>
-          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K83" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py; jameah/verify.py</t>
+          <t>jameah/summary.py</t>
         </is>
       </c>
       <c r="L83" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>JM-19</t>
+          <t>JM-06</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
@@ -7689,22 +7689,22 @@
       </c>
       <c r="C84" s="35" t="inlineStr">
         <is>
-          <t>Hourly academic summary refresh slows the site while it runs</t>
+          <t>Independent verification of every view</t>
         </is>
       </c>
       <c r="D84" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E84" s="34" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G84" s="34" t="inlineStr">
@@ -7714,34 +7714,34 @@
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I84" s="35" t="inlineStr">
         <is>
-          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
+          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
         </is>
       </c>
       <c r="J84" s="35" t="inlineStr">
         <is>
-          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
+          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="K84" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py; hooks.py hourly_long</t>
+          <t>jameah/verify.py; test_jameah.py</t>
         </is>
       </c>
       <c r="L84" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="33" t="inlineStr">
         <is>
-          <t>JM-07</t>
+          <t>JM-18</t>
         </is>
       </c>
       <c r="B85" s="34" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="C85" s="35" t="inlineStr">
         <is>
-          <t>Jameah Data Check page and Employee preview</t>
+          <t>Ministry GPA and credit hours = the college's official figures</t>
         </is>
       </c>
       <c r="D85" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E85" s="34" t="inlineStr">
@@ -7776,34 +7776,34 @@
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I85" s="35" t="inlineStr">
         <is>
-          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
+          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
         </is>
       </c>
       <c r="J85" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
         </is>
       </c>
       <c r="K85" s="35" t="inlineStr">
         <is>
-          <t>page/jameah_data_check</t>
+          <t>jameah/summary.py; jameah/verify.py</t>
         </is>
       </c>
       <c r="L85" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>JM-08</t>
+          <t>JM-19</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="C86" s="35" t="inlineStr">
         <is>
-          <t>Read-only database account for the Ministry agent</t>
+          <t>Hourly academic summary refresh slows the site while it runs</t>
         </is>
       </c>
       <c r="D86" s="34" t="inlineStr">
@@ -7823,49 +7823,49 @@
       </c>
       <c r="E86" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G86" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I86" s="35" t="inlineStr">
         <is>
-          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
+          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
         </is>
       </c>
       <c r="J86" s="35" t="inlineStr">
         <is>
-          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
+          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
         </is>
       </c>
       <c r="K86" s="35" t="inlineStr">
         <is>
-          <t>jameah/README.md</t>
+          <t>jameah/summary.py; hooks.py hourly_long</t>
         </is>
       </c>
       <c r="L86" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="33" t="inlineStr">
         <is>
-          <t>JM-09</t>
+          <t>JM-07</t>
         </is>
       </c>
       <c r="B87" s="34" t="inlineStr">
@@ -7875,47 +7875,47 @@
       </c>
       <c r="C87" s="35" t="inlineStr">
         <is>
-          <t>Confirm view and column names with the Ministry</t>
+          <t>Jameah Data Check page and Employee preview</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E87" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G87" s="34" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I87" s="35" t="inlineStr">
         <is>
-          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
+          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
         </is>
       </c>
       <c r="J87" s="35" t="inlineStr">
         <is>
-          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K87" s="35" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>page/jameah_data_check</t>
         </is>
       </c>
       <c r="L87" s="34" t="inlineStr">
@@ -7927,7 +7927,7 @@
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>JM-10</t>
+          <t>JM-08</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="C88" s="35" t="inlineStr">
         <is>
-          <t>Fill Jameah Settings (6 values)</t>
+          <t>Read-only database account for the Ministry agent</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
@@ -7947,17 +7947,17 @@
       </c>
       <c r="E88" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G88" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H88" s="34" t="inlineStr">
@@ -7967,17 +7967,17 @@
       </c>
       <c r="I88" s="35" t="inlineStr">
         <is>
-          <t>Empty values are sent as empty.</t>
+          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
         </is>
       </c>
       <c r="J88" s="35" t="inlineStr">
         <is>
-          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
+          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
         </is>
       </c>
       <c r="K88" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-settings</t>
+          <t>jameah/README.md</t>
         </is>
       </c>
       <c r="L88" s="34" t="inlineStr">
@@ -7989,7 +7989,7 @@
     <row r="89">
       <c r="A89" s="33" t="inlineStr">
         <is>
-          <t>JM-11</t>
+          <t>JM-09</t>
         </is>
       </c>
       <c r="B89" s="34" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C89" s="35" t="inlineStr">
         <is>
-          <t>Map 3 college values to Ministry codes</t>
+          <t>Confirm view and column names with the Ministry</t>
         </is>
       </c>
       <c r="D89" s="34" t="inlineStr">
@@ -8014,32 +8014,32 @@
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="G89" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I89" s="35" t="inlineStr">
         <is>
-          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
+          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
         </is>
       </c>
       <c r="J89" s="35" t="inlineStr">
         <is>
-          <t>Pick the code in Jameah Code Map and set Verified.</t>
+          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
         </is>
       </c>
       <c r="K89" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-code-map</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="L89" s="34" t="inlineStr">
@@ -8051,7 +8051,7 @@
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>JM-12</t>
+          <t>JM-10</t>
         </is>
       </c>
       <c r="B90" s="34" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="C90" s="35" t="inlineStr">
         <is>
-          <t>Ministry fields with no source in the college system</t>
+          <t>Fill Jameah Settings (6 values)</t>
         </is>
       </c>
       <c r="D90" s="34" t="inlineStr">
@@ -8076,44 +8076,44 @@
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs + Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G90" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I90" s="35" t="inlineStr">
         <is>
-          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
+          <t>Empty values are sent as empty.</t>
         </is>
       </c>
       <c r="J90" s="35" t="inlineStr">
         <is>
-          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
+          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
         </is>
       </c>
       <c r="K90" s="35" t="inlineStr">
         <is>
-          <t>Jameah report; VIEWS.md</t>
+          <t>/app/jameah-settings</t>
         </is>
       </c>
       <c r="L90" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="33" t="inlineStr">
         <is>
-          <t>JM-13</t>
+          <t>JM-11</t>
         </is>
       </c>
       <c r="B91" s="34" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="C91" s="35" t="inlineStr">
         <is>
-          <t>Correct source data found by the checks</t>
+          <t>Map 3 college values to Ministry codes</t>
         </is>
       </c>
       <c r="D91" s="34" t="inlineStr">
@@ -8133,17 +8133,17 @@
       </c>
       <c r="E91" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F91" s="34" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G91" s="34" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="H91" s="34" t="inlineStr">
@@ -8153,29 +8153,29 @@
       </c>
       <c r="I91" s="35" t="inlineStr">
         <is>
-          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
+          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
         </is>
       </c>
       <c r="J91" s="35" t="inlineStr">
         <is>
-          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
+          <t>Pick the code in Jameah Code Map and set Verified.</t>
         </is>
       </c>
       <c r="K91" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-data-check</t>
+          <t>/app/jameah-code-map</t>
         </is>
       </c>
       <c r="L91" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="33" t="inlineStr">
         <is>
-          <t>JM-14</t>
+          <t>JM-12</t>
         </is>
       </c>
       <c r="B92" s="34" t="inlineStr">
@@ -8185,22 +8185,22 @@
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>Faculty views (8 sections)</t>
+          <t>Ministry fields with no source in the college system</t>
         </is>
       </c>
       <c r="D92" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E92" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Academic Affairs + Abdul Hakeem</t>
         </is>
       </c>
       <c r="G92" s="34" t="inlineStr">
@@ -8210,34 +8210,34 @@
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I92" s="35" t="inlineStr">
         <is>
-          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
+          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
         </is>
       </c>
       <c r="J92" s="35" t="inlineStr">
         <is>
-          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
+          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
         </is>
       </c>
       <c r="K92" s="35" t="inlineStr">
         <is>
-          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
+          <t>Jameah report; VIEWS.md</t>
         </is>
       </c>
       <c r="L92" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="33" t="inlineStr">
         <is>
-          <t>JM-15</t>
+          <t>JM-13</t>
         </is>
       </c>
       <c r="B93" s="34" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="C93" s="35" t="inlineStr">
         <is>
-          <t>Institute views (20 sections)</t>
+          <t>Correct source data found by the checks</t>
         </is>
       </c>
       <c r="D93" s="34" t="inlineStr">
@@ -8257,49 +8257,49 @@
       </c>
       <c r="E93" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="G93" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I93" s="35" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
         </is>
       </c>
       <c r="J93" s="35" t="inlineStr">
         <is>
-          <t>Build after Faculty; needs institute data from HR.</t>
+          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
         </is>
       </c>
       <c r="K93" s="35" t="inlineStr">
         <is>
-          <t>MINISTRY_FIELD_MAPPING.html</t>
+          <t>/app/jameah-data-check</t>
         </is>
       </c>
       <c r="L93" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="33" t="inlineStr">
         <is>
-          <t>JM-16</t>
+          <t>JM-14</t>
         </is>
       </c>
       <c r="B94" s="34" t="inlineStr">
@@ -8309,17 +8309,17 @@
       </c>
       <c r="C94" s="35" t="inlineStr">
         <is>
-          <t>Old viewJameah* views (42, earlier version)</t>
+          <t>Faculty views (8 sections)</t>
         </is>
       </c>
       <c r="D94" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E94" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F94" s="34" t="inlineStr">
@@ -8334,95 +8334,219 @@
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I94" s="35" t="inlineStr">
         <is>
-          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
         </is>
       </c>
       <c r="J94" s="35" t="inlineStr">
         <is>
-          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
         </is>
       </c>
       <c r="K94" s="35" t="inlineStr">
         <is>
-          <t>jameah_system (old views)</t>
+          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
         </is>
       </c>
       <c r="L94" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="33" t="inlineStr">
         <is>
+          <t>JM-15</t>
+        </is>
+      </c>
+      <c r="B95" s="34" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C95" s="35" t="inlineStr">
+        <is>
+          <t>Institute views (20 sections)</t>
+        </is>
+      </c>
+      <c r="D95" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="34" t="inlineStr">
+        <is>
+          <t>Pending – development</t>
+        </is>
+      </c>
+      <c r="F95" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G95" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H95" s="34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I95" s="35" t="inlineStr">
+        <is>
+          <t>Not started.</t>
+        </is>
+      </c>
+      <c r="J95" s="35" t="inlineStr">
+        <is>
+          <t>Build after Faculty; needs institute data from HR.</t>
+        </is>
+      </c>
+      <c r="K95" s="35" t="inlineStr">
+        <is>
+          <t>MINISTRY_FIELD_MAPPING.html</t>
+        </is>
+      </c>
+      <c r="L95" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="33" t="inlineStr">
+        <is>
+          <t>JM-16</t>
+        </is>
+      </c>
+      <c r="B96" s="34" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C96" s="35" t="inlineStr">
+        <is>
+          <t>Old viewJameah* views (42, earlier version)</t>
+        </is>
+      </c>
+      <c r="D96" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E96" s="34" t="inlineStr">
+        <is>
+          <t>Pending – decision needed</t>
+        </is>
+      </c>
+      <c r="F96" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G96" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H96" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I96" s="35" t="inlineStr">
+        <is>
+          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+        </is>
+      </c>
+      <c r="J96" s="35" t="inlineStr">
+        <is>
+          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+        </is>
+      </c>
+      <c r="K96" s="35" t="inlineStr">
+        <is>
+          <t>jameah_system (old views)</t>
+        </is>
+      </c>
+      <c r="L96" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="inlineStr">
+        <is>
           <t>JM-17</t>
         </is>
       </c>
-      <c r="B95" s="34" t="inlineStr">
+      <c r="B97" s="34" t="inlineStr">
         <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="C95" s="35" t="inlineStr">
+      <c r="C97" s="35" t="inlineStr">
         <is>
           <t>Transcript GPA rounding at exact ties</t>
         </is>
       </c>
-      <c r="D95" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E95" s="34" t="inlineStr">
+      <c r="D97" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E97" s="34" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F95" s="34" t="inlineStr">
-        <is>
-          <t>Abdul Hakeem</t>
-        </is>
-      </c>
-      <c r="G95" s="34" t="inlineStr">
-        <is>
-          <t>Abdul Hakeem</t>
-        </is>
-      </c>
-      <c r="H95" s="34" t="inlineStr">
+      <c r="F97" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G97" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H97" s="34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I95" s="35" t="inlineStr">
+      <c r="I97" s="35" t="inlineStr">
         <is>
           <t>Resolved by the college's official GPA calculation (exact half-up rounding); the Ministry views use it (JM-18).</t>
         </is>
       </c>
-      <c r="J95" s="35" t="inlineStr">
+      <c r="J97" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="K95" s="35" t="inlineStr">
+      <c r="K97" s="35" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="L95" s="34" t="inlineStr">
+      <c r="L97" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L95"/>
-  <conditionalFormatting sqref="E2:E295">
+  <autoFilter ref="A1:L97"/>
+  <conditionalFormatting sqref="E2:E297">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$E2="Done"</formula>
     </cfRule>
@@ -8448,7 +8572,7 @@
       <formula>$E2="Planned"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H295">
+  <conditionalFormatting sqref="H2:H297">
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
       <formula>$H2="Critical"</formula>
     </cfRule>
@@ -8463,13 +8587,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E2:E295" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
+    <dataValidation sqref="E2:E297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
       <formula1>"Done,Done – client UAT pending,In progress,Pending – decision needed,Pending – data / setup,Pending – development,Pending – other team,Planned"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H295" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G295" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Abdul Hakeem,Fathir,Dinesh,Testing team,To assign"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8483,7 +8607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11334,7 +11458,7 @@
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Fix from Medical HRMS (HR-48)</t>
+          <t>Fixed 27 Oct from Medical HRMS: the copy is switched off and the matching Gender Edu / Department Edu is filled in (HR-48)</t>
         </is>
       </c>
       <c r="G55" s="34" t="inlineStr">
@@ -11344,75 +11468,179 @@
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I55" s="35" t="inlineStr">
         <is>
-          <t>Reproduced 21 Oct</t>
+          <t>Reproduced 21 Oct; unit test; E2E REC-11</t>
         </is>
       </c>
       <c r="J55" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
         <is>
+          <t>B-56</t>
+        </is>
+      </c>
+      <c r="B56" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="34" t="inlineStr">
+        <is>
+          <t>Academic Advisor form</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="inlineStr">
+        <is>
+          <t>Linking an Employee fails on save (same cause as B-26: Gender copied from the Employee)</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>Gender Edu list expects 'Male', the Employee holds 'Gender::1'</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>Same fix as B-26 (HR-48)</t>
+        </is>
+      </c>
+      <c r="G56" s="34" t="inlineStr">
+        <is>
+          <t>HR-48</t>
+        </is>
+      </c>
+      <c r="H56" s="34" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I56" s="35" t="inlineStr">
+        <is>
+          <t>Unit test</t>
+        </is>
+      </c>
+      <c r="J56" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>B-57</t>
+        </is>
+      </c>
+      <c r="B57" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C57" s="34" t="inlineStr">
+        <is>
+          <t>Portals: notification bell</t>
+        </is>
+      </c>
+      <c r="D57" s="35" t="inlineStr">
+        <is>
+          <t>The time under each notification showed HTML code (&lt;span class=frappe-timestamp ...&gt;) instead of '1 minute ago'</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>The time was built as HTML and then escaped</t>
+        </is>
+      </c>
+      <c r="F57" s="35" t="inlineStr">
+        <is>
+          <t>Plain-text time (hr_portal.js)</t>
+        </is>
+      </c>
+      <c r="G57" s="34" t="inlineStr">
+        <is>
+          <t>HR-25</t>
+        </is>
+      </c>
+      <c r="H57" s="34" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I57" s="35" t="inlineStr">
+        <is>
+          <t>Round 2 screenshots</t>
+        </is>
+      </c>
+      <c r="J57" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
           <t>B-27</t>
         </is>
       </c>
-      <c r="B56" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C56" s="34" t="inlineStr">
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C58" s="34" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="D56" s="35" t="inlineStr">
+      <c r="D58" s="35" t="inlineStr">
         <is>
           <t>Logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
-      <c r="E56" s="35" t="inlineStr">
+      <c r="E58" s="35" t="inlineStr">
         <is>
           <t>File not on this copy</t>
         </is>
       </c>
-      <c r="F56" s="35" t="inlineStr">
+      <c r="F58" s="35" t="inlineStr">
         <is>
           <t>Check on the live server</t>
         </is>
       </c>
-      <c r="G56" s="34" t="inlineStr">
+      <c r="G58" s="34" t="inlineStr">
         <is>
           <t>HR-54</t>
         </is>
       </c>
-      <c r="H56" s="34" t="inlineStr">
+      <c r="H58" s="34" t="inlineStr">
         <is>
           <t>Open – check server</t>
         </is>
       </c>
-      <c r="I56" s="35" t="inlineStr">
+      <c r="I58" s="35" t="inlineStr">
         <is>
           <t>Error sweep</t>
         </is>
       </c>
-      <c r="J56" s="34" t="inlineStr">
+      <c r="J58" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J56"/>
-  <conditionalFormatting sqref="H2:H156">
+  <autoFilter ref="A1:J58"/>
+  <conditionalFormatting sqref="H2:H158">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="Fixed"</formula>
     </cfRule>
@@ -11427,7 +11655,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Fixed,Open,Open – other team,Open – check server"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11441,7 +11669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12006,8 +12234,42 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>DEC-16</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Who is told about new employee requests: every HR User and HR Manager login (as built), or a smaller group (for example only the HR Manager, or one person per request type)?</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Built: every enabled HR User / HR Manager login. Changing it is small.</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>HR-25</t>
+        </is>
+      </c>
+      <c r="F17" s="36" t="inlineStr"/>
+      <c r="G17" s="37" t="inlineStr"/>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12018,7 +12280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12063,17 +12325,17 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E2" s="34" t="inlineStr">
@@ -12085,22 +12347,22 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C3" s="35" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E3" s="34" t="inlineStr">
@@ -12122,12 +12384,12 @@
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D4" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E4" s="34" t="inlineStr">
@@ -12144,17 +12406,17 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -12176,12 +12438,12 @@
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -12198,17 +12460,17 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -12220,7 +12482,7 @@
     <row r="8">
       <c r="A8" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
@@ -12230,12 +12492,12 @@
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -12257,12 +12519,12 @@
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -12279,17 +12541,17 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -12301,22 +12563,22 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -12333,17 +12595,17 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -12360,17 +12622,17 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
@@ -12382,7 +12644,7 @@
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
@@ -12392,12 +12654,12 @@
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
@@ -12409,7 +12671,7 @@
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
@@ -12419,12 +12681,12 @@
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
@@ -12436,32 +12698,59 @@
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E17" s="34" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12280,7 +12280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12325,17 +12325,17 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E2" s="34" t="inlineStr">
@@ -12352,17 +12352,17 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C3" s="35" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E3" s="34" t="inlineStr">
@@ -12374,22 +12374,22 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D4" s="35" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E4" s="34" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -12433,17 +12433,17 @@
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -12487,17 +12487,17 @@
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -12509,7 +12509,7 @@
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
@@ -12519,12 +12519,12 @@
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -12546,12 +12546,12 @@
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -12568,17 +12568,17 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -12590,22 +12590,22 @@
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -12622,17 +12622,17 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
@@ -12649,17 +12649,17 @@
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
@@ -12671,7 +12671,7 @@
     <row r="15">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
@@ -12698,7 +12698,7 @@
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
@@ -12725,32 +12725,59 @@
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E17" s="34" t="inlineStr">
+      <c r="E18" s="34" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="I28" s="35" t="inlineStr">
         <is>
-          <t>Round 2 (27 Oct): Rejection Reason is required to reject (10 request types, including Leave Application) and the employee reads it; each request shows its history (every status change, who and when) on the Employee Portal; notifications in the bell, and by e-mail where the mail account works: HR when an employee sends a request, the employee at every later step, with a link that opens the request. Notifications are queued only after the save is committed. Tested: unit tests and browser APR-02, APR-09, APR-10, APR-11.</t>
+          <t>Round 2 (27 Oct): Rejection Reason is required to reject (10 request types, including Leave Application) and the employee reads it; each request shows its history (every status change, who and when) on the Employee Portal; notifications in the bell, and by e-mail where the mail account works: HR when an employee sends a request, the employee at every later step, with a link that opens the request. Notifications are queued only after the save is committed. Tested: unit tests and browser APR-02, APR-09, APR-10, APR-11. Leave e-mails (27 Oct): HRMS e-mails the leave approver and the employee with two new Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal); the migrate chooses them in HR Settings where empty (CL-40). E-mail check on this copy with a local mail catcher (nothing left the machine): a request and a leave rejected with a reason gave the 7 expected e-mails (4 to HR logins, 2 to the employee, 1 to the leave approver) with the right text and links.</t>
         </is>
       </c>
       <c r="J28" s="35" t="inlineStr">
         <is>
-          <t>Testing team: Round 2 cases. E-mails: check on the live server once HR-47 is fixed (Checklist CL-41). Who gets new-request notifications: DEC-16.</t>
+          <t>Testing team: Round 2 cases (TC-LV-19 for the leave e-mails). Delivery from the college e-mail account: check on the live server once HR-47 is fixed (Checklist CL-41). DEC-16 answered: every HR User and HR Manager login.</t>
         </is>
       </c>
       <c r="K28" s="35" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="I61" s="35" t="inlineStr">
         <is>
-          <t>docs/guides/Medical_HRMS_Round_2_Whats_New.pdf (8 pages, for the testing team): what changed, how to test each change, known limits, the 16 Round 2 test cases. The Test Cases workbook has a Round column (filter Round 2) and counts per round. User Guide and Installation and Setup Guide updated for Round 2 (new screenshots, QA data only). Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>docs/guides/Medical_HRMS_Round_2_Whats_New.pdf (8 pages, for the testing team): what changed, how to test each change, known limits, the 17 Round 2 test cases. The Test Cases workbook has a Round column (filter Round 2) and counts per round. User Guide and Installation and Setup Guide updated for Round 2 (new screenshots, QA data only). Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="J61" s="35" t="inlineStr">
@@ -12260,8 +12260,16 @@
           <t>HR-25</t>
         </is>
       </c>
-      <c r="F17" s="36" t="inlineStr"/>
-      <c r="G17" s="37" t="inlineStr"/>
+      <c r="F17" s="36" t="inlineStr">
+        <is>
+          <t>Every HR User and HR Manager login is told (as built).</t>
+        </is>
+      </c>
+      <c r="G17" s="37" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
       <c r="H17" s="34" t="inlineStr">
         <is>
           <t>27 Oct 2026</t>
@@ -12280,7 +12288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12325,17 +12333,17 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Leave e-mails</t>
         </is>
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>HR-76</t>
+          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
         <is>
-          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
+          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
         </is>
       </c>
       <c r="E2" s="34" t="inlineStr">
@@ -12352,17 +12360,17 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C3" s="35" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E3" s="34" t="inlineStr">
@@ -12379,17 +12387,17 @@
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D4" s="35" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E4" s="34" t="inlineStr">
@@ -12401,22 +12409,22 @@
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -12438,12 +12446,12 @@
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -12460,17 +12468,17 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -12492,12 +12500,12 @@
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -12514,17 +12522,17 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -12536,7 +12544,7 @@
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
@@ -12546,12 +12554,12 @@
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -12573,12 +12581,12 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -12595,17 +12603,17 @@
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -12617,22 +12625,22 @@
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
@@ -12649,17 +12657,17 @@
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
@@ -12676,17 +12684,17 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
@@ -12698,7 +12706,7 @@
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
@@ -12708,12 +12716,12 @@
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
@@ -12725,7 +12733,7 @@
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
@@ -12735,12 +12743,12 @@
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
@@ -12752,32 +12760,59 @@
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E18"/>
+  <autoFilter ref="A1:E19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Task_Tracker.xlsx
@@ -15,10 +15,10 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$1:$L$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bugs'!$A$1:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Decisions'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Change Log'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$297,A5)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$298,A5)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="B6" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$297,A6)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$298,A6)</f>
         <v/>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="B7" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$297,A7)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$298,A7)</f>
         <v/>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="B8" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$297,A8)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$298,A8)</f>
         <v/>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B9" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$297,A9)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$298,A9)</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$297,A10)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$298,A10)</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$297,A11)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$298,A11)</f>
         <v/>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="B12" s="23">
-        <f>COUNTIF(Tasks!$E$2:$E$297,A12)</f>
+        <f>COUNTIF(Tasks!$E$2:$E$298,A12)</f>
         <v/>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B16" s="23">
-        <f>COUNTIFS(Tasks!$A$2:$A$297,"HR-*",Tasks!$E$2:$E$297,"Done")+COUNTIFS(Tasks!$A$2:$A$297,"HR-*",Tasks!$E$2:$E$297,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$298,"HR-*",Tasks!$E$2:$E$298,"Done")+COUNTIFS(Tasks!$A$2:$A$298,"HR-*",Tasks!$E$2:$E$298,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C16" s="23">
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>COUNTIF(Tasks!$A$2:$A$297,"HR-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$298,"HR-*")</f>
         <v/>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="B17" s="23">
-        <f>COUNTIFS(Tasks!$A$2:$A$297,"JM-*",Tasks!$E$2:$E$297,"Done")+COUNTIFS(Tasks!$A$2:$A$297,"JM-*",Tasks!$E$2:$E$297,"Done – client UAT pending")</f>
+        <f>COUNTIFS(Tasks!$A$2:$A$298,"JM-*",Tasks!$E$2:$E$298,"Done")+COUNTIFS(Tasks!$A$2:$A$298,"JM-*",Tasks!$E$2:$E$298,"Done – client UAT pending")</f>
         <v/>
       </c>
       <c r="C17" s="23">
@@ -1298,7 +1298,7 @@
         <v/>
       </c>
       <c r="D17" s="23">
-        <f>COUNTIF(Tasks!$A$2:$A$297,"JM-*")</f>
+        <f>COUNTIF(Tasks!$A$2:$A$298,"JM-*")</f>
         <v/>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="B20" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$297,"Earlier (May – 5 Oct 2026)")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$298,"Earlier (May – 5 Oct 2026)")</f>
         <v/>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B21" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$297,"19 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$298,"19 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1344,29 +1344,29 @@
         </is>
       </c>
       <c r="B22" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$297,"20 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$298,"20 Oct 2026")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B23" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$297,"21 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$298,"27 Oct 2026")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B24" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$297,"27 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$298,"21 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="B25" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$297,"22 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$298,"22 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B26" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$297,"23 Oct 2026")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$298,"23 Oct 2026")</f>
         <v/>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="B27" s="23">
-        <f>COUNTIF(Tasks!$D$2:$D$297,"—")</f>
+        <f>COUNTIF(Tasks!$D$2:$D$298,"—")</f>
         <v/>
       </c>
     </row>
@@ -1463,39 +1463,39 @@
         </is>
       </c>
       <c r="B30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A30,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A30,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A30,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A30,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A30,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A30,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A30,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I30" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A30,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A30,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J30" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A30)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A30)</f>
         <v/>
       </c>
     </row>
@@ -1506,39 +1506,39 @@
         </is>
       </c>
       <c r="B31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A31,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A31,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A31,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A31,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A31,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A31,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A31,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I31" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A31,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A31,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J31" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A31)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A31)</f>
         <v/>
       </c>
     </row>
@@ -1549,39 +1549,39 @@
         </is>
       </c>
       <c r="B32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A32,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A32,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A32,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A32,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A32,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A32,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A32,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I32" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A32,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A32,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J32" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A32)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A32)</f>
         <v/>
       </c>
     </row>
@@ -1592,39 +1592,39 @@
         </is>
       </c>
       <c r="B33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A33,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A33,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A33,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A33,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A33,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A33,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A33,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I33" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A33,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A33,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J33" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A33)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A33)</f>
         <v/>
       </c>
     </row>
@@ -1635,39 +1635,39 @@
         </is>
       </c>
       <c r="B34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A34,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A34,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A34,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A34,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A34,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A34,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A34,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I34" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A34,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A34,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J34" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A34)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A34)</f>
         <v/>
       </c>
     </row>
@@ -1678,39 +1678,39 @@
         </is>
       </c>
       <c r="B35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A35,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A35,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A35,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A35,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A35,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A35,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A35,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I35" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A35,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A35,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J35" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A35)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A35)</f>
         <v/>
       </c>
     </row>
@@ -1721,39 +1721,39 @@
         </is>
       </c>
       <c r="B36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A36,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A36,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A36,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A36,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A36,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A36,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A36,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I36" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A36,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A36,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J36" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A36)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A36)</f>
         <v/>
       </c>
     </row>
@@ -1764,39 +1764,39 @@
         </is>
       </c>
       <c r="B37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A37,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A37,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A37,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A37,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A37,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A37,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A37,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I37" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A37,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A37,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J37" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A37)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A37)</f>
         <v/>
       </c>
     </row>
@@ -1807,39 +1807,39 @@
         </is>
       </c>
       <c r="B38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A38,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A38,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A38,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A38,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A38,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A38,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A38,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I38" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A38,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A38,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J38" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A38)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A38)</f>
         <v/>
       </c>
     </row>
@@ -1850,39 +1850,39 @@
         </is>
       </c>
       <c r="B39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A39,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A39,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A39,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A39,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A39,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A39,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A39,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I39" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A39,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A39,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J39" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A39)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A39)</f>
         <v/>
       </c>
     </row>
@@ -1893,39 +1893,39 @@
         </is>
       </c>
       <c r="B40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A40,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A40,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A40,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A40,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A40,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A40,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A40,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I40" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A40,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A40,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J40" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A40)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A40)</f>
         <v/>
       </c>
     </row>
@@ -1936,39 +1936,39 @@
         </is>
       </c>
       <c r="B41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A41,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A41,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A41,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A41,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A41,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A41,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A41,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I41" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A41,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A41,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J41" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A41)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A41)</f>
         <v/>
       </c>
     </row>
@@ -1979,39 +1979,39 @@
         </is>
       </c>
       <c r="B42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A42,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A42,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A42,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A42,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A42,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A42,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A42,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I42" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A42,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A42,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J42" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A42)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A42)</f>
         <v/>
       </c>
     </row>
@@ -2022,39 +2022,39 @@
         </is>
       </c>
       <c r="B43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A43,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A43,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A43,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A43,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A43,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A43,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A43,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I43" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A43,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A43,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J43" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A43)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A43)</f>
         <v/>
       </c>
     </row>
@@ -2065,39 +2065,39 @@
         </is>
       </c>
       <c r="B44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A44,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A44,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A44,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A44,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A44,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A44,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A44,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I44" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A44,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A44,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J44" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A44)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A44)</f>
         <v/>
       </c>
     </row>
@@ -2108,39 +2108,39 @@
         </is>
       </c>
       <c r="B45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A45,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A45,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A45,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A45,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A45,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A45,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A45,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I45" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A45,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A45,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J45" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A45)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A45)</f>
         <v/>
       </c>
     </row>
@@ -2151,39 +2151,39 @@
         </is>
       </c>
       <c r="B46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A46,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A46,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A46,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A46,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A46,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A46,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A46,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I46" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A46,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A46,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J46" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A46)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A46)</f>
         <v/>
       </c>
     </row>
@@ -2194,39 +2194,39 @@
         </is>
       </c>
       <c r="B47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A47,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A47,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A47,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A47,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A47,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A47,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A47,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I47" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A47,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A47,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J47" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A47)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A47)</f>
         <v/>
       </c>
     </row>
@@ -2237,39 +2237,39 @@
         </is>
       </c>
       <c r="B48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A48,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A48,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A48,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A48,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A48,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A48,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A48,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I48" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A48,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A48,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J48" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A48)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A48)</f>
         <v/>
       </c>
     </row>
@@ -2280,39 +2280,39 @@
         </is>
       </c>
       <c r="B49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A49,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A49,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A49,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A49,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A49,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A49,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A49,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I49" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A49,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A49,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J49" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A49)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A49)</f>
         <v/>
       </c>
     </row>
@@ -2323,39 +2323,39 @@
         </is>
       </c>
       <c r="B50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A50,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A50,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A50,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A50,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A50,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A50,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A50,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I50" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A50,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A50,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J50" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A50)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A50)</f>
         <v/>
       </c>
     </row>
@@ -2366,39 +2366,39 @@
         </is>
       </c>
       <c r="B51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A51,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A51,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A51,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A51,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A51,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A51,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A51,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I51" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A51,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A51,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J51" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A51)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A51)</f>
         <v/>
       </c>
     </row>
@@ -2409,39 +2409,39 @@
         </is>
       </c>
       <c r="B52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,B$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A52,Tasks!$E$2:$E$298,B$29)</f>
         <v/>
       </c>
       <c r="C52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,C$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A52,Tasks!$E$2:$E$298,C$29)</f>
         <v/>
       </c>
       <c r="D52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,D$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A52,Tasks!$E$2:$E$298,D$29)</f>
         <v/>
       </c>
       <c r="E52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,E$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A52,Tasks!$E$2:$E$298,E$29)</f>
         <v/>
       </c>
       <c r="F52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,F$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A52,Tasks!$E$2:$E$298,F$29)</f>
         <v/>
       </c>
       <c r="G52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,G$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A52,Tasks!$E$2:$E$298,G$29)</f>
         <v/>
       </c>
       <c r="H52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,H$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A52,Tasks!$E$2:$E$298,H$29)</f>
         <v/>
       </c>
       <c r="I52" s="23">
-        <f>COUNTIFS(Tasks!$B$2:$B$297,$A52,Tasks!$E$2:$E$297,I$29)</f>
+        <f>COUNTIFS(Tasks!$B$2:$B$298,$A52,Tasks!$E$2:$E$298,I$29)</f>
         <v/>
       </c>
       <c r="J52" s="23">
-        <f>COUNTIF(Tasks!$B$2:$B$297,$A52)</f>
+        <f>COUNTIF(Tasks!$B$2:$B$298,$A52)</f>
         <v/>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="B55" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$158,A55)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$160,A55)</f>
         <v/>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="B56" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$158,A56)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$160,A56)</f>
         <v/>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B57" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$158,A57)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$160,A57)</f>
         <v/>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="B58" s="23">
-        <f>COUNTIF(Bugs!$H$2:$H$158,A58)</f>
+        <f>COUNTIF(Bugs!$H$2:$H$160,A58)</f>
         <v/>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="D12" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done – client UAT pending</t>
         </is>
       </c>
       <c r="F12" s="34" t="inlineStr">
@@ -3255,22 +3255,22 @@
       </c>
       <c r="I12" s="35" t="inlineStr">
         <is>
-          <t>Not started. Instructors with an Employee record can already use /app/employee-dashboard.</t>
+          <t>Round 3 (27 Oct): a My HR card on the staff dashboards of the education app (Instructor, Department Head, Dean, Vice Deans, IT, Academic Operations, Student Affairs, Admission, Finance, Clinical, Advisor), for logins linked to an Employee record: leave balances and what's next, the latest requests with their status, Apply for Leave, New Request (the 11 services) and View, with the same windows as the Employee Portal (moved to public/js/self_service.js). Placed after each dashboard's first row of figures, in its colours, dark mode and Arabic; nothing in the education app changed. Staff without an Employee record see no card. Tested: 111/111 browser checks (10 new: SHR-01 - SHR-10), 53 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; card placement checked on 11 staff dashboards (8 with figures, Advisor under its heading, Dean and Department Head in the browser tests); Error Log: only test-caused entries, removed.</t>
         </is>
       </c>
       <c r="J12" s="35" t="inlineStr">
         <is>
-          <t>Add the request and leave cards to the Instructor / HOD dashboards from Medical HRMS (page scripts in this app).</t>
+          <t>Testing team: Round 3 cases TC-STF-01 - 10 (docs/guides/Medical_HRMS_Round_3_Whats_New.pdf). Most instructors have no Employee record yet (HR-55), so they see the card once HR links them.</t>
         </is>
       </c>
       <c r="K12" s="35" t="inlineStr">
         <is>
-          <t>HRM_TASK_TRACKER.md</t>
+          <t>public/js/staff_hr_card.js; public/js/self_service.js</t>
         </is>
       </c>
       <c r="L12" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -6377,22 +6377,22 @@
     <row r="63">
       <c r="A63" s="33" t="inlineStr">
         <is>
-          <t>HR-74</t>
+          <t>HR-78</t>
         </is>
       </c>
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C63" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide and User Guide (PDF)</t>
+          <t>Round 3 feature document and test cases</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
@@ -6417,44 +6417,44 @@
       </c>
       <c r="I63" s="35" t="inlineStr">
         <is>
-          <t>Two PDF guides in docs/guides: Installation and Setup Guide (21 pages: install, update, checks, first-time setup, leave year, sick leave, Jameah setup, Ministry agent account, staff data sheets, testing, troubleshooting, commands) and User Guide (30 pages: Employee Portal and the leave flow, every request, HR Portal, leave approvals and returns, recruitment, Ministry data, Academic Presence, Jameah pages, approvers, how to test and report bugs, Q&amp;A). 31 screenshots from the test site with QA test data only. Sources (HTML) and build.py kept in docs/guides/src so the guides can be rebuilt after changes. Writing them found two bugs (B-54, B-55). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>docs/guides/Medical_HRMS_Round_3_Whats_New.pdf (5 pages, for the testing team): the My HR card on the staff dashboards, where it is on each dashboard, how to test it, known limits, the 10 Round 3 test cases (TC-STF-01 - 10, filter Round 3 in the Test Cases workbook). User Guide (section 2.11, Q&amp;A) and Installation Guide (troubleshooting) updated. Re-tested: 111/111 browser checks (10 new: SHR-01 - SHR-10), 53 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; card placement checked on 11 staff dashboards (8 with figures, Advisor under its heading, Dean and Department Head in the browser tests); Error Log: only test-caused entries, removed.</t>
         </is>
       </c>
       <c r="J63" s="35" t="inlineStr">
         <is>
-          <t>HR, managers and the testing team read the User Guide; the server admin the Installation Guide (Checklist CL-37). Rebuild after changes: python docs/guides/src/build.py.</t>
+          <t>Give the document and the workbook to the testing team with Round 2, after both are on their test server (Checklist CL-42).</t>
         </is>
       </c>
       <c r="K63" s="35" t="inlineStr">
         <is>
-          <t>docs/guides</t>
+          <t>docs/guides; Test Cases workbook</t>
         </is>
       </c>
       <c r="L63" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-74</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
         <is>
-          <t>HR dashboard</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C64" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college design</t>
+          <t>Installation and Setup Guide and User Guide (PDF)</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="I64" s="35" t="inlineStr">
         <is>
-          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
+          <t>Two PDF guides in docs/guides: Installation and Setup Guide (21 pages: install, update, checks, first-time setup, leave year, sick leave, Jameah setup, Ministry agent account, staff data sheets, testing, troubleshooting, commands) and User Guide (30 pages: Employee Portal and the leave flow, every request, HR Portal, leave approvals and returns, recruitment, Ministry data, Academic Presence, Jameah pages, approvers, how to test and report bugs, Q&amp;A). 31 screenshots from the test site with QA test data only. Sources (HTML) and build.py kept in docs/guides/src so the guides can be rebuilt after changes. Writing them found two bugs (B-54, B-55). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="J64" s="35" t="inlineStr">
         <is>
-          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
+          <t>HR, managers and the testing team read the User Guide; the server admin the Installation Guide (Checklist CL-37). Rebuild after changes: python docs/guides/src/build.py.</t>
         </is>
       </c>
       <c r="K64" s="35" t="inlineStr">
         <is>
-          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
+          <t>docs/guides</t>
         </is>
       </c>
       <c r="L64" s="34" t="inlineStr">
@@ -6501,17 +6501,17 @@
     <row r="65">
       <c r="A65" s="33" t="inlineStr">
         <is>
-          <t>HR-62</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="B65" s="34" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>HR dashboard</t>
         </is>
       </c>
       <c r="C65" s="35" t="inlineStr">
         <is>
-          <t>HR User could not open the Holiday List ('Not permitted')</t>
+          <t>HR Portal and Employee Portal in the new college design</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
@@ -6536,44 +6536,44 @@
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I65" s="35" t="inlineStr">
         <is>
-          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
+          <t>The college portal design: left menu with sections, top bar with breadcrumb, EN/AR, dark mode, notifications and account menu, page heading, 'Today at a Glance' cards. Covers the HR Dashboard, Employee Dashboard, Academic Presence and Jameah Data Check; menu entries only show pages the user can open; phone layout; right-to-left Arabic with 216 new Arabic translations. Our own code and class names, so changes in other apps cannot break these pages.</t>
         </is>
       </c>
       <c r="J65" s="35" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>Client to review the look; standard Frappe lists and forms keep the normal desk.</t>
         </is>
       </c>
       <c r="K65" s="35" t="inlineStr">
         <is>
-          <t>hr_core_permissions.py</t>
+          <t>hr_portal.js; hr_portal.css; translations/ar.csv</t>
         </is>
       </c>
       <c r="L65" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>HR-46</t>
+          <t>HR-62</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C66" s="35" t="inlineStr">
         <is>
-          <t>Full end-to-end test with error sweep (round 3)</t>
+          <t>HR User could not open the Holiday List ('Not permitted')</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
@@ -6598,22 +6598,22 @@
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I66" s="35" t="inlineStr">
         <is>
-          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
+          <t>ERPNext grants Holiday List to HR Manager only, but HR Users manage employees (whose form links a holiday list) and check holidays when approving leave. HR User now has read-only access.</t>
         </is>
       </c>
       <c r="J66" s="35" t="inlineStr">
         <is>
-          <t>Client UAT.</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="K66" s="35" t="inlineStr">
         <is>
-          <t>Test Report</t>
+          <t>hr_core_permissions.py</t>
         </is>
       </c>
       <c r="L66" s="34" t="inlineStr">
@@ -6625,37 +6625,37 @@
     <row r="67">
       <c r="A67" s="33" t="inlineStr">
         <is>
-          <t>HR-47</t>
+          <t>HR-46</t>
         </is>
       </c>
       <c r="B67" s="34" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C67" s="35" t="inlineStr">
         <is>
-          <t>System e-mail account password cannot be decrypted</t>
+          <t>Full end-to-end test with error sweep (round 3)</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G67" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H67" s="34" t="inlineStr">
@@ -6665,17 +6665,17 @@
       </c>
       <c r="I67" s="35" t="inlineStr">
         <is>
-          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
+          <t>All modules plus an error sweep of every page for four roles. Results in the Test Report.</t>
         </is>
       </c>
       <c r="J67" s="35" t="inlineStr">
         <is>
-          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
+          <t>Client UAT.</t>
         </is>
       </c>
       <c r="K67" s="35" t="inlineStr">
         <is>
-          <t>Error Log; Email Queue</t>
+          <t>Test Report</t>
         </is>
       </c>
       <c r="L67" s="34" t="inlineStr">
@@ -6687,89 +6687,89 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>HR-48</t>
+          <t>HR-47</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C68" s="35" t="inlineStr">
         <is>
-          <t>Instructor form: linking an Employee fails on save</t>
+          <t>System e-mail account password cannot be decrypted</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>Done – client UAT pending</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G68" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I68" s="35" t="inlineStr">
         <is>
-          <t>Round 2 (27 Oct), fixed from Medical HRMS without touching the education app: the copy of gender / department from the Employee is switched off on Instructor and Academic Advisor (Property Setters) and the matching Gender Edu / Department Edu value is filled in instead, on the form and on save. The Academic Advisor form had the same problem (B-56). Tested: unit tests and browser REC-11.</t>
+          <t>Error Log: 'Failed to decrypt key Email Account.Notifications.password' 10 times (13–20 Oct); 3 e-mails stuck. Every system e-mail fails while this is broken.</t>
         </is>
       </c>
       <c r="J68" s="35" t="inlineStr">
         <is>
-          <t>Testing team: TC-EMP-13, TC-EMP-14.</t>
+          <t>On the live server: open Email Account 'Notifications', re-enter the password, save, send a test e-mail. Check the Error Log there for the same error.</t>
         </is>
       </c>
       <c r="K68" s="35" t="inlineStr">
         <is>
-          <t>staff_links.py; public/js/staff_employee_link.js</t>
+          <t>Error Log; Email Queue</t>
         </is>
       </c>
       <c r="L68" s="34" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="33" t="inlineStr">
         <is>
-          <t>HR-49</t>
+          <t>HR-48</t>
         </is>
       </c>
       <c r="B69" s="34" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C69" s="35" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Instructor form: linking an Employee fails on save</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Done – client UAT pending</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
@@ -6789,29 +6789,29 @@
       </c>
       <c r="I69" s="35" t="inlineStr">
         <is>
-          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
+          <t>Round 2 (27 Oct), fixed from Medical HRMS without touching the education app: the copy of gender / department from the Employee is switched off on Instructor and Academic Advisor (Property Setters) and the matching Gender Edu / Department Edu value is filled in instead, on the form and on save. The Academic Advisor form had the same problem (B-56). Tested: unit tests and browser REC-11.</t>
         </is>
       </c>
       <c r="J69" s="35" t="inlineStr">
         <is>
-          <t>HR to use it to complete the data (HR-50 sheet).</t>
+          <t>Testing team: TC-EMP-13, TC-EMP-14.</t>
         </is>
       </c>
       <c r="K69" s="35" t="inlineStr">
         <is>
-          <t>report/employees_missing_ministry_data</t>
+          <t>staff_links.py; public/js/staff_employee_link.js</t>
         </is>
       </c>
       <c r="L69" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>HR-50</t>
+          <t>HR-49</t>
         </is>
       </c>
       <c r="B70" s="34" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="C70" s="35" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
@@ -6851,17 +6851,17 @@
       </c>
       <c r="I70" s="35" t="inlineStr">
         <is>
-          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
+          <t>Report (HR Portal &gt; Ministry (Jameah)) listing each employee the Ministry views send with every Ministry-mandatory value still empty, named as the Employee form field (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). Read from the views themselves, so it shows exactly what the Ministry would receive.</t>
         </is>
       </c>
       <c r="J70" s="35" t="inlineStr">
         <is>
-          <t>HR to fill the sheet for all non-academic staff.</t>
+          <t>HR to use it to complete the data (HR-50 sheet).</t>
         </is>
       </c>
       <c r="K70" s="35" t="inlineStr">
         <is>
-          <t>employee_data_sheet.py</t>
+          <t>report/employees_missing_ministry_data</t>
         </is>
       </c>
       <c r="L70" s="34" t="inlineStr">
@@ -6873,17 +6873,17 @@
     <row r="71">
       <c r="A71" s="33" t="inlineStr">
         <is>
-          <t>HR-51</t>
+          <t>HR-50</t>
         </is>
       </c>
       <c r="B71" s="34" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C71" s="35" t="inlineStr">
         <is>
-          <t>Unused duplicate of the applicant Ministry fields removed</t>
+          <t>Data sheet for non-academic staff</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
@@ -6908,22 +6908,22 @@
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I71" s="35" t="inlineStr">
         <is>
-          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
+          <t>From the report (HR Manager only): Download Data Sheet (current values filled in, Ministry-mandatory empty cells red, Ministry dropdowns), Check (nothing saved, result sheet per row), Import (saved through the normal Employee checks). Tested: bad date / unknown nationality refused; valid row checked then imported.</t>
         </is>
       </c>
       <c r="J71" s="35" t="inlineStr">
         <is>
-          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
+          <t>HR to fill the sheet for all non-academic staff.</t>
         </is>
       </c>
       <c r="K71" s="35" t="inlineStr">
         <is>
-          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
+          <t>employee_data_sheet.py</t>
         </is>
       </c>
       <c r="L71" s="34" t="inlineStr">
@@ -6935,57 +6935,57 @@
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>HR-52</t>
+          <t>HR-51</t>
         </is>
       </c>
       <c r="B72" s="34" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C72" s="35" t="inlineStr">
         <is>
-          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
+          <t>Unused duplicate of the applicant Ministry fields removed</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
         <is>
-          <t>HR + Ministry contact</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I72" s="35" t="inlineStr">
         <is>
-          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
+          <t>The duplicate was on HRMS's own 'Job Applicant' (16 Ministry fields and 4 child tables, added by an old setup patch on 11 Sep; recruitment uses our Employee Job Applicant). Old patch retired; a clean-up patch removes the copy wherever it still exists, only if it holds no data (it reports anything it keeps). Tested on this site.</t>
         </is>
       </c>
       <c r="J72" s="35" t="inlineStr">
         <is>
-          <t>Confirm whether 9-digit numbers must be accepted.</t>
+          <t>Watch the migrate output on the live server for 'Kept (they hold data...)'.</t>
         </is>
       </c>
       <c r="K72" s="35" t="inlineStr">
         <is>
-          <t>ministry_lookup_validation.py</t>
+          <t>patches/remove_duplicate_job_applicant_ministry_fields.py</t>
         </is>
       </c>
       <c r="L72" s="34" t="inlineStr">
@@ -6997,17 +6997,17 @@
     <row r="73">
       <c r="A73" s="33" t="inlineStr">
         <is>
-          <t>HR-53</t>
+          <t>HR-52</t>
         </is>
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C73" s="35" t="inlineStr">
         <is>
-          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
+          <t>Identity number length: 9–10 digits (spec) vs exactly 10 (current check)</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
@@ -7017,37 +7017,37 @@
       </c>
       <c r="E73" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Ministry contact</t>
         </is>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I73" s="35" t="inlineStr">
         <is>
-          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
+          <t>Current rule: National ID and Iqama = exactly 10 digits (real format). Ministry document says civil registry 9–10 digits.</t>
         </is>
       </c>
       <c r="J73" s="35" t="inlineStr">
         <is>
-          <t>Complete or delete the demo record before go-live.</t>
+          <t>Confirm whether 9-digit numbers must be accepted.</t>
         </is>
       </c>
       <c r="K73" s="35" t="inlineStr">
         <is>
-          <t>Employee EMP-00001</t>
+          <t>ministry_lookup_validation.py</t>
         </is>
       </c>
       <c r="L73" s="34" t="inlineStr">
@@ -7059,7 +7059,7 @@
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>HR-54</t>
+          <t>HR-53</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C74" s="35" t="inlineStr">
         <is>
-          <t>Website logo file missing (/files/rchs-logo.png)</t>
+          <t>Demo employee EMP-00001 misses mandatory Ministry fields</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H74" s="34" t="inlineStr">
@@ -7099,17 +7099,17 @@
       </c>
       <c r="I74" s="35" t="inlineStr">
         <is>
-          <t>Missing on the local copy; every page requests it.</t>
+          <t>It can't be saved again until completed. Belongs to the demo company 'Medical College'.</t>
         </is>
       </c>
       <c r="J74" s="35" t="inlineStr">
         <is>
-          <t>Check the file exists on the live server.</t>
+          <t>Complete or delete the demo record before go-live.</t>
         </is>
       </c>
       <c r="K74" s="35" t="inlineStr">
         <is>
-          <t>Website Settings</t>
+          <t>Employee EMP-00001</t>
         </is>
       </c>
       <c r="L74" s="34" t="inlineStr">
@@ -7121,7 +7121,7 @@
     <row r="75">
       <c r="A75" s="33" t="inlineStr">
         <is>
-          <t>HR-55</t>
+          <t>HR-54</t>
         </is>
       </c>
       <c r="B75" s="34" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="C75" s="35" t="inlineStr">
         <is>
-          <t>Link the 216 existing Instructors to Employees</t>
+          <t>Website logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
@@ -7146,32 +7146,32 @@
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I75" s="35" t="inlineStr">
         <is>
-          <t>Tool ready (HR-35). 1 of 216 linked.</t>
+          <t>Missing on the local copy; every page requests it.</t>
         </is>
       </c>
       <c r="J75" s="35" t="inlineStr">
         <is>
-          <t>HR fills the Instructor data sheet; run the import with commit.</t>
+          <t>Check the file exists on the live server.</t>
         </is>
       </c>
       <c r="K75" s="35" t="inlineStr">
         <is>
-          <t>instructor_data_sheet.py</t>
+          <t>Website Settings</t>
         </is>
       </c>
       <c r="L75" s="34" t="inlineStr">
@@ -7183,17 +7183,17 @@
     <row r="76">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>HR-56</t>
+          <t>HR-55</t>
         </is>
       </c>
       <c r="B76" s="34" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C76" s="35" t="inlineStr">
         <is>
-          <t>Connect attendance devices</t>
+          <t>Link the 216 existing Instructors to Employees</t>
         </is>
       </c>
       <c r="D76" s="34" t="inlineStr">
@@ -7208,32 +7208,32 @@
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
         <is>
-          <t>HR + IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I76" s="35" t="inlineStr">
         <is>
-          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
+          <t>Tool ready (HR-35). 1 of 216 linked.</t>
         </is>
       </c>
       <c r="J76" s="35" t="inlineStr">
         <is>
-          <t>Connect devices; map device user IDs to Employees.</t>
+          <t>HR fills the Instructor data sheet; run the import with commit.</t>
         </is>
       </c>
       <c r="K76" s="35" t="inlineStr">
         <is>
-          <t>bfac883</t>
+          <t>instructor_data_sheet.py</t>
         </is>
       </c>
       <c r="L76" s="34" t="inlineStr">
@@ -7245,7 +7245,7 @@
     <row r="77">
       <c r="A77" s="33" t="inlineStr">
         <is>
-          <t>HR-57</t>
+          <t>HR-56</t>
         </is>
       </c>
       <c r="B77" s="34" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="C77" s="35" t="inlineStr">
         <is>
-          <t>Set the Academic Holiday List</t>
+          <t>Connect attendance devices</t>
         </is>
       </c>
       <c r="D77" s="34" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="G77" s="34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + IT</t>
         </is>
       </c>
       <c r="H77" s="34" t="inlineStr">
@@ -7285,17 +7285,17 @@
       </c>
       <c r="I77" s="35" t="inlineStr">
         <is>
-          <t>Not set; the page warns about it.</t>
+          <t>Presence page already uses device check-ins when they exist (HRMS Employee Checkin).</t>
         </is>
       </c>
       <c r="J77" s="35" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
+          <t>Connect devices; map device user IDs to Employees.</t>
         </is>
       </c>
       <c r="K77" s="35" t="inlineStr">
         <is>
-          <t>academic_presence_setup.py</t>
+          <t>bfac883</t>
         </is>
       </c>
       <c r="L77" s="34" t="inlineStr">
@@ -7307,17 +7307,17 @@
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>HR-58</t>
+          <t>HR-57</t>
         </is>
       </c>
       <c r="B78" s="34" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C78" s="35" t="inlineStr">
         <is>
-          <t>Deploy to the live server</t>
+          <t>Set the Academic Holiday List</t>
         </is>
       </c>
       <c r="D78" s="34" t="inlineStr">
@@ -7332,69 +7332,69 @@
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G78" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I78" s="35" t="inlineStr">
         <is>
-          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
+          <t>Not set; the page warns about it.</t>
         </is>
       </c>
       <c r="J78" s="35" t="inlineStr">
         <is>
-          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
+          <t>HR Settings -&gt; Academic Holiday List; tick event types that suspend classes.</t>
         </is>
       </c>
       <c r="K78" s="35" t="inlineStr">
         <is>
-          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
+          <t>academic_presence_setup.py</t>
         </is>
       </c>
       <c r="L78" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="33" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>HR-58</t>
         </is>
       </c>
       <c r="B79" s="34" t="inlineStr">
         <is>
-          <t>Jameah</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C79" s="35" t="inlineStr">
         <is>
-          <t>Research: Jameah system, Ministry documents, view contract</t>
+          <t>Deploy to the live server</t>
         </is>
       </c>
       <c r="D79" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E79" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G79" s="34" t="inlineStr">
@@ -7409,29 +7409,29 @@
       </c>
       <c r="I79" s="35" t="inlineStr">
         <is>
-          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
+          <t>Branches pushed: fix/hrm-e2e-approval-permission-bugs, feature/jameah-ministry-views (contains both). 22 Oct: feature/uat-2026-10-22 has all work to date (portal design, leave flow, Faculty views, reports) - the branch to test and deploy. Later on 22 Oct develop (with Fathir's job application update) was merged into it, so it now contains develop too. 23 Oct: every branch merged into develop (HR-71); develop is the branch to deploy.</t>
         </is>
       </c>
       <c r="J79" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>On the server: check out develop, bench migrate, build, restart; smoke-test with the Test Cases workbook (Checklist CL-01 - CL-05).</t>
         </is>
       </c>
       <c r="K79" s="35" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>GitHub phpdevpro/edu-alriyada-hrm</t>
         </is>
       </c>
       <c r="L79" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="C80" s="35" t="inlineStr">
         <is>
-          <t>Ministry views for Employees (5) and Students (10)</t>
+          <t>Research: Jameah system, Ministry documents, view contract</t>
         </is>
       </c>
       <c r="D80" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>19 Oct 2026</t>
         </is>
       </c>
       <c r="E80" s="34" t="inlineStr">
@@ -7466,22 +7466,22 @@
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I80" s="35" t="inlineStr">
         <is>
-          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
+          <t>Ministry schema V0.1, field mapping HTML, 'Views Data' PDF and code workbooks reviewed; findings shared.</t>
         </is>
       </c>
       <c r="J80" s="35" t="inlineStr">
         <is>
-          <t>Deploy (HR-58).</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K80" s="35" t="inlineStr">
         <is>
-          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="L80" s="34" t="inlineStr">
@@ -7493,7 +7493,7 @@
     <row r="81">
       <c r="A81" s="33" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="B81" s="34" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C81" s="35" t="inlineStr">
         <is>
-          <t>Code crosswalk (Jameah Code Map)</t>
+          <t>Ministry views for Employees (5) and Students (10)</t>
         </is>
       </c>
       <c r="D81" s="34" t="inlineStr">
@@ -7528,34 +7528,34 @@
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I81" s="35" t="inlineStr">
         <is>
-          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
+          <t>15 views with the HTML column names; Ministry codes only; faculty excluded from Employee views; source records never changed.</t>
         </is>
       </c>
       <c r="J81" s="35" t="inlineStr">
         <is>
-          <t>Review 3 values (JM-11).</t>
+          <t>Deploy (HR-58).</t>
         </is>
       </c>
       <c r="K81" s="35" t="inlineStr">
         <is>
-          <t>jameah/code_map.py</t>
+          <t>d690cb7; jameah/views.py; jameah/VIEWS.md</t>
         </is>
       </c>
       <c r="L81" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>JM-04</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C82" s="35" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>Code crosswalk (Jameah Code Map)</t>
         </is>
       </c>
       <c r="D82" s="34" t="inlineStr">
@@ -7595,29 +7595,29 @@
       </c>
       <c r="I82" s="35" t="inlineStr">
         <is>
-          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
+          <t>299 college values mapped to official codes by meaning; wrong codes in the college master lists (City 90, REL001...) no longer reach the Ministry.</t>
         </is>
       </c>
       <c r="J82" s="35" t="inlineStr">
         <is>
-          <t>Fill 6 values (JM-10).</t>
+          <t>Review 3 values (JM-11).</t>
         </is>
       </c>
       <c r="K82" s="35" t="inlineStr">
         <is>
-          <t>Jameah Settings</t>
+          <t>jameah/code_map.py</t>
         </is>
       </c>
       <c r="L82" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="33" t="inlineStr">
         <is>
-          <t>JM-05</t>
+          <t>JM-04</t>
         </is>
       </c>
       <c r="B83" s="34" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="C83" s="35" t="inlineStr">
         <is>
-          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="D83" s="34" t="inlineStr">
@@ -7657,29 +7657,29 @@
       </c>
       <c r="I83" s="35" t="inlineStr">
         <is>
-          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
+          <t>Institution values; P18, country 101 and GPA type pre-filled.</t>
         </is>
       </c>
       <c r="J83" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Fill 6 values (JM-10).</t>
         </is>
       </c>
       <c r="K83" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py</t>
+          <t>Jameah Settings</t>
         </is>
       </c>
       <c r="L83" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>JM-06</t>
+          <t>JM-05</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="C84" s="35" t="inlineStr">
         <is>
-          <t>Independent verification of every view</t>
+          <t>Academic figures (GPA, credit hours) refreshed hourly</t>
         </is>
       </c>
       <c r="D84" s="34" t="inlineStr">
@@ -7714,34 +7714,34 @@
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I84" s="35" t="inlineStr">
         <is>
-          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
+          <t>Follows the transcript; view answers in ~3 s instead of 30 s. 22 Oct: only one rebuild runs at a time, so a migrate no longer fails when it overlaps the hourly refresh (B-43).</t>
         </is>
       </c>
       <c r="J84" s="35" t="inlineStr">
         <is>
-          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K84" s="35" t="inlineStr">
         <is>
-          <t>jameah/verify.py; test_jameah.py</t>
+          <t>jameah/summary.py</t>
         </is>
       </c>
       <c r="L84" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="33" t="inlineStr">
         <is>
-          <t>JM-18</t>
+          <t>JM-06</t>
         </is>
       </c>
       <c r="B85" s="34" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="C85" s="35" t="inlineStr">
         <is>
-          <t>Ministry GPA and credit hours = the college's official figures</t>
+          <t>Independent verification of every view</t>
         </is>
       </c>
       <c r="D85" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E85" s="34" t="inlineStr">
@@ -7781,17 +7781,17 @@
       </c>
       <c r="I85" s="35" t="inlineStr">
         <is>
-          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
+          <t>All views match the source records value by value; 0 invalid codes. Re-run 21 Oct after the GPA update (JM-18) and with the Faculty views (JM-14): all 23 OK.</t>
         </is>
       </c>
       <c r="J85" s="35" t="inlineStr">
         <is>
-          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
+          <t>Re-run after data changes: bench execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="K85" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py; jameah/verify.py</t>
+          <t>jameah/verify.py; test_jameah.py</t>
         </is>
       </c>
       <c r="L85" s="34" t="inlineStr">
@@ -7803,7 +7803,7 @@
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>JM-19</t>
+          <t>JM-18</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
@@ -7813,22 +7813,22 @@
       </c>
       <c r="C86" s="35" t="inlineStr">
         <is>
-          <t>Hourly academic summary refresh slows the site while it runs</t>
+          <t>Ministry GPA and credit hours = the college's official figures</t>
         </is>
       </c>
       <c r="D86" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E86" s="34" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem + Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G86" s="34" t="inlineStr">
@@ -7838,34 +7838,34 @@
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I86" s="35" t="inlineStr">
         <is>
-          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
+          <t>Found 21 Oct: the education app's master branch now has one official GPA calculation (retakes, superseded fails, XF/W, legacy baselines) and one for credit hours. Our views still used the old rules: GPA differed from the transcript for 1,197 of 2,854 students and required hours for ~10%. The hourly summary now reads those official functions (read only; the education app is not changed); verified: GPA equals the transcript for 2,854 of 2,854 students; all 15 views OK. Refresh moved to the long queue (~7 min).</t>
         </is>
       </c>
       <c r="J86" s="35" t="inlineStr">
         <is>
-          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
+          <t>Deploy together with the education app's master update (HR-58); re-run verify on the live server.</t>
         </is>
       </c>
       <c r="K86" s="35" t="inlineStr">
         <is>
-          <t>jameah/summary.py; hooks.py hourly_long</t>
+          <t>jameah/summary.py; jameah/verify.py</t>
         </is>
       </c>
       <c r="L86" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="33" t="inlineStr">
         <is>
-          <t>JM-07</t>
+          <t>JM-19</t>
         </is>
       </c>
       <c r="B87" s="34" t="inlineStr">
@@ -7875,22 +7875,22 @@
       </c>
       <c r="C87" s="35" t="inlineStr">
         <is>
-          <t>Jameah Data Check page and Employee preview</t>
+          <t>Hourly academic summary refresh slows the site while it runs</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Abdul Hakeem + Server admin</t>
         </is>
       </c>
       <c r="G87" s="34" t="inlineStr">
@@ -7900,34 +7900,34 @@
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I87" s="35" t="inlineStr">
         <is>
-          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
+          <t>Seen 22 Oct on the development machine (8 GB, shared with the editor): the hourly rebuild of the GPA / credit-hour summary for 3,357 students takes 10-13 minutes, and while it runs pages take 15-45 s (login to the desk 45 s). Tests run between two refreshes pass.</t>
         </is>
       </c>
       <c r="J87" s="35" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Check page speed on the live server at the top of the hour. If it is noticeable: refresh every few hours or at night, or only students whose marks changed.</t>
         </is>
       </c>
       <c r="K87" s="35" t="inlineStr">
         <is>
-          <t>page/jameah_data_check</t>
+          <t>jameah/summary.py; hooks.py hourly_long</t>
         </is>
       </c>
       <c r="L87" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>JM-08</t>
+          <t>JM-07</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
@@ -7937,27 +7937,27 @@
       </c>
       <c r="C88" s="35" t="inlineStr">
         <is>
-          <t>Read-only database account for the Ministry agent</t>
+          <t>Jameah Data Check page and Employee preview</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="E88" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="G88" s="34" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H88" s="34" t="inlineStr">
@@ -7967,17 +7967,17 @@
       </c>
       <c r="I88" s="35" t="inlineStr">
         <is>
-          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
+          <t>HR sees gaps, invalid codes, settings to fill and source problems; 'Ministry (Jameah) Data' button on the Employee form.</t>
         </is>
       </c>
       <c r="J88" s="35" t="inlineStr">
         <is>
-          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="K88" s="35" t="inlineStr">
         <is>
-          <t>jameah/README.md</t>
+          <t>page/jameah_data_check</t>
         </is>
       </c>
       <c r="L88" s="34" t="inlineStr">
@@ -7989,7 +7989,7 @@
     <row r="89">
       <c r="A89" s="33" t="inlineStr">
         <is>
-          <t>JM-09</t>
+          <t>JM-08</t>
         </is>
       </c>
       <c r="B89" s="34" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C89" s="35" t="inlineStr">
         <is>
-          <t>Confirm view and column names with the Ministry</t>
+          <t>Read-only database account for the Ministry agent</t>
         </is>
       </c>
       <c r="D89" s="34" t="inlineStr">
@@ -8009,37 +8009,37 @@
       </c>
       <c r="E89" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="G89" s="34" t="inlineStr">
         <is>
-          <t>Ministry contact (Ms. Najah)</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I89" s="35" t="inlineStr">
         <is>
-          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
+          <t>SQL generated by medical_hrms.jameah.views.grant_statements.</t>
         </is>
       </c>
       <c r="J89" s="35" t="inlineStr">
         <is>
-          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
+          <t>Create the account on the live server; give the Ministry host, port, database, user, password.</t>
         </is>
       </c>
       <c r="K89" s="35" t="inlineStr">
         <is>
-          <t>Jameah report</t>
+          <t>jameah/README.md</t>
         </is>
       </c>
       <c r="L89" s="34" t="inlineStr">
@@ -8051,7 +8051,7 @@
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>JM-10</t>
+          <t>JM-09</t>
         </is>
       </c>
       <c r="B90" s="34" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="C90" s="35" t="inlineStr">
         <is>
-          <t>Fill Jameah Settings (6 values)</t>
+          <t>Confirm view and column names with the Ministry</t>
         </is>
       </c>
       <c r="D90" s="34" t="inlineStr">
@@ -8076,32 +8076,32 @@
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="G90" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs</t>
+          <t>Ministry contact (Ms. Najah)</t>
         </is>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I90" s="35" t="inlineStr">
         <is>
-          <t>Empty values are sent as empty.</t>
+          <t>Views use the HTML names; Ministry schema V0.1 names some columns differently (list in the Jameah report).</t>
         </is>
       </c>
       <c r="J90" s="35" t="inlineStr">
         <is>
-          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
+          <t>Ask which names the Jameah agent reads; renaming is a small change.</t>
         </is>
       </c>
       <c r="K90" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-settings</t>
+          <t>Jameah report</t>
         </is>
       </c>
       <c r="L90" s="34" t="inlineStr">
@@ -8113,7 +8113,7 @@
     <row r="91">
       <c r="A91" s="33" t="inlineStr">
         <is>
-          <t>JM-11</t>
+          <t>JM-10</t>
         </is>
       </c>
       <c r="B91" s="34" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="C91" s="35" t="inlineStr">
         <is>
-          <t>Map 3 college values to Ministry codes</t>
+          <t>Fill Jameah Settings (6 values)</t>
         </is>
       </c>
       <c r="D91" s="34" t="inlineStr">
@@ -8153,17 +8153,17 @@
       </c>
       <c r="I91" s="35" t="inlineStr">
         <is>
-          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
+          <t>Empty values are sent as empty.</t>
         </is>
       </c>
       <c r="J91" s="35" t="inlineStr">
         <is>
-          <t>Pick the code in Jameah Code Map and set Verified.</t>
+          <t>College code, campus city, study type (regular/bridging), program duration and unit.</t>
         </is>
       </c>
       <c r="K91" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-code-map</t>
+          <t>/app/jameah-settings</t>
         </is>
       </c>
       <c r="L91" s="34" t="inlineStr">
@@ -8175,7 +8175,7 @@
     <row r="92">
       <c r="A92" s="33" t="inlineStr">
         <is>
-          <t>JM-12</t>
+          <t>JM-11</t>
         </is>
       </c>
       <c r="B92" s="34" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>Ministry fields with no source in the college system</t>
+          <t>Map 3 college values to Ministry codes</t>
         </is>
       </c>
       <c r="D92" s="34" t="inlineStr">
@@ -8200,44 +8200,44 @@
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
-          <t>Academic Affairs + Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="G92" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Academic Affairs</t>
         </is>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I92" s="35" t="inlineStr">
         <is>
-          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
+          <t>Program 'Bachelor of Science in Nursing' -&gt; department; Major 'Sciences in Nursing'; status 'Internship' (238 students).</t>
         </is>
       </c>
       <c r="J92" s="35" t="inlineStr">
         <is>
-          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
+          <t>Pick the code in Jameah Code Map and set Verified.</t>
         </is>
       </c>
       <c r="K92" s="35" t="inlineStr">
         <is>
-          <t>Jameah report; VIEWS.md</t>
+          <t>/app/jameah-code-map</t>
         </is>
       </c>
       <c r="L92" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="33" t="inlineStr">
         <is>
-          <t>JM-13</t>
+          <t>JM-12</t>
         </is>
       </c>
       <c r="B93" s="34" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="C93" s="35" t="inlineStr">
         <is>
-          <t>Correct source data found by the checks</t>
+          <t>Ministry fields with no source in the college system</t>
         </is>
       </c>
       <c r="D93" s="34" t="inlineStr">
@@ -8257,37 +8257,37 @@
       </c>
       <c r="E93" s="34" t="inlineStr">
         <is>
-          <t>Pending – data / setup</t>
+          <t>Pending – decision needed</t>
         </is>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Academic Affairs + Abdul Hakeem</t>
         </is>
       </c>
       <c r="G93" s="34" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Abdul Hakeem</t>
         </is>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I93" s="35" t="inlineStr">
         <is>
-          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
+          <t>Students: scholarship, visa, warnings, rewards, clearance, thesis, evaluation grade, major type, language and relationship lists are sent empty. Faculty (added 21 Oct): research type/status/nature/domain/category, publisher, ISBN, edition, pages, publishing place, summary, language, key words; qualification research type, authentication, sub-level, included specialization; experience major/minor and job type; course type list.</t>
         </is>
       </c>
       <c r="J93" s="35" t="inlineStr">
         <is>
-          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
+          <t>Decide which to capture (Student Ministry Detail is filled for 1,256 of 3,357 students).</t>
         </is>
       </c>
       <c r="K93" s="35" t="inlineStr">
         <is>
-          <t>/app/jameah-data-check</t>
+          <t>Jameah report; VIEWS.md</t>
         </is>
       </c>
       <c r="L93" s="34" t="inlineStr">
@@ -8299,7 +8299,7 @@
     <row r="94">
       <c r="A94" s="33" t="inlineStr">
         <is>
-          <t>JM-14</t>
+          <t>JM-13</t>
         </is>
       </c>
       <c r="B94" s="34" t="inlineStr">
@@ -8309,27 +8309,27 @@
       </c>
       <c r="C94" s="35" t="inlineStr">
         <is>
-          <t>Faculty views (8 sections)</t>
+          <t>Correct source data found by the checks</t>
         </is>
       </c>
       <c r="D94" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E94" s="34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Pending – data / setup</t>
         </is>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="G94" s="34" t="inlineStr">
         <is>
-          <t>Abdul Hakeem</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="H94" s="34" t="inlineStr">
@@ -8339,29 +8339,29 @@
       </c>
       <c r="I94" s="35" t="inlineStr">
         <is>
-          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
+          <t>1,067 graduates still 'Enrolled'; 1,378 students on plans with no total credits; 1,266 relative addresses in Sri Lanka; 240 placeholder birth dates; 39 graduates without a graduate document; 7 enrollments without date; 6 orphan rows.</t>
         </is>
       </c>
       <c r="J94" s="35" t="inlineStr">
         <is>
-          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
+          <t>Fix at the source; the Jameah Data Check page shows the counts.</t>
         </is>
       </c>
       <c r="K94" s="35" t="inlineStr">
         <is>
-          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
+          <t>/app/jameah-data-check</t>
         </is>
       </c>
       <c r="L94" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="33" t="inlineStr">
         <is>
-          <t>JM-15</t>
+          <t>JM-14</t>
         </is>
       </c>
       <c r="B95" s="34" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="C95" s="35" t="inlineStr">
         <is>
-          <t>Institute views (20 sections)</t>
+          <t>Faculty views (8 sections)</t>
         </is>
       </c>
       <c r="D95" s="34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="E95" s="34" t="inlineStr">
         <is>
-          <t>Pending – development</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F95" s="34" t="inlineStr">
@@ -8396,22 +8396,22 @@
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I95" s="35" t="inlineStr">
         <is>
-          <t>Not started.</t>
+          <t>8 views (personal info, research, qualifications, academic experience, previous experience, certificates, awards, attachments) with the Ministry document's column names. Faculty = 168 active Instructors; personal data from the Instructor's Jameah fields, else the same person's Employee record; teaching staff are sent once (as Faculty, never as Employees). Rank / status / contract via the Code Map. Verified 8/8 value by value, 0 invalid codes; 5 unit tests. Data is thin until HR completes the Instructor sheet (HR-55).</t>
         </is>
       </c>
       <c r="J95" s="35" t="inlineStr">
         <is>
-          <t>Build after Faculty; needs institute data from HR.</t>
+          <t>Academic Affairs: DEC-12, DEC-13; Ministry: DEC-01.</t>
         </is>
       </c>
       <c r="K95" s="35" t="inlineStr">
         <is>
-          <t>MINISTRY_FIELD_MAPPING.html</t>
+          <t>jameah/views.py faculty_views; verify.py; VIEWS.md</t>
         </is>
       </c>
       <c r="L95" s="34" t="inlineStr">
@@ -8423,7 +8423,7 @@
     <row r="96">
       <c r="A96" s="33" t="inlineStr">
         <is>
-          <t>JM-16</t>
+          <t>JM-15</t>
         </is>
       </c>
       <c r="B96" s="34" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="C96" s="35" t="inlineStr">
         <is>
-          <t>Old viewJameah* views (42, earlier version)</t>
+          <t>Institute views (20 sections)</t>
         </is>
       </c>
       <c r="D96" s="34" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="E96" s="34" t="inlineStr">
         <is>
-          <t>Pending – decision needed</t>
+          <t>Pending – development</t>
         </is>
       </c>
       <c r="F96" s="34" t="inlineStr">
@@ -8458,95 +8458,157 @@
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I96" s="35" t="inlineStr">
         <is>
-          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+          <t>Not started.</t>
         </is>
       </c>
       <c r="J96" s="35" t="inlineStr">
         <is>
-          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+          <t>Build after Faculty; needs institute data from HR.</t>
         </is>
       </c>
       <c r="K96" s="35" t="inlineStr">
         <is>
-          <t>jameah_system (old views)</t>
+          <t>MINISTRY_FIELD_MAPPING.html</t>
         </is>
       </c>
       <c r="L96" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="33" t="inlineStr">
         <is>
+          <t>JM-16</t>
+        </is>
+      </c>
+      <c r="B97" s="34" t="inlineStr">
+        <is>
+          <t>Jameah</t>
+        </is>
+      </c>
+      <c r="C97" s="35" t="inlineStr">
+        <is>
+          <t>Old viewJameah* views (42, earlier version)</t>
+        </is>
+      </c>
+      <c r="D97" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" s="34" t="inlineStr">
+        <is>
+          <t>Pending – decision needed</t>
+        </is>
+      </c>
+      <c r="F97" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G97" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H97" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I97" s="35" t="inlineStr">
+        <is>
+          <t>Left untouched; they send record names and NULLs in places. Ours are named jameah*.</t>
+        </is>
+      </c>
+      <c r="J97" s="35" t="inlineStr">
+        <is>
+          <t>When the Ministry confirms our jameah* views (JM-09), decide whether the old viewJameah* views are dropped.</t>
+        </is>
+      </c>
+      <c r="K97" s="35" t="inlineStr">
+        <is>
+          <t>jameah_system (old views)</t>
+        </is>
+      </c>
+      <c r="L97" s="34" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="inlineStr">
+        <is>
           <t>JM-17</t>
         </is>
       </c>
-      <c r="B97" s="34" t="inlineStr">
+      <c r="B98" s="34" t="inlineStr">
         <is>
           <t>Jameah</t>
         </is>
       </c>
-      <c r="C97" s="35" t="inlineStr">
+      <c r="C98" s="35" t="inlineStr">
         <is>
           <t>Transcript GPA rounding at exact ties</t>
         </is>
       </c>
-      <c r="D97" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="E97" s="34" t="inlineStr">
+      <c r="D98" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E98" s="34" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="F97" s="34" t="inlineStr">
-        <is>
-          <t>Abdul Hakeem</t>
-        </is>
-      </c>
-      <c r="G97" s="34" t="inlineStr">
-        <is>
-          <t>Abdul Hakeem</t>
-        </is>
-      </c>
-      <c r="H97" s="34" t="inlineStr">
+      <c r="F98" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="G98" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+      <c r="H98" s="34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I97" s="35" t="inlineStr">
+      <c r="I98" s="35" t="inlineStr">
         <is>
           <t>Resolved by the college's official GPA calculation (exact half-up rounding); the Ministry views use it (JM-18).</t>
         </is>
       </c>
-      <c r="J97" s="35" t="inlineStr">
+      <c r="J98" s="35" t="inlineStr">
         <is>
           <t>None.</t>
         </is>
       </c>
-      <c r="K97" s="35" t="inlineStr">
+      <c r="K98" s="35" t="inlineStr">
         <is>
           <t>Jameah report</t>
         </is>
       </c>
-      <c r="L97" s="34" t="inlineStr">
+      <c r="L98" s="34" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L97"/>
-  <conditionalFormatting sqref="E2:E297">
+  <autoFilter ref="A1:L98"/>
+  <conditionalFormatting sqref="E2:E298">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$E2="Done"</formula>
     </cfRule>
@@ -8572,7 +8634,7 @@
       <formula>$E2="Planned"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H297">
+  <conditionalFormatting sqref="H2:H298">
     <cfRule type="expression" priority="9" dxfId="8" stopIfTrue="1">
       <formula>$H2="Critical"</formula>
     </cfRule>
@@ -8587,13 +8649,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E2:E297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
+    <dataValidation sqref="E2:E298" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Status" error="Pick a status from the list." type="list">
       <formula1>"Done,Done – client UAT pending,In progress,Pending – decision needed,Pending – data / setup,Pending – development,Pending – other team,Planned"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H298" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G298" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Abdul Hakeem,Fathir,Dinesh,Testing team,To assign"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8607,7 +8669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11589,58 +11651,162 @@
     <row r="58">
       <c r="A58" s="34" t="inlineStr">
         <is>
+          <t>B-58</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C58" s="34" t="inlineStr">
+        <is>
+          <t>Advisor dashboard (education app)</t>
+        </is>
+      </c>
+      <c r="D58" s="35" t="inlineStr">
+        <is>
+          <t>The browser console shows 'frappe.get_open_dialog is not a function' (3 times) when the Advisor dashboard opens</t>
+        </is>
+      </c>
+      <c r="E58" s="35" t="inlineStr">
+        <is>
+          <t>advisor_dashboard.js in the education app calls a function this Frappe version does not have; not caused by Medical HRMS (the My HR card is placed after the page has loaded)</t>
+        </is>
+      </c>
+      <c r="F58" s="35" t="inlineStr">
+        <is>
+          <t>Education app owner to replace the call; Medical HRMS does not change the education app</t>
+        </is>
+      </c>
+      <c r="G58" s="34" t="inlineStr">
+        <is>
+          <t>HR-11</t>
+        </is>
+      </c>
+      <c r="H58" s="34" t="inlineStr">
+        <is>
+          <t>Open – other team</t>
+        </is>
+      </c>
+      <c r="I58" s="35" t="inlineStr">
+        <is>
+          <t>Round 3 dashboard check</t>
+        </is>
+      </c>
+      <c r="J58" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>B-59</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C59" s="34" t="inlineStr">
+        <is>
+          <t>My HR card (Round 3)</t>
+        </is>
+      </c>
+      <c r="D59" s="35" t="inlineStr">
+        <is>
+          <t>Every list and form page logged 'Cannot read properties of null (reading 0)' in the browser console</t>
+        </is>
+      </c>
+      <c r="E59" s="35" t="inlineStr">
+        <is>
+          <t>At the first page load the card script asked for the page name before Frappe had a route</t>
+        </is>
+      </c>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t>Checks for no route first (staff_hr_card.js); found by the full browser run before release</t>
+        </is>
+      </c>
+      <c r="G59" s="34" t="inlineStr">
+        <is>
+          <t>HR-11</t>
+        </is>
+      </c>
+      <c r="H59" s="34" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I59" s="35" t="inlineStr">
+        <is>
+          <t>Error sweep SWP-01 - 04, HRD-03</t>
+        </is>
+      </c>
+      <c r="J59" s="34" t="inlineStr">
+        <is>
+          <t>27 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
           <t>B-27</t>
         </is>
       </c>
-      <c r="B58" s="34" t="inlineStr">
-        <is>
-          <t>21 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C58" s="34" t="inlineStr">
+      <c r="B60" s="34" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C60" s="34" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="D58" s="35" t="inlineStr">
+      <c r="D60" s="35" t="inlineStr">
         <is>
           <t>Logo file missing (/files/rchs-logo.png)</t>
         </is>
       </c>
-      <c r="E58" s="35" t="inlineStr">
+      <c r="E60" s="35" t="inlineStr">
         <is>
           <t>File not on this copy</t>
         </is>
       </c>
-      <c r="F58" s="35" t="inlineStr">
+      <c r="F60" s="35" t="inlineStr">
         <is>
           <t>Check on the live server</t>
         </is>
       </c>
-      <c r="G58" s="34" t="inlineStr">
+      <c r="G60" s="34" t="inlineStr">
         <is>
           <t>HR-54</t>
         </is>
       </c>
-      <c r="H58" s="34" t="inlineStr">
+      <c r="H60" s="34" t="inlineStr">
         <is>
           <t>Open – check server</t>
         </is>
       </c>
-      <c r="I58" s="35" t="inlineStr">
+      <c r="I60" s="35" t="inlineStr">
         <is>
           <t>Error sweep</t>
         </is>
       </c>
-      <c r="J58" s="34" t="inlineStr">
+      <c r="J60" s="34" t="inlineStr">
         <is>
           <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J58"/>
-  <conditionalFormatting sqref="H2:H158">
+  <autoFilter ref="A1:J60"/>
+  <conditionalFormatting sqref="H2:H160">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="Fixed"</formula>
     </cfRule>
@@ -11655,7 +11821,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Fixed,Open,Open – other team,Open – check server"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12288,7 +12454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12333,17 +12499,17 @@
       </c>
       <c r="B2" s="34" t="inlineStr">
         <is>
-          <t>Leave e-mails</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C2" s="35" t="inlineStr">
         <is>
-          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
+          <t>HR-11, HR-78, B-58, B-59, CL-42, TC-STF-01 - TC-STF-10</t>
         </is>
       </c>
       <c r="D2" s="35" t="inlineStr">
         <is>
-          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
+          <t>Round 3: a My HR card on the education staff dashboards (Instructor, Department Head, Dean, Vice Deans, IT, Academic Operations, Student Affairs, Admission, Finance, Clinical, Advisor) for logins linked to an Employee record: leave balances and what's next, the latest requests, Apply for Leave, New Request and View, with the Employee Portal's own windows (now shared: public/js/self_service.js). Nothing in the education app changed. New: the Round 3 document for the testers, 10 test cases (Round 3), User Guide section 2.11, Installation Guide troubleshooting, QA logins qa.hod, qa.dean, qa.staff.nolink. Tested: 111/111 browser checks (10 new: SHR-01 - SHR-10), 53 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; card placement checked on 11 staff dashboards (8 with figures, Advisor under its heading, Dean and Department Head in the browser tests); Error Log: only test-caused entries, removed. The full run caught a script error of the card on every other page (B-59), fixed before release.</t>
         </is>
       </c>
       <c r="E2" s="34" t="inlineStr">
@@ -12360,17 +12526,17 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Leave e-mails</t>
         </is>
       </c>
       <c r="C3" s="35" t="inlineStr">
         <is>
-          <t>HR-76</t>
+          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
         </is>
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
-          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
+          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
         </is>
       </c>
       <c r="E3" s="34" t="inlineStr">
@@ -12387,17 +12553,17 @@
       </c>
       <c r="B4" s="34" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D4" s="35" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E4" s="34" t="inlineStr">
@@ -12414,17 +12580,17 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E5" s="34" t="inlineStr">
@@ -12436,22 +12602,22 @@
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C6" s="35" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D6" s="35" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -12473,12 +12639,12 @@
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D7" s="35" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -12495,17 +12661,17 @@
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D8" s="35" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -12527,12 +12693,12 @@
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -12549,17 +12715,17 @@
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C10" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D10" s="35" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -12571,7 +12737,7 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
@@ -12581,12 +12747,12 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -12608,12 +12774,12 @@
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -12630,17 +12796,17 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
@@ -12652,22 +12818,22 @@
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
@@ -12684,17 +12850,17 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
@@ -12711,17 +12877,17 @@
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
@@ -12733,7 +12899,7 @@
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
@@ -12743,12 +12909,12 @@
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
@@ -12760,7 +12926,7 @@
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
@@ -12770,12 +12936,12 @@
       </c>
       <c r="C18" s="35" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
@@ -12787,32 +12953,59 @@
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="E20" s="34" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>